--- a/gstdatabase/GSTR-1-2022-2023.xlsx
+++ b/gstdatabase/GSTR-1-2022-2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395FBB4F-24FE-46FD-9F5C-3F30475A1387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DD1C8E-6DDE-4076-AA9A-3787F9261610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -182,10 +182,10 @@
     <t>Gujarat</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -1021,14 +1021,14 @@
       </c>
       <c r="E10" s="3">
         <f>F10-D10</f>
-        <v>38322</v>
+        <v>38323</v>
       </c>
       <c r="F10" s="5">
-        <v>63070</v>
+        <v>63071</v>
       </c>
       <c r="G10" s="4">
         <f>F10/C10</f>
-        <v>0.95073713407096994</v>
+        <v>0.95075220838734964</v>
       </c>
       <c r="H10" s="5">
         <v>68361</v>
@@ -1038,14 +1038,14 @@
       </c>
       <c r="J10" s="3">
         <f>K10-I10</f>
-        <v>36249</v>
+        <v>36250</v>
       </c>
       <c r="K10" s="5">
-        <v>64493</v>
+        <v>64494</v>
       </c>
       <c r="L10" s="4">
         <f>K10/H10</f>
-        <v>0.94341803074852626</v>
+        <v>0.94343265897222095</v>
       </c>
       <c r="M10" s="9">
         <v>109205</v>
@@ -1057,11 +1057,11 @@
         <v>101752</v>
       </c>
       <c r="P10" s="5">
-        <v>102088</v>
+        <v>102092</v>
       </c>
       <c r="Q10" s="4">
         <f>P10/M10</f>
-        <v>0.93482899134655006</v>
+        <v>0.93486561970605742</v>
       </c>
       <c r="R10" s="5">
         <v>68216</v>
@@ -1071,14 +1071,14 @@
       </c>
       <c r="T10" s="3">
         <f>U10-S10</f>
-        <v>36271</v>
+        <v>36273</v>
       </c>
       <c r="U10" s="5">
-        <v>64406</v>
+        <v>64408</v>
       </c>
       <c r="V10" s="4">
         <f>U10/R10</f>
-        <v>0.94414800046909819</v>
+        <v>0.94417731910402247</v>
       </c>
       <c r="W10" s="5">
         <v>69437</v>
@@ -1088,14 +1088,14 @@
       </c>
       <c r="Y10" s="3">
         <f>Z10-X10</f>
-        <v>38320</v>
+        <v>38322</v>
       </c>
       <c r="Z10" s="5">
-        <v>65688</v>
+        <v>65690</v>
       </c>
       <c r="AA10" s="4">
         <f>Z10/W10</f>
-        <v>0.94600861212321963</v>
+        <v>0.94603741521091056</v>
       </c>
       <c r="AB10" s="5">
         <v>112849</v>
@@ -1105,14 +1105,14 @@
       </c>
       <c r="AD10" s="3">
         <f>AE10-AC10</f>
-        <v>69972</v>
+        <v>69974</v>
       </c>
       <c r="AE10" s="5">
-        <v>112568</v>
+        <v>112570</v>
       </c>
       <c r="AF10" s="4">
         <f>AE10/AB10</f>
-        <v>0.99750994692022088</v>
+        <v>0.99752766971794171</v>
       </c>
       <c r="AG10" s="5">
         <v>69494</v>
@@ -1122,14 +1122,14 @@
       </c>
       <c r="AI10" s="3">
         <f>AJ10-AH10</f>
-        <v>39144</v>
+        <v>39145</v>
       </c>
       <c r="AJ10" s="5">
-        <v>69258</v>
+        <v>69259</v>
       </c>
       <c r="AK10" s="4">
         <f>AJ10/AG10</f>
-        <v>0.99660402336892395</v>
+        <v>0.99661841310041155</v>
       </c>
       <c r="AL10" s="5">
         <v>70757</v>
@@ -1139,14 +1139,14 @@
       </c>
       <c r="AN10" s="3">
         <f>AO10-AM10</f>
-        <v>39793</v>
+        <v>39794</v>
       </c>
       <c r="AO10" s="5">
-        <v>70293</v>
+        <v>70294</v>
       </c>
       <c r="AP10" s="4">
         <f>AO10/AL10</f>
-        <v>0.99344234492700367</v>
+        <v>0.99345647780431623</v>
       </c>
       <c r="AQ10" s="3">
         <v>115882</v>
@@ -1156,14 +1156,14 @@
       </c>
       <c r="AS10" s="3">
         <f>AT10-AR10</f>
-        <v>67750</v>
+        <v>67753</v>
       </c>
       <c r="AT10" s="3">
-        <v>114939</v>
+        <v>114942</v>
       </c>
       <c r="AU10" s="4">
         <f>AT10/AQ10</f>
-        <v>0.99186241176369061</v>
+        <v>0.9918883001674117</v>
       </c>
       <c r="AV10" s="5">
         <v>70382</v>
@@ -1173,14 +1173,14 @@
       </c>
       <c r="AX10" s="3">
         <f>AY10-AW10</f>
-        <v>37837</v>
+        <v>37838</v>
       </c>
       <c r="AY10" s="5">
-        <v>69377</v>
+        <v>69378</v>
       </c>
       <c r="AZ10" s="4">
         <f>AY10/AV10</f>
-        <v>0.98572078088147541</v>
+        <v>0.9857349890597028</v>
       </c>
       <c r="BA10" s="10">
         <v>70494</v>
@@ -1190,14 +1190,14 @@
       </c>
       <c r="BC10" s="3">
         <f>BD10-BB10</f>
-        <v>38937</v>
+        <v>38938</v>
       </c>
       <c r="BD10" s="5">
-        <v>70595</v>
+        <v>70596</v>
       </c>
       <c r="BE10" s="4">
         <f>BD10/BA10</f>
-        <v>1.0014327460493091</v>
+        <v>1.0014469316537578</v>
       </c>
       <c r="BF10" s="10">
         <v>117563</v>
@@ -1207,14 +1207,14 @@
       </c>
       <c r="BH10" s="3">
         <f>BI10-BG10</f>
-        <v>74254</v>
+        <v>74256</v>
       </c>
       <c r="BI10" s="5">
-        <v>117780</v>
+        <v>117782</v>
       </c>
       <c r="BJ10" s="4">
         <f>BI10/BF10</f>
-        <v>1.0018458188375594</v>
+        <v>1.0018628309927444</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1232,14 +1232,14 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" ref="E11:E47" si="0">F11-D11</f>
-        <v>17925</v>
+        <v>17927</v>
       </c>
       <c r="F11" s="5">
-        <v>42554</v>
+        <v>42556</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" ref="G11:G47" si="1">F11/C11</f>
-        <v>0.96006678097644615</v>
+        <v>0.96011190325782869</v>
       </c>
       <c r="H11" s="5">
         <v>45199</v>
@@ -1249,14 +1249,14 @@
       </c>
       <c r="J11" s="3">
         <f t="shared" ref="J11:J47" si="2">K11-I11</f>
-        <v>17714</v>
+        <v>17716</v>
       </c>
       <c r="K11" s="5">
-        <v>43480</v>
+        <v>43482</v>
       </c>
       <c r="L11" s="4">
         <f t="shared" ref="L11:L47" si="3">K11/H11</f>
-        <v>0.96196818513683935</v>
+        <v>0.96201243390340496</v>
       </c>
       <c r="M11" s="9">
         <v>98966</v>
@@ -1268,11 +1268,11 @@
         <v>95308</v>
       </c>
       <c r="P11" s="5">
-        <v>95536</v>
+        <v>95538</v>
       </c>
       <c r="Q11" s="4">
         <f t="shared" ref="Q11:Q47" si="4">P11/M11</f>
-        <v>0.96534163247984162</v>
+        <v>0.96536184144049475</v>
       </c>
       <c r="R11" s="5">
         <v>44504</v>
@@ -1282,14 +1282,14 @@
       </c>
       <c r="T11" s="3">
         <f t="shared" ref="T11:T47" si="5">U11-S11</f>
-        <v>17484</v>
+        <v>17487</v>
       </c>
       <c r="U11" s="5">
-        <v>42545</v>
+        <v>42548</v>
       </c>
       <c r="V11" s="4">
         <f t="shared" ref="V11:V47" si="6">U11/R11</f>
-        <v>0.95598148481035417</v>
+        <v>0.95604889448139496</v>
       </c>
       <c r="W11" s="5">
         <v>45023</v>
@@ -1299,14 +1299,14 @@
       </c>
       <c r="Y11" s="3">
         <f t="shared" ref="Y11:Y47" si="7">Z11-X11</f>
-        <v>19084</v>
+        <v>19086</v>
       </c>
       <c r="Z11" s="5">
-        <v>43350</v>
+        <v>43352</v>
       </c>
       <c r="AA11" s="4">
         <f t="shared" ref="AA11:AA47" si="8">Z11/W11</f>
-        <v>0.96284121449037163</v>
+        <v>0.96288563623037116</v>
       </c>
       <c r="AB11" s="5">
         <v>99888</v>
@@ -1316,14 +1316,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD47" si="9">AE11-AC11</f>
-        <v>49058</v>
+        <v>49059</v>
       </c>
       <c r="AE11" s="5">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF47" si="10">AE11/AB11</f>
-        <v>0.97673394201505681</v>
+        <v>0.97674395322761498</v>
       </c>
       <c r="AG11" s="5">
         <v>44744</v>
@@ -1333,14 +1333,14 @@
       </c>
       <c r="AI11" s="3">
         <f t="shared" ref="AI11:AI47" si="11">AJ11-AH11</f>
-        <v>16570</v>
+        <v>16571</v>
       </c>
       <c r="AJ11" s="5">
-        <v>43113</v>
+        <v>43114</v>
       </c>
       <c r="AK11" s="4">
         <f t="shared" ref="AK11:AK47" si="12">AJ11/AG11</f>
-        <v>0.9635481852315394</v>
+        <v>0.96357053459681741</v>
       </c>
       <c r="AL11" s="5">
         <v>45303</v>
@@ -1350,14 +1350,14 @@
       </c>
       <c r="AN11" s="3">
         <f t="shared" ref="AN11:AN47" si="13">AO11-AM11</f>
-        <v>17188</v>
+        <v>17189</v>
       </c>
       <c r="AO11" s="5">
-        <v>43683</v>
+        <v>43684</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" ref="AP11:AP47" si="14">AO11/AL11</f>
-        <v>0.96424077875637371</v>
+        <v>0.96426285234973397</v>
       </c>
       <c r="AQ11" s="3">
         <v>100769</v>
@@ -1367,14 +1367,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS47" si="15">AT11-AR11</f>
-        <v>43285</v>
+        <v>43286</v>
       </c>
       <c r="AT11" s="3">
-        <v>98528</v>
+        <v>98529</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU47" si="16">AT11/AQ11</f>
-        <v>0.97776101777332314</v>
+        <v>0.97777094146017129</v>
       </c>
       <c r="AV11" s="5">
         <v>46153</v>
@@ -1384,14 +1384,14 @@
       </c>
       <c r="AX11" s="3">
         <f t="shared" ref="AX11:AX47" si="17">AY11-AW11</f>
-        <v>14950</v>
+        <v>14951</v>
       </c>
       <c r="AY11" s="5">
-        <v>43455</v>
+        <v>43456</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" ref="AZ11:AZ47" si="18">AY11/AV11</f>
-        <v>0.94154226160812948</v>
+        <v>0.94156392867202565</v>
       </c>
       <c r="BA11" s="10">
         <v>44735</v>
@@ -1401,14 +1401,14 @@
       </c>
       <c r="BC11" s="3">
         <f t="shared" ref="BC11:BC47" si="19">BD11-BB11</f>
-        <v>16367</v>
+        <v>16368</v>
       </c>
       <c r="BD11" s="5">
-        <v>44639</v>
+        <v>44640</v>
       </c>
       <c r="BE11" s="4">
         <f t="shared" ref="BE11:BE47" si="20">BD11/BA11</f>
-        <v>0.99785402928355871</v>
+        <v>0.99787638314518834</v>
       </c>
       <c r="BF11" s="10">
         <v>99991</v>
@@ -1418,14 +1418,14 @@
       </c>
       <c r="BH11" s="3">
         <f t="shared" ref="BH11:BH33" si="21">BI11-BG11</f>
-        <v>49939</v>
+        <v>49942</v>
       </c>
       <c r="BI11" s="5">
-        <v>100932</v>
+        <v>100935</v>
       </c>
       <c r="BJ11" s="4">
         <f t="shared" ref="BJ11:BJ33" si="22">BI11/BF11</f>
-        <v>1.009410846976228</v>
+        <v>1.0094408496764709</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1443,14 +1443,14 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>34891</v>
+        <v>34892</v>
       </c>
       <c r="F12" s="5">
-        <v>154331</v>
+        <v>154332</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="1"/>
-        <v>0.93615640316397342</v>
+        <v>0.93616246906391032</v>
       </c>
       <c r="H12" s="5">
         <v>167213</v>
@@ -1460,14 +1460,14 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="2"/>
-        <v>33863</v>
+        <v>33864</v>
       </c>
       <c r="K12" s="5">
-        <v>157645</v>
+        <v>157646</v>
       </c>
       <c r="L12" s="4">
         <f t="shared" si="3"/>
-        <v>0.94277956857421374</v>
+        <v>0.94278554897047473</v>
       </c>
       <c r="M12" s="9">
         <v>342449</v>
@@ -1479,11 +1479,11 @@
         <v>324491</v>
       </c>
       <c r="P12" s="5">
-        <v>324807</v>
+        <v>324809</v>
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="4"/>
-        <v>0.94848283978052206</v>
+        <v>0.94848868006622888</v>
       </c>
       <c r="R12" s="5">
         <v>167538</v>
@@ -1493,14 +1493,14 @@
       </c>
       <c r="T12" s="3">
         <f t="shared" si="5"/>
-        <v>36314</v>
+        <v>36315</v>
       </c>
       <c r="U12" s="5">
-        <v>156768</v>
+        <v>156769</v>
       </c>
       <c r="V12" s="4">
         <f t="shared" si="6"/>
-        <v>0.93571607635282739</v>
+        <v>0.93572204514796642</v>
       </c>
       <c r="W12" s="5">
         <v>169859</v>
@@ -1510,14 +1510,14 @@
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="7"/>
-        <v>38460</v>
+        <v>38461</v>
       </c>
       <c r="Z12" s="5">
-        <v>159340</v>
+        <v>159341</v>
       </c>
       <c r="AA12" s="4">
         <f t="shared" si="8"/>
-        <v>0.93807216573746466</v>
+        <v>0.93807805297334845</v>
       </c>
       <c r="AB12" s="5">
         <v>346997</v>
@@ -1527,14 +1527,14 @@
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="9"/>
-        <v>94415</v>
+        <v>94417</v>
       </c>
       <c r="AE12" s="5">
-        <v>332060</v>
+        <v>332062</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="10"/>
-        <v>0.95695351833012965</v>
+        <v>0.95695928206872105</v>
       </c>
       <c r="AG12" s="5">
         <v>170493</v>
@@ -1544,14 +1544,14 @@
       </c>
       <c r="AI12" s="3">
         <f t="shared" si="11"/>
-        <v>34202</v>
+        <v>34203</v>
       </c>
       <c r="AJ12" s="5">
-        <v>160006</v>
+        <v>160007</v>
       </c>
       <c r="AK12" s="4">
         <f t="shared" si="12"/>
-        <v>0.93849014329034042</v>
+        <v>0.93849600863378557</v>
       </c>
       <c r="AL12" s="5">
         <v>172338</v>
@@ -1561,14 +1561,14 @@
       </c>
       <c r="AN12" s="3">
         <f t="shared" si="13"/>
-        <v>35480</v>
+        <v>35481</v>
       </c>
       <c r="AO12" s="5">
-        <v>162426</v>
+        <v>162427</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="14"/>
-        <v>0.94248511645719457</v>
+        <v>0.94249091900799586</v>
       </c>
       <c r="AQ12" s="3">
         <v>350104</v>
@@ -1578,14 +1578,14 @@
       </c>
       <c r="AS12" s="3">
         <f t="shared" si="15"/>
-        <v>82934</v>
+        <v>82936</v>
       </c>
       <c r="AT12" s="3">
-        <v>335793</v>
+        <v>335795</v>
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="16"/>
-        <v>0.95912357470922927</v>
+        <v>0.9591292872974887</v>
       </c>
       <c r="AV12" s="5">
         <v>177002</v>
@@ -1595,14 +1595,14 @@
       </c>
       <c r="AX12" s="3">
         <f t="shared" si="17"/>
-        <v>29965</v>
+        <v>29966</v>
       </c>
       <c r="AY12" s="5">
-        <v>162049</v>
+        <v>162050</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="18"/>
-        <v>0.91552072857933808</v>
+        <v>0.9155263782330143</v>
       </c>
       <c r="BA12" s="10">
         <v>166689</v>
@@ -1612,14 +1612,14 @@
       </c>
       <c r="BC12" s="3">
         <f t="shared" si="19"/>
-        <v>31825</v>
+        <v>31826</v>
       </c>
       <c r="BD12" s="5">
-        <v>164474</v>
+        <v>164475</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="20"/>
-        <v>0.98671178062139675</v>
+        <v>0.98671777981750441</v>
       </c>
       <c r="BF12" s="10">
         <v>341156</v>
@@ -1629,14 +1629,14 @@
       </c>
       <c r="BH12" s="3">
         <f t="shared" si="21"/>
-        <v>93915</v>
+        <v>93920</v>
       </c>
       <c r="BI12" s="5">
-        <v>340509</v>
+        <v>340514</v>
       </c>
       <c r="BJ12" s="4">
         <f t="shared" si="22"/>
-        <v>0.99810350690006922</v>
+        <v>0.99811816295184608</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1789,14 +1789,14 @@
       </c>
       <c r="AS13" s="3">
         <f t="shared" si="15"/>
-        <v>6208</v>
+        <v>6209</v>
       </c>
       <c r="AT13" s="3">
-        <v>27561</v>
+        <v>27562</v>
       </c>
       <c r="AU13" s="4">
         <f t="shared" si="16"/>
-        <v>0.98099305926321412</v>
+        <v>0.98102865278519313</v>
       </c>
       <c r="AV13" s="5">
         <v>16929</v>
@@ -1865,14 +1865,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>34889</v>
+        <v>34890</v>
       </c>
       <c r="F14" s="5">
-        <v>77290</v>
+        <v>77291</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>0.93345410628019321</v>
+        <v>0.9334661835748792</v>
       </c>
       <c r="H14" s="5">
         <v>84757</v>
@@ -1882,14 +1882,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>34519</v>
+        <v>34523</v>
       </c>
       <c r="K14" s="5">
-        <v>79130</v>
+        <v>79134</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.93361020328704414</v>
+        <v>0.93365739702915396</v>
       </c>
       <c r="M14" s="9">
         <v>154914</v>
@@ -1901,11 +1901,11 @@
         <v>144482</v>
       </c>
       <c r="P14" s="5">
-        <v>145034</v>
+        <v>145045</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="4"/>
-        <v>0.93622267838929984</v>
+        <v>0.93629368552874503</v>
       </c>
       <c r="R14" s="5">
         <v>85475</v>
@@ -1915,14 +1915,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="5"/>
-        <v>36052</v>
+        <v>36055</v>
       </c>
       <c r="U14" s="5">
-        <v>78721</v>
+        <v>78724</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="6"/>
-        <v>0.92098274349224918</v>
+        <v>0.92101784147411525</v>
       </c>
       <c r="W14" s="5">
         <v>86445</v>
@@ -1932,14 +1932,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="7"/>
-        <v>36733</v>
+        <v>36736</v>
       </c>
       <c r="Z14" s="5">
-        <v>80012</v>
+        <v>80015</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="8"/>
-        <v>0.92558274047081956</v>
+        <v>0.92561744461796513</v>
       </c>
       <c r="AB14" s="5">
         <v>156524</v>
@@ -1949,14 +1949,14 @@
       </c>
       <c r="AD14" s="3">
         <f t="shared" si="9"/>
-        <v>77491</v>
+        <v>77498</v>
       </c>
       <c r="AE14" s="5">
-        <v>149291</v>
+        <v>149298</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="10"/>
-        <v>0.95378983414684015</v>
+        <v>0.95383455572308395</v>
       </c>
       <c r="AG14" s="5">
         <v>86459</v>
@@ -1966,14 +1966,14 @@
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="11"/>
-        <v>34523</v>
+        <v>34526</v>
       </c>
       <c r="AJ14" s="5">
-        <v>81191</v>
+        <v>81194</v>
       </c>
       <c r="AK14" s="4">
         <f t="shared" si="12"/>
-        <v>0.9390693854890757</v>
+        <v>0.93910408401670153</v>
       </c>
       <c r="AL14" s="5">
         <v>87786</v>
@@ -1983,14 +1983,14 @@
       </c>
       <c r="AN14" s="3">
         <f t="shared" si="13"/>
-        <v>34695</v>
+        <v>34698</v>
       </c>
       <c r="AO14" s="5">
-        <v>82758</v>
+        <v>82761</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="14"/>
-        <v>0.94272435240243324</v>
+        <v>0.94275852641651292</v>
       </c>
       <c r="AQ14" s="3">
         <v>158597</v>
@@ -2000,14 +2000,14 @@
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="15"/>
-        <v>69811</v>
+        <v>69820</v>
       </c>
       <c r="AT14" s="3">
-        <v>151804</v>
+        <v>151813</v>
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="16"/>
-        <v>0.95716816837645102</v>
+        <v>0.95722491598201731</v>
       </c>
       <c r="AV14" s="5">
         <v>90863</v>
@@ -2017,14 +2017,14 @@
       </c>
       <c r="AX14" s="3">
         <f t="shared" si="17"/>
-        <v>32097</v>
+        <v>32101</v>
       </c>
       <c r="AY14" s="5">
-        <v>83338</v>
+        <v>83342</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="18"/>
-        <v>0.91718301178697603</v>
+        <v>0.91722703410629192</v>
       </c>
       <c r="BA14" s="10">
         <v>86219</v>
@@ -2034,14 +2034,14 @@
       </c>
       <c r="BC14" s="3">
         <f t="shared" si="19"/>
-        <v>35282</v>
+        <v>35287</v>
       </c>
       <c r="BD14" s="5">
-        <v>85160</v>
+        <v>85165</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="20"/>
-        <v>0.98771732448764193</v>
+        <v>0.98777531634558513</v>
       </c>
       <c r="BF14" s="10">
         <v>155639</v>
@@ -2051,14 +2051,14 @@
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="21"/>
-        <v>76819</v>
+        <v>76837</v>
       </c>
       <c r="BI14" s="5">
-        <v>155131</v>
+        <v>155149</v>
       </c>
       <c r="BJ14" s="4">
         <f t="shared" si="22"/>
-        <v>0.99673603659751087</v>
+        <v>0.99685168884405584</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2143,14 +2143,14 @@
       </c>
       <c r="Y15" s="3">
         <f t="shared" si="7"/>
-        <v>76238</v>
+        <v>76239</v>
       </c>
       <c r="Z15" s="5">
-        <v>266101</v>
+        <v>266102</v>
       </c>
       <c r="AA15" s="4">
         <f t="shared" si="8"/>
-        <v>0.95236748863677034</v>
+        <v>0.95237106760674273</v>
       </c>
       <c r="AB15" s="5">
         <v>484645</v>
@@ -2160,14 +2160,14 @@
       </c>
       <c r="AD15" s="3">
         <f t="shared" si="9"/>
-        <v>149016</v>
+        <v>149017</v>
       </c>
       <c r="AE15" s="5">
-        <v>466046</v>
+        <v>466047</v>
       </c>
       <c r="AF15" s="4">
         <f t="shared" si="10"/>
-        <v>0.96162345634433455</v>
+        <v>0.96162551971030341</v>
       </c>
       <c r="AG15" s="5">
         <v>282622</v>
@@ -2177,14 +2177,14 @@
       </c>
       <c r="AI15" s="3">
         <f t="shared" si="11"/>
-        <v>69865</v>
+        <v>69866</v>
       </c>
       <c r="AJ15" s="5">
-        <v>268529</v>
+        <v>268530</v>
       </c>
       <c r="AK15" s="4">
         <f t="shared" si="12"/>
-        <v>0.95013480903822067</v>
+        <v>0.95013834733318714</v>
       </c>
       <c r="AL15" s="5">
         <v>285773</v>
@@ -2194,14 +2194,14 @@
       </c>
       <c r="AN15" s="3">
         <f t="shared" si="13"/>
-        <v>72078</v>
+        <v>72079</v>
       </c>
       <c r="AO15" s="5">
-        <v>272715</v>
+        <v>272716</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="14"/>
-        <v>0.95430639003684747</v>
+        <v>0.95430988931774519</v>
       </c>
       <c r="AQ15" s="3">
         <v>491220</v>
@@ -2211,14 +2211,14 @@
       </c>
       <c r="AS15" s="3">
         <f t="shared" si="15"/>
-        <v>128569</v>
+        <v>128570</v>
       </c>
       <c r="AT15" s="3">
-        <v>473152</v>
+        <v>473153</v>
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="16"/>
-        <v>0.96321811001180735</v>
+        <v>0.96322014575953752</v>
       </c>
       <c r="AV15" s="5">
         <v>292625</v>
@@ -2228,14 +2228,14 @@
       </c>
       <c r="AX15" s="3">
         <f t="shared" si="17"/>
-        <v>61931</v>
+        <v>61932</v>
       </c>
       <c r="AY15" s="5">
-        <v>274841</v>
+        <v>274842</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="18"/>
-        <v>0.93922597180692013</v>
+        <v>0.93922938914993592</v>
       </c>
       <c r="BA15" s="10">
         <v>283148</v>
@@ -2245,14 +2245,14 @@
       </c>
       <c r="BC15" s="3">
         <f t="shared" si="19"/>
-        <v>67150</v>
+        <v>67151</v>
       </c>
       <c r="BD15" s="5">
-        <v>280073</v>
+        <v>280074</v>
       </c>
       <c r="BE15" s="4">
         <f t="shared" si="20"/>
-        <v>0.9891399550764971</v>
+        <v>0.98914348679842345</v>
       </c>
       <c r="BF15" s="10">
         <v>485122</v>
@@ -2262,14 +2262,14 @@
       </c>
       <c r="BH15" s="3">
         <f t="shared" si="21"/>
-        <v>144899</v>
+        <v>144900</v>
       </c>
       <c r="BI15" s="5">
-        <v>482978</v>
+        <v>482979</v>
       </c>
       <c r="BJ15" s="4">
         <f t="shared" si="22"/>
-        <v>0.99558049315429931</v>
+        <v>0.9955825544914475</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2287,14 +2287,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>106331</v>
+        <v>106337</v>
       </c>
       <c r="F16" s="5">
-        <v>390215</v>
+        <v>390221</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.95108973827757493</v>
+        <v>0.95110436236539742</v>
       </c>
       <c r="H16" s="5">
         <v>416018</v>
@@ -2304,14 +2304,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>103636</v>
+        <v>103643</v>
       </c>
       <c r="K16" s="5">
-        <v>398177</v>
+        <v>398184</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.95711483637727213</v>
+        <v>0.95713166257229254</v>
       </c>
       <c r="M16" s="9">
         <v>750813</v>
@@ -2323,11 +2323,11 @@
         <v>716590</v>
       </c>
       <c r="P16" s="5">
-        <v>717990</v>
+        <v>718005</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="4"/>
-        <v>0.95628338880653374</v>
+        <v>0.95630336715000941</v>
       </c>
       <c r="R16" s="5">
         <v>419109</v>
@@ -2337,14 +2337,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="5"/>
-        <v>111539</v>
+        <v>111548</v>
       </c>
       <c r="U16" s="5">
-        <v>399082</v>
+        <v>399091</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="6"/>
-        <v>0.95221529482783718</v>
+        <v>0.95223676895509279</v>
       </c>
       <c r="W16" s="5">
         <v>423539</v>
@@ -2354,14 +2354,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="7"/>
-        <v>110425</v>
+        <v>110434</v>
       </c>
       <c r="Z16" s="5">
-        <v>405265</v>
+        <v>405274</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="8"/>
-        <v>0.95685403233232358</v>
+        <v>0.95687528185125814</v>
       </c>
       <c r="AB16" s="5">
         <v>762171</v>
@@ -2371,14 +2371,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="9"/>
-        <v>204070</v>
+        <v>204088</v>
       </c>
       <c r="AE16" s="5">
-        <v>732804</v>
+        <v>732822</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="10"/>
-        <v>0.96146927657966519</v>
+        <v>0.96149289332708798</v>
       </c>
       <c r="AG16" s="5">
         <v>429452</v>
@@ -2388,14 +2388,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="11"/>
-        <v>106263</v>
+        <v>106273</v>
       </c>
       <c r="AJ16" s="5">
-        <v>410488</v>
+        <v>410498</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="12"/>
-        <v>0.95584139787450051</v>
+        <v>0.95586468336391495</v>
       </c>
       <c r="AL16" s="5">
         <v>434676</v>
@@ -2405,14 +2405,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="13"/>
-        <v>110255</v>
+        <v>110265</v>
       </c>
       <c r="AO16" s="5">
-        <v>416366</v>
+        <v>416376</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="14"/>
-        <v>0.95787667135981747</v>
+        <v>0.95789967700080059</v>
       </c>
       <c r="AQ16" s="3">
         <v>772632</v>
@@ -2422,14 +2422,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="15"/>
-        <v>180816</v>
+        <v>180837</v>
       </c>
       <c r="AT16" s="3">
-        <v>743460</v>
+        <v>743481</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="16"/>
-        <v>0.96224334482651508</v>
+        <v>0.9622705246482155</v>
       </c>
       <c r="AV16" s="5">
         <v>448203</v>
@@ -2439,14 +2439,14 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="17"/>
-        <v>98383</v>
+        <v>98396</v>
       </c>
       <c r="AY16" s="5">
-        <v>418462</v>
+        <v>418475</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="18"/>
-        <v>0.93364390689040455</v>
+        <v>0.93367291160478627</v>
       </c>
       <c r="BA16" s="10">
         <v>429555</v>
@@ -2456,14 +2456,14 @@
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="19"/>
-        <v>103404</v>
+        <v>103418</v>
       </c>
       <c r="BD16" s="5">
-        <v>424678</v>
+        <v>424692</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="20"/>
-        <v>0.98864638986858489</v>
+        <v>0.98867898173691382</v>
       </c>
       <c r="BF16" s="10">
         <v>753579</v>
@@ -2473,14 +2473,14 @@
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="21"/>
-        <v>197200</v>
+        <v>197234</v>
       </c>
       <c r="BI16" s="5">
-        <v>753284</v>
+        <v>753318</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="22"/>
-        <v>0.99960853473889266</v>
+        <v>0.99965365276898643</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2498,14 +2498,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>97159</v>
+        <v>97170</v>
       </c>
       <c r="F17" s="5">
-        <v>273137</v>
+        <v>273148</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.96558855450010783</v>
+        <v>0.96562744148392732</v>
       </c>
       <c r="H17" s="5">
         <v>290053</v>
@@ -2515,14 +2515,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>89038</v>
+        <v>89048</v>
       </c>
       <c r="K17" s="5">
-        <v>281329</v>
+        <v>281339</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.96992273825818043</v>
+        <v>0.96995721471593122</v>
       </c>
       <c r="M17" s="9">
         <v>666005</v>
@@ -2534,11 +2534,11 @@
         <v>640256</v>
       </c>
       <c r="P17" s="5">
-        <v>641478</v>
+        <v>641491</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="4"/>
-        <v>0.96317294915203344</v>
+        <v>0.96319246852501106</v>
       </c>
       <c r="R17" s="5">
         <v>287981</v>
@@ -2548,14 +2548,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="5"/>
-        <v>96328</v>
+        <v>96338</v>
       </c>
       <c r="U17" s="5">
-        <v>276600</v>
+        <v>276610</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="6"/>
-        <v>0.96048003166875595</v>
+        <v>0.96051475618183146</v>
       </c>
       <c r="W17" s="5">
         <v>293004</v>
@@ -2565,14 +2565,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="7"/>
-        <v>99037</v>
+        <v>99046</v>
       </c>
       <c r="Z17" s="5">
-        <v>283303</v>
+        <v>283312</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="8"/>
-        <v>0.96689123697969992</v>
+        <v>0.96692195328391417</v>
       </c>
       <c r="AB17" s="5">
         <v>677720</v>
@@ -2582,14 +2582,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="9"/>
-        <v>263368</v>
+        <v>263381</v>
       </c>
       <c r="AE17" s="5">
-        <v>660003</v>
+        <v>660016</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="10"/>
-        <v>0.97385793543056132</v>
+        <v>0.97387711739361393</v>
       </c>
       <c r="AG17" s="5">
         <v>295677</v>
@@ -2599,14 +2599,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="11"/>
-        <v>86952</v>
+        <v>86959</v>
       </c>
       <c r="AJ17" s="5">
-        <v>286403</v>
+        <v>286410</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="12"/>
-        <v>0.96863469258684309</v>
+        <v>0.96865836706947106</v>
       </c>
       <c r="AL17" s="5">
         <v>303084</v>
@@ -2616,14 +2616,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="13"/>
-        <v>89230</v>
+        <v>89238</v>
       </c>
       <c r="AO17" s="5">
-        <v>294587</v>
+        <v>294595</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="14"/>
-        <v>0.97196486782542135</v>
+        <v>0.97199126314817019</v>
       </c>
       <c r="AQ17" s="3">
         <v>690105</v>
@@ -2633,14 +2633,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="15"/>
-        <v>218575</v>
+        <v>218594</v>
       </c>
       <c r="AT17" s="3">
-        <v>674456</v>
+        <v>674475</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="16"/>
-        <v>0.9773237405902</v>
+        <v>0.97735127263242549</v>
       </c>
       <c r="AV17" s="5">
         <v>311697</v>
@@ -2650,14 +2650,14 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="17"/>
-        <v>74890</v>
+        <v>74897</v>
       </c>
       <c r="AY17" s="5">
-        <v>292908</v>
+        <v>292915</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="18"/>
-        <v>0.93972030529648987</v>
+        <v>0.93974276300381465</v>
       </c>
       <c r="BA17" s="10">
         <v>307540</v>
@@ -2667,14 +2667,14 @@
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="19"/>
-        <v>81865</v>
+        <v>81873</v>
       </c>
       <c r="BD17" s="5">
-        <v>300833</v>
+        <v>300841</v>
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="20"/>
-        <v>0.97819145477011116</v>
+        <v>0.97821746764648498</v>
       </c>
       <c r="BF17" s="10">
         <v>689646</v>
@@ -2684,14 +2684,14 @@
       </c>
       <c r="BH17" s="3">
         <f t="shared" si="21"/>
-        <v>257480</v>
+        <v>257504</v>
       </c>
       <c r="BI17" s="5">
-        <v>688720</v>
+        <v>688744</v>
       </c>
       <c r="BJ17" s="4">
         <f t="shared" si="22"/>
-        <v>0.99865728214185245</v>
+        <v>0.99869208260469866</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2709,14 +2709,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>397873</v>
+        <v>397885</v>
       </c>
       <c r="F18" s="5">
-        <v>804236</v>
+        <v>804248</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>0.95685539185650426</v>
+        <v>0.95686966908943383</v>
       </c>
       <c r="H18" s="5">
         <v>861805</v>
@@ -2726,14 +2726,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>381232</v>
+        <v>381245</v>
       </c>
       <c r="K18" s="5">
-        <v>819349</v>
+        <v>819362</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.95073595534952804</v>
+        <v>0.95075103996843835</v>
       </c>
       <c r="M18" s="9">
         <v>1358945</v>
@@ -2745,11 +2745,11 @@
         <v>1272521</v>
       </c>
       <c r="P18" s="5">
-        <v>1276351</v>
+        <v>1276372</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="4"/>
-        <v>0.93922196998406848</v>
+        <v>0.93923742314810388</v>
       </c>
       <c r="R18" s="5">
         <v>869959</v>
@@ -2759,14 +2759,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="5"/>
-        <v>402904</v>
+        <v>402920</v>
       </c>
       <c r="U18" s="5">
-        <v>822364</v>
+        <v>822380</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="6"/>
-        <v>0.94529052518566969</v>
+        <v>0.94530891685700136</v>
       </c>
       <c r="W18" s="5">
         <v>883450</v>
@@ -2776,14 +2776,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="7"/>
-        <v>412745</v>
+        <v>412759</v>
       </c>
       <c r="Z18" s="5">
-        <v>838141</v>
+        <v>838155</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="8"/>
-        <v>0.94871356613277491</v>
+        <v>0.94872941309638348</v>
       </c>
       <c r="AB18" s="5">
         <v>1397129</v>
@@ -2793,14 +2793,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="9"/>
-        <v>718445</v>
+        <v>718457</v>
       </c>
       <c r="AE18" s="5">
-        <v>1341440</v>
+        <v>1341452</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="10"/>
-        <v>0.96014040221053321</v>
+        <v>0.9601489912527762</v>
       </c>
       <c r="AG18" s="5">
         <v>899515</v>
@@ -2810,14 +2810,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="11"/>
-        <v>400318</v>
+        <v>400328</v>
       </c>
       <c r="AJ18" s="5">
-        <v>863717</v>
+        <v>863727</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="12"/>
-        <v>0.96020299828240774</v>
+        <v>0.9602141153844016</v>
       </c>
       <c r="AL18" s="5">
         <v>914748</v>
@@ -2827,14 +2827,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="13"/>
-        <v>398121</v>
+        <v>398131</v>
       </c>
       <c r="AO18" s="5">
-        <v>880098</v>
+        <v>880108</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="14"/>
-        <v>0.96212071521337028</v>
+        <v>0.96213164718589161</v>
       </c>
       <c r="AQ18" s="3">
         <v>1436617</v>
@@ -2844,14 +2844,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="15"/>
-        <v>655846</v>
+        <v>655862</v>
       </c>
       <c r="AT18" s="3">
-        <v>1378585</v>
+        <v>1378601</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="16"/>
-        <v>0.95960510003710109</v>
+        <v>0.95961623731307644</v>
       </c>
       <c r="AV18" s="5">
         <v>954168</v>
@@ -2861,14 +2861,14 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="17"/>
-        <v>385890</v>
+        <v>385901</v>
       </c>
       <c r="AY18" s="5">
-        <v>892984</v>
+        <v>892995</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="18"/>
-        <v>0.93587712017170976</v>
+        <v>0.93588864853987974</v>
       </c>
       <c r="BA18" s="10">
         <v>922519</v>
@@ -2878,14 +2878,14 @@
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="19"/>
-        <v>429117</v>
+        <v>429129</v>
       </c>
       <c r="BD18" s="5">
-        <v>910817</v>
+        <v>910829</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" si="20"/>
-        <v>0.9873151664084967</v>
+        <v>0.98732817427066544</v>
       </c>
       <c r="BF18" s="10">
         <v>1428140</v>
@@ -2895,14 +2895,14 @@
       </c>
       <c r="BH18" s="3">
         <f t="shared" si="21"/>
-        <v>725088</v>
+        <v>725116</v>
       </c>
       <c r="BI18" s="5">
-        <v>1417071</v>
+        <v>1417099</v>
       </c>
       <c r="BJ18" s="4">
         <f t="shared" si="22"/>
-        <v>0.99224935930651059</v>
+        <v>0.99226896522749874</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -2920,14 +2920,14 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>162676</v>
+        <v>162681</v>
       </c>
       <c r="F19" s="5">
-        <v>236277</v>
+        <v>236282</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>0.85467639951962726</v>
+        <v>0.85469448584202679</v>
       </c>
       <c r="H19" s="5">
         <v>280982</v>
@@ -2937,14 +2937,14 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>160621</v>
+        <v>160627</v>
       </c>
       <c r="K19" s="5">
-        <v>240904</v>
+        <v>240910</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="3"/>
-        <v>0.85736452868867041</v>
+        <v>0.85738588236968916</v>
       </c>
       <c r="M19" s="9">
         <v>470659</v>
@@ -2956,11 +2956,11 @@
         <v>406179</v>
       </c>
       <c r="P19" s="5">
-        <v>408661</v>
+        <v>408672</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="4"/>
-        <v>0.86827405828848492</v>
+        <v>0.86829742977399771</v>
       </c>
       <c r="R19" s="5">
         <v>282327</v>
@@ -2970,14 +2970,14 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" si="5"/>
-        <v>164068</v>
+        <v>164073</v>
       </c>
       <c r="U19" s="5">
-        <v>240706</v>
+        <v>240711</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="6"/>
-        <v>0.85257874733907846</v>
+        <v>0.85259645729951439</v>
       </c>
       <c r="W19" s="5">
         <v>286093</v>
@@ -2987,14 +2987,14 @@
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="7"/>
-        <v>167488</v>
+        <v>167494</v>
       </c>
       <c r="Z19" s="5">
-        <v>245961</v>
+        <v>245967</v>
       </c>
       <c r="AA19" s="4">
         <f t="shared" si="8"/>
-        <v>0.85972393592293417</v>
+        <v>0.85974490812428128</v>
       </c>
       <c r="AB19" s="5">
         <v>481143</v>
@@ -3004,14 +3004,14 @@
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="9"/>
-        <v>316651</v>
+        <v>316659</v>
       </c>
       <c r="AE19" s="5">
-        <v>436086</v>
+        <v>436094</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="10"/>
-        <v>0.90635424395657838</v>
+        <v>0.90637087103002645</v>
       </c>
       <c r="AG19" s="5">
         <v>287213</v>
@@ -3021,14 +3021,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="11"/>
-        <v>164973</v>
+        <v>164978</v>
       </c>
       <c r="AJ19" s="5">
-        <v>254423</v>
+        <v>254428</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="12"/>
-        <v>0.88583385849526308</v>
+        <v>0.88585126717801765</v>
       </c>
       <c r="AL19" s="5">
         <v>292666</v>
@@ -3038,14 +3038,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="13"/>
-        <v>159530</v>
+        <v>159535</v>
       </c>
       <c r="AO19" s="5">
-        <v>260126</v>
+        <v>260131</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="14"/>
-        <v>0.88881523648117644</v>
+        <v>0.88883232080255303</v>
       </c>
       <c r="AQ19" s="3">
         <v>495564</v>
@@ -3055,14 +3055,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="15"/>
-        <v>290896</v>
+        <v>290904</v>
       </c>
       <c r="AT19" s="3">
-        <v>448256</v>
+        <v>448264</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="16"/>
-        <v>0.90453705273183682</v>
+        <v>0.90455319595450845</v>
       </c>
       <c r="AV19" s="5">
         <v>310298</v>
@@ -3072,14 +3072,14 @@
       </c>
       <c r="AX19" s="3">
         <f t="shared" si="17"/>
-        <v>162860</v>
+        <v>162867</v>
       </c>
       <c r="AY19" s="5">
-        <v>263959</v>
+        <v>263966</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="18"/>
-        <v>0.85066291113703596</v>
+        <v>0.85068547009648787</v>
       </c>
       <c r="BA19" s="10">
         <v>280202</v>
@@ -3089,14 +3089,14 @@
       </c>
       <c r="BC19" s="3">
         <f t="shared" si="19"/>
-        <v>182656</v>
+        <v>182663</v>
       </c>
       <c r="BD19" s="5">
-        <v>272725</v>
+        <v>272732</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="20"/>
-        <v>0.97331567940271657</v>
+        <v>0.97334066138000441</v>
       </c>
       <c r="BF19" s="10">
         <v>473091</v>
@@ -3106,14 +3106,14 @@
       </c>
       <c r="BH19" s="3">
         <f t="shared" si="21"/>
-        <v>327661</v>
+        <v>327681</v>
       </c>
       <c r="BI19" s="5">
-        <v>464725</v>
+        <v>464745</v>
       </c>
       <c r="BJ19" s="4">
         <f t="shared" si="22"/>
-        <v>0.98231629855566904</v>
+        <v>0.98235857372048929</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3131,14 +3131,14 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>3105</v>
+        <v>3107</v>
       </c>
       <c r="F20" s="5">
-        <v>5059</v>
+        <v>5061</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="1"/>
-        <v>0.83813783962889332</v>
+        <v>0.83846918489065603</v>
       </c>
       <c r="H20" s="5">
         <v>6124</v>
@@ -3148,14 +3148,14 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" si="2"/>
-        <v>3024</v>
+        <v>3026</v>
       </c>
       <c r="K20" s="5">
-        <v>5125</v>
+        <v>5127</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="3"/>
-        <v>0.83687132593076419</v>
+        <v>0.83719790986283471</v>
       </c>
       <c r="M20" s="9">
         <v>9262</v>
@@ -3167,11 +3167,11 @@
         <v>7959</v>
       </c>
       <c r="P20" s="5">
-        <v>8079</v>
+        <v>8083</v>
       </c>
       <c r="Q20" s="4">
         <f t="shared" si="4"/>
-        <v>0.87227380695314183</v>
+        <v>0.87270567911898078</v>
       </c>
       <c r="R20" s="5">
         <v>6202</v>
@@ -3181,14 +3181,14 @@
       </c>
       <c r="T20" s="3">
         <f t="shared" si="5"/>
-        <v>3059</v>
+        <v>3061</v>
       </c>
       <c r="U20" s="5">
-        <v>5196</v>
+        <v>5198</v>
       </c>
       <c r="V20" s="4">
         <f t="shared" si="6"/>
-        <v>0.83779425991615608</v>
+        <v>0.83811673653660113</v>
       </c>
       <c r="W20" s="5">
         <v>6226</v>
@@ -3198,14 +3198,14 @@
       </c>
       <c r="Y20" s="3">
         <f t="shared" si="7"/>
-        <v>3155</v>
+        <v>3157</v>
       </c>
       <c r="Z20" s="5">
-        <v>5266</v>
+        <v>5268</v>
       </c>
       <c r="AA20" s="4">
         <f t="shared" si="8"/>
-        <v>0.8458079023450048</v>
+        <v>0.84612913588178607</v>
       </c>
       <c r="AB20" s="5">
         <v>9386</v>
@@ -3215,14 +3215,14 @@
       </c>
       <c r="AD20" s="3">
         <f t="shared" si="9"/>
-        <v>5859</v>
+        <v>5862</v>
       </c>
       <c r="AE20" s="5">
-        <v>8438</v>
+        <v>8441</v>
       </c>
       <c r="AF20" s="4">
         <f t="shared" si="10"/>
-        <v>0.89899850841679096</v>
+        <v>0.89931813339015554</v>
       </c>
       <c r="AG20" s="5">
         <v>6315</v>
@@ -3232,14 +3232,14 @@
       </c>
       <c r="AI20" s="3">
         <f t="shared" si="11"/>
-        <v>3230</v>
+        <v>3232</v>
       </c>
       <c r="AJ20" s="5">
-        <v>5448</v>
+        <v>5450</v>
       </c>
       <c r="AK20" s="4">
         <f t="shared" si="12"/>
-        <v>0.86270783847981003</v>
+        <v>0.86302454473475854</v>
       </c>
       <c r="AL20" s="5">
         <v>6446</v>
@@ -3249,14 +3249,14 @@
       </c>
       <c r="AN20" s="3">
         <f t="shared" si="13"/>
-        <v>3250</v>
+        <v>3252</v>
       </c>
       <c r="AO20" s="5">
-        <v>5545</v>
+        <v>5547</v>
       </c>
       <c r="AP20" s="4">
         <f t="shared" si="14"/>
-        <v>0.86022339435308715</v>
+        <v>0.86053366428793054</v>
       </c>
       <c r="AQ20" s="3">
         <v>9604</v>
@@ -3266,14 +3266,14 @@
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="15"/>
-        <v>5294</v>
+        <v>5298</v>
       </c>
       <c r="AT20" s="3">
-        <v>8623</v>
+        <v>8627</v>
       </c>
       <c r="AU20" s="4">
         <f t="shared" si="16"/>
-        <v>0.89785506039150353</v>
+        <v>0.89827155351936694</v>
       </c>
       <c r="AV20" s="5">
         <v>6642</v>
@@ -3283,14 +3283,14 @@
       </c>
       <c r="AX20" s="3">
         <f t="shared" si="17"/>
-        <v>3116</v>
+        <v>3118</v>
       </c>
       <c r="AY20" s="5">
-        <v>5604</v>
+        <v>5606</v>
       </c>
       <c r="AZ20" s="4">
         <f t="shared" si="18"/>
-        <v>0.84372177055103881</v>
+        <v>0.84402288467329123</v>
       </c>
       <c r="BA20" s="10">
         <v>5628</v>
@@ -3300,14 +3300,14 @@
       </c>
       <c r="BC20" s="3">
         <f t="shared" si="19"/>
-        <v>3327</v>
+        <v>3329</v>
       </c>
       <c r="BD20" s="5">
-        <v>5720</v>
+        <v>5722</v>
       </c>
       <c r="BE20" s="4">
         <f t="shared" si="20"/>
-        <v>1.0163468372423596</v>
+        <v>1.0167022032693676</v>
       </c>
       <c r="BF20" s="10">
         <v>8802</v>
@@ -3317,14 +3317,14 @@
       </c>
       <c r="BH20" s="3">
         <f t="shared" si="21"/>
-        <v>5778</v>
+        <v>5783</v>
       </c>
       <c r="BI20" s="5">
-        <v>8966</v>
+        <v>8971</v>
       </c>
       <c r="BJ20" s="4">
         <f t="shared" si="22"/>
-        <v>1.018632129061577</v>
+        <v>1.019200181776869</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3342,14 +3342,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>6067</v>
+        <v>6071</v>
       </c>
       <c r="F21" s="5">
-        <v>8302</v>
+        <v>8306</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>0.78195347084863898</v>
+        <v>0.78233022511067152</v>
       </c>
       <c r="H21" s="5">
         <v>10811</v>
@@ -3359,14 +3359,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>5865</v>
+        <v>5869</v>
       </c>
       <c r="K21" s="5">
-        <v>8428</v>
+        <v>8432</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>0.77957635741374531</v>
+        <v>0.77994635093885856</v>
       </c>
       <c r="M21" s="9">
         <v>14133</v>
@@ -3378,11 +3378,11 @@
         <v>11192</v>
       </c>
       <c r="P21" s="5">
-        <v>11396</v>
+        <v>11400</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="4"/>
-        <v>0.80633977216443786</v>
+        <v>0.80662279770749312</v>
       </c>
       <c r="R21" s="5">
         <v>11019</v>
@@ -3392,14 +3392,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="5"/>
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="U21" s="5">
-        <v>8623</v>
+        <v>8627</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="6"/>
-        <v>0.78255740085307202</v>
+        <v>0.78292041020056269</v>
       </c>
       <c r="W21" s="5">
         <v>11175</v>
@@ -3409,14 +3409,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="7"/>
-        <v>6278</v>
+        <v>6282</v>
       </c>
       <c r="Z21" s="5">
-        <v>8794</v>
+        <v>8798</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="8"/>
-        <v>0.78693512304250557</v>
+        <v>0.78729306487695749</v>
       </c>
       <c r="AB21" s="5">
         <v>14571</v>
@@ -3426,14 +3426,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="9"/>
-        <v>9099</v>
+        <v>9104</v>
       </c>
       <c r="AE21" s="5">
-        <v>12216</v>
+        <v>12221</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="10"/>
-        <v>0.83837759934115708</v>
+        <v>0.83872074668862806</v>
       </c>
       <c r="AG21" s="5">
         <v>11345</v>
@@ -3443,14 +3443,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="11"/>
-        <v>6289</v>
+        <v>6293</v>
       </c>
       <c r="AJ21" s="5">
-        <v>9217</v>
+        <v>9221</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="12"/>
-        <v>0.8124283825473777</v>
+        <v>0.81278096077567208</v>
       </c>
       <c r="AL21" s="5">
         <v>11441</v>
@@ -3460,14 +3460,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="13"/>
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="AO21" s="5">
-        <v>9328</v>
+        <v>9332</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="14"/>
-        <v>0.81531334673542522</v>
+        <v>0.81566296652390524</v>
       </c>
       <c r="AQ21" s="3">
         <v>14790</v>
@@ -3477,14 +3477,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="15"/>
-        <v>8833</v>
+        <v>8838</v>
       </c>
       <c r="AT21" s="3">
-        <v>12523</v>
+        <v>12528</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="16"/>
-        <v>0.84672075726842466</v>
+        <v>0.84705882352941175</v>
       </c>
       <c r="AV21" s="5">
         <v>11740</v>
@@ -3494,14 +3494,14 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="17"/>
-        <v>6323</v>
+        <v>6327</v>
       </c>
       <c r="AY21" s="5">
-        <v>9468</v>
+        <v>9472</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="18"/>
-        <v>0.80647359454855194</v>
+        <v>0.80681431005110738</v>
       </c>
       <c r="BA21" s="10">
         <v>9242</v>
@@ -3528,14 +3528,14 @@
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="21"/>
-        <v>9730</v>
+        <v>9734</v>
       </c>
       <c r="BI21" s="5">
-        <v>12921</v>
+        <v>12925</v>
       </c>
       <c r="BJ21" s="4">
         <f t="shared" si="22"/>
-        <v>1.0300542091836735</v>
+        <v>1.0303730867346939</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3553,14 +3553,14 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>3773</v>
+        <v>3776</v>
       </c>
       <c r="F22" s="5">
-        <v>5527</v>
+        <v>5530</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>0.90517523747133966</v>
+        <v>0.90566655748444158</v>
       </c>
       <c r="H22" s="5">
         <v>6184</v>
@@ -3570,14 +3570,14 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>3781</v>
+        <v>3784</v>
       </c>
       <c r="K22" s="5">
-        <v>5603</v>
+        <v>5606</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="3"/>
-        <v>0.90604786545924965</v>
+        <v>0.90653298835705043</v>
       </c>
       <c r="M22" s="9">
         <v>7446</v>
@@ -3589,11 +3589,11 @@
         <v>6697</v>
       </c>
       <c r="P22" s="5">
-        <v>6759</v>
+        <v>6763</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="4"/>
-        <v>0.90773569701853341</v>
+        <v>0.90827289820037604</v>
       </c>
       <c r="R22" s="5">
         <v>6325</v>
@@ -3603,14 +3603,14 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" si="5"/>
-        <v>3914</v>
+        <v>3918</v>
       </c>
       <c r="U22" s="5">
-        <v>5734</v>
+        <v>5738</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="6"/>
-        <v>0.90656126482213439</v>
+        <v>0.90719367588932809</v>
       </c>
       <c r="W22" s="5">
         <v>6418</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="7"/>
-        <v>4040</v>
+        <v>4044</v>
       </c>
       <c r="Z22" s="5">
-        <v>5820</v>
+        <v>5824</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" si="8"/>
-        <v>0.90682455593642874</v>
+        <v>0.90744780305391093</v>
       </c>
       <c r="AB22" s="5">
         <v>7662</v>
@@ -3637,14 +3637,14 @@
       </c>
       <c r="AD22" s="3">
         <f t="shared" si="9"/>
-        <v>5023</v>
+        <v>5027</v>
       </c>
       <c r="AE22" s="5">
-        <v>7104</v>
+        <v>7108</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="10"/>
-        <v>0.92717306186374315</v>
+        <v>0.92769511876794575</v>
       </c>
       <c r="AG22" s="5">
         <v>6546</v>
@@ -3654,14 +3654,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="11"/>
-        <v>4108</v>
+        <v>4112</v>
       </c>
       <c r="AJ22" s="5">
-        <v>6012</v>
+        <v>6016</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="12"/>
-        <v>0.91842346471127401</v>
+        <v>0.9190345249007027</v>
       </c>
       <c r="AL22" s="5">
         <v>6648</v>
@@ -3671,14 +3671,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="13"/>
-        <v>3814</v>
+        <v>3818</v>
       </c>
       <c r="AO22" s="5">
-        <v>6072</v>
+        <v>6076</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="14"/>
-        <v>0.91335740072202165</v>
+        <v>0.91395908543922988</v>
       </c>
       <c r="AQ22" s="3">
         <v>7880</v>
@@ -3688,14 +3688,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="15"/>
-        <v>4825</v>
+        <v>4831</v>
       </c>
       <c r="AT22" s="3">
-        <v>7281</v>
+        <v>7287</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="16"/>
-        <v>0.92398477157360404</v>
+        <v>0.92474619289340099</v>
       </c>
       <c r="AV22" s="5">
         <v>6715</v>
@@ -3705,14 +3705,14 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="17"/>
-        <v>3909</v>
+        <v>3915</v>
       </c>
       <c r="AY22" s="5">
-        <v>6092</v>
+        <v>6098</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="18"/>
-        <v>0.90722263588979901</v>
+        <v>0.90811615785554733</v>
       </c>
       <c r="BA22" s="10">
         <v>6117</v>
@@ -3722,14 +3722,14 @@
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="19"/>
-        <v>4024</v>
+        <v>4029</v>
       </c>
       <c r="BD22" s="5">
-        <v>6141</v>
+        <v>6146</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" si="20"/>
-        <v>1.0039234919077979</v>
+        <v>1.0047408860552558</v>
       </c>
       <c r="BF22" s="10">
         <v>7349</v>
@@ -3739,14 +3739,14 @@
       </c>
       <c r="BH22" s="3">
         <f t="shared" si="21"/>
-        <v>5139</v>
+        <v>5144</v>
       </c>
       <c r="BI22" s="5">
-        <v>7412</v>
+        <v>7417</v>
       </c>
       <c r="BJ22" s="4">
         <f t="shared" si="22"/>
-        <v>1.0085725949108721</v>
+        <v>1.0092529595863382</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -3764,14 +3764,14 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>5398</v>
+        <v>5399</v>
       </c>
       <c r="F23" s="5">
-        <v>7274</v>
+        <v>7275</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>0.80714602751886377</v>
+        <v>0.80725699067909451</v>
       </c>
       <c r="H23" s="5">
         <v>9118</v>
@@ -3781,14 +3781,14 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>5297</v>
+        <v>5298</v>
       </c>
       <c r="K23" s="5">
-        <v>7402</v>
+        <v>7403</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="3"/>
-        <v>0.81180083351612198</v>
+        <v>0.81191050669006359</v>
       </c>
       <c r="M23" s="9">
         <v>11079</v>
@@ -3800,11 +3800,11 @@
         <v>9029</v>
       </c>
       <c r="P23" s="5">
-        <v>9123</v>
+        <v>9124</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" si="4"/>
-        <v>0.82344976983482265</v>
+        <v>0.82354003068869031</v>
       </c>
       <c r="R23" s="5">
         <v>9156</v>
@@ -3814,14 +3814,14 @@
       </c>
       <c r="T23" s="3">
         <f t="shared" si="5"/>
-        <v>5371</v>
+        <v>5372</v>
       </c>
       <c r="U23" s="5">
-        <v>7566</v>
+        <v>7567</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="6"/>
-        <v>0.8263433813892529</v>
+        <v>0.82645259938837923</v>
       </c>
       <c r="W23" s="5">
         <v>9166</v>
@@ -3831,14 +3831,14 @@
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="7"/>
-        <v>5708</v>
+        <v>5709</v>
       </c>
       <c r="Z23" s="5">
-        <v>7747</v>
+        <v>7748</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="8"/>
-        <v>0.84518874099934538</v>
+        <v>0.84529783984289764</v>
       </c>
       <c r="AB23" s="5">
         <v>11322</v>
@@ -3848,14 +3848,14 @@
       </c>
       <c r="AD23" s="3">
         <f t="shared" si="9"/>
-        <v>7303</v>
+        <v>7305</v>
       </c>
       <c r="AE23" s="5">
-        <v>10060</v>
+        <v>10062</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="10"/>
-        <v>0.88853559441794738</v>
+        <v>0.88871224165341811</v>
       </c>
       <c r="AG23" s="5">
         <v>9569</v>
@@ -3865,14 +3865,14 @@
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="11"/>
-        <v>5886</v>
+        <v>5888</v>
       </c>
       <c r="AJ23" s="5">
-        <v>8232</v>
+        <v>8234</v>
       </c>
       <c r="AK23" s="4">
         <f t="shared" si="12"/>
-        <v>0.86027798098024877</v>
+        <v>0.86048698923607481</v>
       </c>
       <c r="AL23" s="5">
         <v>9502</v>
@@ -3882,14 +3882,14 @@
       </c>
       <c r="AN23" s="3">
         <f t="shared" si="13"/>
-        <v>6032</v>
+        <v>6034</v>
       </c>
       <c r="AO23" s="5">
-        <v>8358</v>
+        <v>8360</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="14"/>
-        <v>0.8796042938328773</v>
+        <v>0.87981477583666601</v>
       </c>
       <c r="AQ23" s="3">
         <v>11767</v>
@@ -3899,14 +3899,14 @@
       </c>
       <c r="AS23" s="3">
         <f t="shared" si="15"/>
-        <v>7338</v>
+        <v>7340</v>
       </c>
       <c r="AT23" s="3">
-        <v>10374</v>
+        <v>10376</v>
       </c>
       <c r="AU23" s="4">
         <f t="shared" si="16"/>
-        <v>0.88161808447352763</v>
+        <v>0.88178805132999061</v>
       </c>
       <c r="AV23" s="5">
         <v>9805</v>
@@ -3916,14 +3916,14 @@
       </c>
       <c r="AX23" s="3">
         <f t="shared" si="17"/>
-        <v>5853</v>
+        <v>5855</v>
       </c>
       <c r="AY23" s="5">
-        <v>8448</v>
+        <v>8450</v>
       </c>
       <c r="AZ23" s="4">
         <f t="shared" si="18"/>
-        <v>0.86160122386537485</v>
+        <v>0.86180520142784289</v>
       </c>
       <c r="BA23" s="10">
         <v>8694</v>
@@ -3933,14 +3933,14 @@
       </c>
       <c r="BC23" s="3">
         <f t="shared" si="19"/>
-        <v>6349</v>
+        <v>6351</v>
       </c>
       <c r="BD23" s="5">
-        <v>8556</v>
+        <v>8558</v>
       </c>
       <c r="BE23" s="4">
         <f t="shared" si="20"/>
-        <v>0.98412698412698407</v>
+        <v>0.98435702783528867</v>
       </c>
       <c r="BF23" s="10">
         <v>11229</v>
@@ -3950,14 +3950,14 @@
       </c>
       <c r="BH23" s="3">
         <f t="shared" si="21"/>
-        <v>7864</v>
+        <v>7867</v>
       </c>
       <c r="BI23" s="5">
-        <v>10633</v>
+        <v>10636</v>
       </c>
       <c r="BJ23" s="4">
         <f t="shared" si="22"/>
-        <v>0.94692314542701927</v>
+        <v>0.94719031080238669</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4186,14 +4186,14 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>9248</v>
+        <v>9249</v>
       </c>
       <c r="F25" s="5">
-        <v>17190</v>
+        <v>17191</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="1"/>
-        <v>0.9058333772461401</v>
+        <v>0.90588607261421716</v>
       </c>
       <c r="H25" s="5">
         <v>19277</v>
@@ -4203,14 +4203,14 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" si="2"/>
-        <v>8612</v>
+        <v>8613</v>
       </c>
       <c r="K25" s="5">
-        <v>17431</v>
+        <v>17432</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="3"/>
-        <v>0.90423821133993876</v>
+        <v>0.90429008663173727</v>
       </c>
       <c r="M25" s="9">
         <v>26614</v>
@@ -4222,11 +4222,11 @@
         <v>24298</v>
       </c>
       <c r="P25" s="5">
-        <v>24424</v>
+        <v>24428</v>
       </c>
       <c r="Q25" s="4">
         <f t="shared" si="4"/>
-        <v>0.91771248215225065</v>
+        <v>0.91786277898850233</v>
       </c>
       <c r="R25" s="5">
         <v>19402</v>
@@ -4236,14 +4236,14 @@
       </c>
       <c r="T25" s="3">
         <f t="shared" si="5"/>
-        <v>9096</v>
+        <v>9098</v>
       </c>
       <c r="U25" s="5">
-        <v>17570</v>
+        <v>17572</v>
       </c>
       <c r="V25" s="4">
         <f t="shared" si="6"/>
-        <v>0.90557674466549842</v>
+        <v>0.90567982682197712</v>
       </c>
       <c r="W25" s="5">
         <v>19474</v>
@@ -4253,14 +4253,14 @@
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="7"/>
-        <v>9544</v>
+        <v>9546</v>
       </c>
       <c r="Z25" s="5">
-        <v>17812</v>
+        <v>17814</v>
       </c>
       <c r="AA25" s="4">
         <f t="shared" si="8"/>
-        <v>0.91465543801992399</v>
+        <v>0.91475813905720449</v>
       </c>
       <c r="AB25" s="5">
         <v>27081</v>
@@ -4270,14 +4270,14 @@
       </c>
       <c r="AD25" s="3">
         <f t="shared" si="9"/>
-        <v>15020</v>
+        <v>15024</v>
       </c>
       <c r="AE25" s="5">
-        <v>25199</v>
+        <v>25203</v>
       </c>
       <c r="AF25" s="4">
         <f t="shared" si="10"/>
-        <v>0.93050478195044495</v>
+        <v>0.93065248698349401</v>
       </c>
       <c r="AG25" s="5">
         <v>19543</v>
@@ -4287,14 +4287,14 @@
       </c>
       <c r="AI25" s="3">
         <f t="shared" si="11"/>
-        <v>8971</v>
+        <v>8973</v>
       </c>
       <c r="AJ25" s="5">
-        <v>18098</v>
+        <v>18100</v>
       </c>
       <c r="AK25" s="4">
         <f t="shared" si="12"/>
-        <v>0.92606048201402036</v>
+        <v>0.92616282044721898</v>
       </c>
       <c r="AL25" s="5">
         <v>19594</v>
@@ -4304,14 +4304,14 @@
       </c>
       <c r="AN25" s="3">
         <f t="shared" si="13"/>
-        <v>9103</v>
+        <v>9105</v>
       </c>
       <c r="AO25" s="5">
-        <v>18271</v>
+        <v>18273</v>
       </c>
       <c r="AP25" s="4">
         <f t="shared" si="14"/>
-        <v>0.93247933040726749</v>
+        <v>0.93258140247014387</v>
       </c>
       <c r="AQ25" s="3">
         <v>26830</v>
@@ -4321,14 +4321,14 @@
       </c>
       <c r="AS25" s="3">
         <f t="shared" si="15"/>
-        <v>13138</v>
+        <v>13142</v>
       </c>
       <c r="AT25" s="3">
-        <v>25468</v>
+        <v>25472</v>
       </c>
       <c r="AU25" s="4">
         <f t="shared" si="16"/>
-        <v>0.94923592992918371</v>
+        <v>0.94938501677226983</v>
       </c>
       <c r="AV25" s="5">
         <v>19719</v>
@@ -4338,14 +4338,14 @@
       </c>
       <c r="AX25" s="3">
         <f t="shared" si="17"/>
-        <v>8708</v>
+        <v>8711</v>
       </c>
       <c r="AY25" s="5">
-        <v>18363</v>
+        <v>18366</v>
       </c>
       <c r="AZ25" s="4">
         <f t="shared" si="18"/>
-        <v>0.93123383538719007</v>
+        <v>0.9313859729195193</v>
       </c>
       <c r="BA25" s="10">
         <v>18241</v>
@@ -4355,14 +4355,14 @@
       </c>
       <c r="BC25" s="3">
         <f t="shared" si="19"/>
-        <v>9434</v>
+        <v>9437</v>
       </c>
       <c r="BD25" s="5">
-        <v>18415</v>
+        <v>18418</v>
       </c>
       <c r="BE25" s="4">
         <f t="shared" si="20"/>
-        <v>1.0095389507154213</v>
+        <v>1.0097034153829285</v>
       </c>
       <c r="BF25" s="10">
         <v>25358</v>
@@ -4372,14 +4372,14 @@
       </c>
       <c r="BH25" s="3">
         <f t="shared" si="21"/>
-        <v>15161</v>
+        <v>15167</v>
       </c>
       <c r="BI25" s="5">
-        <v>25695</v>
+        <v>25701</v>
       </c>
       <c r="BJ25" s="4">
         <f t="shared" si="22"/>
-        <v>1.0132896916160581</v>
+        <v>1.0135263033362252</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4433,11 +4433,11 @@
         <v>21793</v>
       </c>
       <c r="P26" s="5">
-        <v>22081</v>
+        <v>22088</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="4"/>
-        <v>0.80265358051617597</v>
+        <v>0.80290803344238459</v>
       </c>
       <c r="R26" s="5">
         <v>16566</v>
@@ -4481,14 +4481,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="9"/>
-        <v>18092</v>
+        <v>18093</v>
       </c>
       <c r="AE26" s="5">
-        <v>24958</v>
+        <v>24959</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="10"/>
-        <v>0.88378186968838524</v>
+        <v>0.8838172804532578</v>
       </c>
       <c r="AG26" s="5">
         <v>16538</v>
@@ -4532,14 +4532,14 @@
       </c>
       <c r="AS26" s="3">
         <f t="shared" si="15"/>
-        <v>17035</v>
+        <v>17037</v>
       </c>
       <c r="AT26" s="3">
-        <v>25109</v>
+        <v>25111</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="16"/>
-        <v>0.88393297190734355</v>
+        <v>0.88400337956769692</v>
       </c>
       <c r="AV26" s="5">
         <v>16717</v>
@@ -4566,14 +4566,14 @@
       </c>
       <c r="BC26" s="3">
         <f t="shared" si="19"/>
-        <v>8536</v>
+        <v>8537</v>
       </c>
       <c r="BD26" s="5">
-        <v>13370</v>
+        <v>13371</v>
       </c>
       <c r="BE26" s="4">
         <f t="shared" si="20"/>
-        <v>0.9745608280486916</v>
+        <v>0.97463371965886725</v>
       </c>
       <c r="BF26" s="10">
         <v>25779</v>
@@ -4583,14 +4583,14 @@
       </c>
       <c r="BH26" s="3">
         <f t="shared" si="21"/>
-        <v>17869</v>
+        <v>17872</v>
       </c>
       <c r="BI26" s="5">
-        <v>25154</v>
+        <v>25157</v>
       </c>
       <c r="BJ26" s="4">
         <f t="shared" si="22"/>
-        <v>0.97575545987043721</v>
+        <v>0.97587183366305907</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4608,14 +4608,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>70228</v>
+        <v>70244</v>
       </c>
       <c r="F27" s="5">
-        <v>109118</v>
+        <v>109134</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>0.92078038242789395</v>
+        <v>0.9209153966887752</v>
       </c>
       <c r="H27" s="5">
         <v>121212</v>
@@ -4625,14 +4625,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>66295</v>
+        <v>66311</v>
       </c>
       <c r="K27" s="5">
-        <v>111192</v>
+        <v>111208</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.91733491733491734</v>
+        <v>0.91746691746691744</v>
       </c>
       <c r="M27" s="9">
         <v>178312</v>
@@ -4644,11 +4644,11 @@
         <v>161829</v>
       </c>
       <c r="P27" s="5">
-        <v>163098</v>
+        <v>163118</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="4"/>
-        <v>0.91467764368073934</v>
+        <v>0.91478980663107368</v>
       </c>
       <c r="R27" s="5">
         <v>121489</v>
@@ -4658,14 +4658,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="5"/>
-        <v>67684</v>
+        <v>67700</v>
       </c>
       <c r="U27" s="5">
-        <v>111712</v>
+        <v>111728</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="6"/>
-        <v>0.91952357826634512</v>
+        <v>0.91965527743252473</v>
       </c>
       <c r="W27" s="5">
         <v>123451</v>
@@ -4675,14 +4675,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="7"/>
-        <v>70969</v>
+        <v>70984</v>
       </c>
       <c r="Z27" s="5">
-        <v>113695</v>
+        <v>113710</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="8"/>
-        <v>0.92097269361933076</v>
+        <v>0.921094199317948</v>
       </c>
       <c r="AB27" s="5">
         <v>182601</v>
@@ -4692,14 +4692,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="9"/>
-        <v>117953</v>
+        <v>117971</v>
       </c>
       <c r="AE27" s="5">
-        <v>173225</v>
+        <v>173243</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="10"/>
-        <v>0.94865307418907896</v>
+        <v>0.94875164977190707</v>
       </c>
       <c r="AG27" s="5">
         <v>124689</v>
@@ -4709,14 +4709,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="11"/>
-        <v>69001</v>
+        <v>69016</v>
       </c>
       <c r="AJ27" s="5">
-        <v>117332</v>
+        <v>117347</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="12"/>
-        <v>0.94099720103617801</v>
+        <v>0.94111750034084807</v>
       </c>
       <c r="AL27" s="5">
         <v>127177</v>
@@ -4726,14 +4726,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" si="13"/>
-        <v>69439</v>
+        <v>69454</v>
       </c>
       <c r="AO27" s="5">
-        <v>119026</v>
+        <v>119041</v>
       </c>
       <c r="AP27" s="4">
         <f t="shared" si="14"/>
-        <v>0.93590822239870419</v>
+        <v>0.93602616825369367</v>
       </c>
       <c r="AQ27" s="3">
         <v>185152</v>
@@ -4743,14 +4743,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" si="15"/>
-        <v>105593</v>
+        <v>105614</v>
       </c>
       <c r="AT27" s="3">
-        <v>176789</v>
+        <v>176810</v>
       </c>
       <c r="AU27" s="4">
         <f t="shared" si="16"/>
-        <v>0.95483170584168686</v>
+        <v>0.95494512616660909</v>
       </c>
       <c r="AV27" s="5">
         <v>127611</v>
@@ -4760,14 +4760,14 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" si="17"/>
-        <v>66545</v>
+        <v>66562</v>
       </c>
       <c r="AY27" s="5">
-        <v>119092</v>
+        <v>119109</v>
       </c>
       <c r="AZ27" s="4">
         <f t="shared" si="18"/>
-        <v>0.93324243207873925</v>
+        <v>0.93337564943460982</v>
       </c>
       <c r="BA27" s="10">
         <v>122070</v>
@@ -4777,14 +4777,14 @@
       </c>
       <c r="BC27" s="3">
         <f t="shared" si="19"/>
-        <v>69487</v>
+        <v>69506</v>
       </c>
       <c r="BD27" s="5">
-        <v>120752</v>
+        <v>120771</v>
       </c>
       <c r="BE27" s="4">
         <f t="shared" si="20"/>
-        <v>0.98920291635946589</v>
+        <v>0.98935856475792583</v>
       </c>
       <c r="BF27" s="10">
         <v>180737</v>
@@ -4794,14 +4794,14 @@
       </c>
       <c r="BH27" s="3">
         <f t="shared" si="21"/>
-        <v>116035</v>
+        <v>116068</v>
       </c>
       <c r="BI27" s="5">
-        <v>179700</v>
+        <v>179733</v>
       </c>
       <c r="BJ27" s="4">
         <f t="shared" si="22"/>
-        <v>0.99426238125010369</v>
+        <v>0.99444496699624318</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4819,14 +4819,14 @@
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>155497</v>
+        <v>155503</v>
       </c>
       <c r="F28" s="5">
-        <v>342699</v>
+        <v>342705</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>0.9405505543967505</v>
+        <v>0.94056702162696237</v>
       </c>
       <c r="H28" s="5">
         <v>368904</v>
@@ -4836,14 +4836,14 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>152901</v>
+        <v>152906</v>
       </c>
       <c r="K28" s="5">
-        <v>347623</v>
+        <v>347628</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="3"/>
-        <v>0.94231290525448352</v>
+        <v>0.94232645891614075</v>
       </c>
       <c r="M28" s="9">
         <v>633580</v>
@@ -4855,11 +4855,11 @@
         <v>594498</v>
       </c>
       <c r="P28" s="5">
-        <v>595735</v>
+        <v>595743</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="4"/>
-        <v>0.94026800088386631</v>
+        <v>0.94028062754506136</v>
       </c>
       <c r="R28" s="5">
         <v>370844</v>
@@ -4869,14 +4869,14 @@
       </c>
       <c r="T28" s="3">
         <f t="shared" si="5"/>
-        <v>152902</v>
+        <v>152907</v>
       </c>
       <c r="U28" s="5">
-        <v>350171</v>
+        <v>350176</v>
       </c>
       <c r="V28" s="4">
         <f t="shared" si="6"/>
-        <v>0.94425418774471204</v>
+        <v>0.94426767050296079</v>
       </c>
       <c r="W28" s="5">
         <v>375522</v>
@@ -4886,14 +4886,14 @@
       </c>
       <c r="Y28" s="3">
         <f t="shared" si="7"/>
-        <v>159765</v>
+        <v>159771</v>
       </c>
       <c r="Z28" s="5">
-        <v>355196</v>
+        <v>355202</v>
       </c>
       <c r="AA28" s="4">
         <f t="shared" si="8"/>
-        <v>0.9458726785647712</v>
+        <v>0.94588865632373065</v>
       </c>
       <c r="AB28" s="5">
         <v>643156</v>
@@ -4903,14 +4903,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="9"/>
-        <v>319748</v>
+        <v>319754</v>
       </c>
       <c r="AE28" s="5">
-        <v>621195</v>
+        <v>621201</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="10"/>
-        <v>0.9658543183924273</v>
+        <v>0.96586364738881392</v>
       </c>
       <c r="AG28" s="5">
         <v>378725</v>
@@ -4920,14 +4920,14 @@
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="11"/>
-        <v>153056</v>
+        <v>153060</v>
       </c>
       <c r="AJ28" s="5">
-        <v>362795</v>
+        <v>362799</v>
       </c>
       <c r="AK28" s="4">
         <f t="shared" si="12"/>
-        <v>0.95793781767773445</v>
+        <v>0.95794837943098554</v>
       </c>
       <c r="AL28" s="5">
         <v>382864</v>
@@ -4937,14 +4937,14 @@
       </c>
       <c r="AN28" s="3">
         <f t="shared" si="13"/>
-        <v>155539</v>
+        <v>155544</v>
       </c>
       <c r="AO28" s="5">
-        <v>368172</v>
+        <v>368177</v>
       </c>
       <c r="AP28" s="4">
         <f t="shared" si="14"/>
-        <v>0.96162606042876841</v>
+        <v>0.96163911989636008</v>
       </c>
       <c r="AQ28" s="3">
         <v>653033</v>
@@ -4954,14 +4954,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="15"/>
-        <v>268759</v>
+        <v>268767</v>
       </c>
       <c r="AT28" s="3">
-        <v>629776</v>
+        <v>629784</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" si="16"/>
-        <v>0.96438617956519812</v>
+        <v>0.96439843009465065</v>
       </c>
       <c r="AV28" s="5">
         <v>393378</v>
@@ -4971,14 +4971,14 @@
       </c>
       <c r="AX28" s="3">
         <f t="shared" si="17"/>
-        <v>145228</v>
+        <v>145235</v>
       </c>
       <c r="AY28" s="5">
-        <v>371019</v>
+        <v>371026</v>
       </c>
       <c r="AZ28" s="4">
         <f t="shared" si="18"/>
-        <v>0.9431615392828272</v>
+        <v>0.94317933387225517</v>
       </c>
       <c r="BA28" s="10">
         <v>381893</v>
@@ -4988,14 +4988,14 @@
       </c>
       <c r="BC28" s="3">
         <f t="shared" si="19"/>
-        <v>155329</v>
+        <v>155336</v>
       </c>
       <c r="BD28" s="5">
-        <v>376415</v>
+        <v>376422</v>
       </c>
       <c r="BE28" s="4">
         <f t="shared" si="20"/>
-        <v>0.98565566794887571</v>
+        <v>0.98567399769045261</v>
       </c>
       <c r="BF28" s="10">
         <v>643514</v>
@@ -5005,14 +5005,14 @@
       </c>
       <c r="BH28" s="3">
         <f t="shared" si="21"/>
-        <v>301308</v>
+        <v>301321</v>
       </c>
       <c r="BI28" s="5">
-        <v>640657</v>
+        <v>640670</v>
       </c>
       <c r="BJ28" s="4">
         <f t="shared" si="22"/>
-        <v>0.99556031415011947</v>
+        <v>0.99558051573081552</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5066,11 +5066,11 @@
         <v>159082</v>
       </c>
       <c r="P29" s="5">
-        <v>159521</v>
+        <v>159522</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="4"/>
-        <v>0.94448687661710984</v>
+        <v>0.94449279738538872</v>
       </c>
       <c r="R29" s="5">
         <v>122532</v>
@@ -5114,14 +5114,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="9"/>
-        <v>96102</v>
+        <v>96104</v>
       </c>
       <c r="AE29" s="5">
-        <v>166280</v>
+        <v>166282</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="10"/>
-        <v>0.96297626148847826</v>
+        <v>0.96298784407521731</v>
       </c>
       <c r="AG29" s="5">
         <v>125793</v>
@@ -5131,14 +5131,14 @@
       </c>
       <c r="AI29" s="3">
         <f t="shared" si="11"/>
-        <v>61137</v>
+        <v>61138</v>
       </c>
       <c r="AJ29" s="5">
-        <v>120740</v>
+        <v>120741</v>
       </c>
       <c r="AK29" s="4">
         <f t="shared" si="12"/>
-        <v>0.95983083319421592</v>
+        <v>0.95983878276215684</v>
       </c>
       <c r="AL29" s="5">
         <v>126934</v>
@@ -5148,14 +5148,14 @@
       </c>
       <c r="AN29" s="3">
         <f t="shared" si="13"/>
-        <v>59755</v>
+        <v>59756</v>
       </c>
       <c r="AO29" s="5">
-        <v>122148</v>
+        <v>122149</v>
       </c>
       <c r="AP29" s="4">
         <f t="shared" si="14"/>
-        <v>0.96229536609576627</v>
+        <v>0.96230324420565017</v>
       </c>
       <c r="AQ29" s="3">
         <v>175834</v>
@@ -5165,14 +5165,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="15"/>
-        <v>84971</v>
+        <v>84973</v>
       </c>
       <c r="AT29" s="3">
-        <v>169371</v>
+        <v>169373</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="16"/>
-        <v>0.96324374125595735</v>
+        <v>0.96325511562041466</v>
       </c>
       <c r="AV29" s="5">
         <v>130198</v>
@@ -5182,14 +5182,14 @@
       </c>
       <c r="AX29" s="3">
         <f t="shared" si="17"/>
-        <v>57545</v>
+        <v>57546</v>
       </c>
       <c r="AY29" s="5">
-        <v>123683</v>
+        <v>123684</v>
       </c>
       <c r="AZ29" s="4">
         <f t="shared" si="18"/>
-        <v>0.94996082889138078</v>
+        <v>0.94996850950091394</v>
       </c>
       <c r="BA29" s="10">
         <v>127545</v>
@@ -5199,14 +5199,14 @@
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="19"/>
-        <v>63483</v>
+        <v>63484</v>
       </c>
       <c r="BD29" s="5">
-        <v>125564</v>
+        <v>125565</v>
       </c>
       <c r="BE29" s="4">
         <f t="shared" si="20"/>
-        <v>0.98446822690030966</v>
+        <v>0.98447606727037518</v>
       </c>
       <c r="BF29" s="10">
         <v>174166</v>
@@ -5216,14 +5216,14 @@
       </c>
       <c r="BH29" s="3">
         <f t="shared" si="21"/>
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="BI29" s="5">
-        <v>172937</v>
+        <v>172941</v>
       </c>
       <c r="BJ29" s="4">
         <f t="shared" si="22"/>
-        <v>0.99294351365938238</v>
+        <v>0.99296648025446987</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>88704</v>
+        <v>88711</v>
       </c>
       <c r="F30" s="5">
-        <v>147116</v>
+        <v>147123</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>0.92743938572491269</v>
+        <v>0.92748351468233459</v>
       </c>
       <c r="H30" s="5">
         <v>160653</v>
@@ -5258,14 +5258,14 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>85760</v>
+        <v>85766</v>
       </c>
       <c r="K30" s="5">
-        <v>150111</v>
+        <v>150117</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="3"/>
-        <v>0.93438031035835001</v>
+        <v>0.93441765793355869</v>
       </c>
       <c r="M30" s="9">
         <v>275749</v>
@@ -5277,11 +5277,11 @@
         <v>254361</v>
       </c>
       <c r="P30" s="5">
-        <v>255509</v>
+        <v>255525</v>
       </c>
       <c r="Q30" s="4">
         <f t="shared" si="4"/>
-        <v>0.92659991514021811</v>
+        <v>0.92665793892271597</v>
       </c>
       <c r="R30" s="5">
         <v>161454</v>
@@ -5291,14 +5291,14 @@
       </c>
       <c r="T30" s="3">
         <f t="shared" si="5"/>
-        <v>89009</v>
+        <v>89018</v>
       </c>
       <c r="U30" s="5">
-        <v>150294</v>
+        <v>150303</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" si="6"/>
-        <v>0.93087814485859754</v>
+        <v>0.9309338882901631</v>
       </c>
       <c r="W30" s="5">
         <v>163696</v>
@@ -5308,14 +5308,14 @@
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="7"/>
-        <v>91660</v>
+        <v>91670</v>
       </c>
       <c r="Z30" s="5">
-        <v>153477</v>
+        <v>153487</v>
       </c>
       <c r="AA30" s="4">
         <f t="shared" si="8"/>
-        <v>0.937573306617144</v>
+        <v>0.9376343954647639</v>
       </c>
       <c r="AB30" s="5">
         <v>281667</v>
@@ -5325,14 +5325,14 @@
       </c>
       <c r="AD30" s="3">
         <f t="shared" si="9"/>
-        <v>177373</v>
+        <v>177385</v>
       </c>
       <c r="AE30" s="5">
-        <v>271163</v>
+        <v>271175</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="10"/>
-        <v>0.96270773644054863</v>
+        <v>0.96275033994042614</v>
       </c>
       <c r="AG30" s="5">
         <v>165324</v>
@@ -5342,14 +5342,14 @@
       </c>
       <c r="AI30" s="3">
         <f t="shared" si="11"/>
-        <v>90146</v>
+        <v>90153</v>
       </c>
       <c r="AJ30" s="5">
-        <v>158263</v>
+        <v>158270</v>
       </c>
       <c r="AK30" s="4">
         <f t="shared" si="12"/>
-        <v>0.95728992765720644</v>
+        <v>0.95733226875710731</v>
       </c>
       <c r="AL30" s="5">
         <v>168552</v>
@@ -5359,14 +5359,14 @@
       </c>
       <c r="AN30" s="3">
         <f t="shared" si="13"/>
-        <v>88483</v>
+        <v>88490</v>
       </c>
       <c r="AO30" s="5">
-        <v>161670</v>
+        <v>161677</v>
       </c>
       <c r="AP30" s="4">
         <f t="shared" si="14"/>
-        <v>0.95916987042574398</v>
+        <v>0.95921140063600552</v>
       </c>
       <c r="AQ30" s="3">
         <v>288456</v>
@@ -5376,14 +5376,14 @@
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="15"/>
-        <v>160979</v>
+        <v>160992</v>
       </c>
       <c r="AT30" s="3">
-        <v>277786</v>
+        <v>277799</v>
       </c>
       <c r="AU30" s="4">
         <f t="shared" si="16"/>
-        <v>0.96300995645783061</v>
+        <v>0.96305502398979392</v>
       </c>
       <c r="AV30" s="5">
         <v>173481</v>
@@ -5393,14 +5393,14 @@
       </c>
       <c r="AX30" s="3">
         <f t="shared" si="17"/>
-        <v>85695</v>
+        <v>85702</v>
       </c>
       <c r="AY30" s="5">
-        <v>162665</v>
+        <v>162672</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="18"/>
-        <v>0.93765311475031843</v>
+        <v>0.9376934649904024</v>
       </c>
       <c r="BA30" s="10">
         <v>168414</v>
@@ -5410,14 +5410,14 @@
       </c>
       <c r="BC30" s="3">
         <f t="shared" si="19"/>
-        <v>90655</v>
+        <v>90663</v>
       </c>
       <c r="BD30" s="5">
-        <v>165606</v>
+        <v>165614</v>
       </c>
       <c r="BE30" s="4">
         <f t="shared" si="20"/>
-        <v>0.98332680180982579</v>
+        <v>0.98337430379897162</v>
       </c>
       <c r="BF30" s="10">
         <v>284492</v>
@@ -5427,14 +5427,14 @@
       </c>
       <c r="BH30" s="3">
         <f t="shared" si="21"/>
-        <v>173840</v>
+        <v>173856</v>
       </c>
       <c r="BI30" s="5">
-        <v>283703</v>
+        <v>283719</v>
       </c>
       <c r="BJ30" s="4">
         <f t="shared" si="22"/>
-        <v>0.99722663554686952</v>
+        <v>0.99728287614414468</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5452,14 +5452,14 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>37117</v>
+        <v>37120</v>
       </c>
       <c r="F31" s="5">
-        <v>70028</v>
+        <v>70031</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>0.94186953597848011</v>
+        <v>0.94190988567585743</v>
       </c>
       <c r="H31" s="5">
         <v>75353</v>
@@ -5469,14 +5469,14 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>35308</v>
+        <v>35313</v>
       </c>
       <c r="K31" s="5">
-        <v>71146</v>
+        <v>71151</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="3"/>
-        <v>0.94416944249067725</v>
+        <v>0.94423579684949499</v>
       </c>
       <c r="M31" s="9">
         <v>132153</v>
@@ -5488,11 +5488,11 @@
         <v>124102</v>
       </c>
       <c r="P31" s="5">
-        <v>124744</v>
+        <v>124749</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="4"/>
-        <v>0.94393619516772231</v>
+        <v>0.94397403010147329</v>
       </c>
       <c r="R31" s="5">
         <v>74474</v>
@@ -5502,14 +5502,14 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="5"/>
-        <v>35653</v>
+        <v>35658</v>
       </c>
       <c r="U31" s="5">
-        <v>69996</v>
+        <v>70001</v>
       </c>
       <c r="V31" s="4">
         <f t="shared" si="6"/>
-        <v>0.93987163305314603</v>
+        <v>0.93993877057765129</v>
       </c>
       <c r="W31" s="5">
         <v>75697</v>
@@ -5519,14 +5519,14 @@
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="7"/>
-        <v>36672</v>
+        <v>36677</v>
       </c>
       <c r="Z31" s="5">
-        <v>71276</v>
+        <v>71281</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" si="8"/>
-        <v>0.94159610024175333</v>
+        <v>0.94166215305758483</v>
       </c>
       <c r="AB31" s="5">
         <v>133809</v>
@@ -5536,14 +5536,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="9"/>
-        <v>73403</v>
+        <v>73406</v>
       </c>
       <c r="AE31" s="5">
-        <v>129289</v>
+        <v>129292</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="10"/>
-        <v>0.96622050833650952</v>
+        <v>0.96624292835310033</v>
       </c>
       <c r="AG31" s="5">
         <v>75434</v>
@@ -5553,14 +5553,14 @@
       </c>
       <c r="AI31" s="3">
         <f t="shared" si="11"/>
-        <v>33304</v>
+        <v>33307</v>
       </c>
       <c r="AJ31" s="5">
-        <v>72071</v>
+        <v>72074</v>
       </c>
       <c r="AK31" s="4">
         <f t="shared" si="12"/>
-        <v>0.95541798128165023</v>
+        <v>0.95545775114669773</v>
       </c>
       <c r="AL31" s="5">
         <v>76990</v>
@@ -5570,14 +5570,14 @@
       </c>
       <c r="AN31" s="3">
         <f t="shared" si="13"/>
-        <v>33569</v>
+        <v>33572</v>
       </c>
       <c r="AO31" s="5">
-        <v>73086</v>
+        <v>73089</v>
       </c>
       <c r="AP31" s="4">
         <f t="shared" si="14"/>
-        <v>0.94929211585920248</v>
+        <v>0.94933108195869598</v>
       </c>
       <c r="AQ31" s="3">
         <v>135546</v>
@@ -5587,14 +5587,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="15"/>
-        <v>64944</v>
+        <v>64949</v>
       </c>
       <c r="AT31" s="3">
-        <v>131236</v>
+        <v>131241</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="16"/>
-        <v>0.96820267658211967</v>
+        <v>0.96823956442831216</v>
       </c>
       <c r="AV31" s="5">
         <v>78435</v>
@@ -5604,14 +5604,14 @@
       </c>
       <c r="AX31" s="3">
         <f t="shared" si="17"/>
-        <v>30756</v>
+        <v>30760</v>
       </c>
       <c r="AY31" s="5">
-        <v>73080</v>
+        <v>73084</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="18"/>
-        <v>0.93172690763052213</v>
+        <v>0.9317779052718812</v>
       </c>
       <c r="BA31" s="10">
         <v>76166</v>
@@ -5621,14 +5621,14 @@
       </c>
       <c r="BC31" s="3">
         <f t="shared" si="19"/>
-        <v>33771</v>
+        <v>33774</v>
       </c>
       <c r="BD31" s="5">
-        <v>74308</v>
+        <v>74311</v>
       </c>
       <c r="BE31" s="4">
         <f t="shared" si="20"/>
-        <v>0.97560591339967961</v>
+        <v>0.97564530105296321</v>
       </c>
       <c r="BF31" s="10">
         <v>132970</v>
@@ -5638,14 +5638,14 @@
       </c>
       <c r="BH31" s="3">
         <f t="shared" si="21"/>
-        <v>74220</v>
+        <v>74225</v>
       </c>
       <c r="BI31" s="5">
-        <v>133195</v>
+        <v>133200</v>
       </c>
       <c r="BJ31" s="4">
         <f t="shared" si="22"/>
-        <v>1.0016921110024817</v>
+        <v>1.0017297134692036</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5663,14 +5663,14 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>91608</v>
+        <v>91610</v>
       </c>
       <c r="F32" s="5">
-        <v>184442</v>
+        <v>184444</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>0.96064542338982695</v>
+        <v>0.96065584016500172</v>
       </c>
       <c r="H32" s="5">
         <v>196288</v>
@@ -5680,14 +5680,14 @@
       </c>
       <c r="J32" s="3">
         <f t="shared" si="2"/>
-        <v>87694</v>
+        <v>87697</v>
       </c>
       <c r="K32" s="5">
-        <v>188227</v>
+        <v>188230</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="3"/>
-        <v>0.95893279263123576</v>
+        <v>0.95894807629605483</v>
       </c>
       <c r="M32" s="9">
         <v>418497</v>
@@ -5699,11 +5699,11 @@
         <v>397306</v>
       </c>
       <c r="P32" s="5">
-        <v>398323</v>
+        <v>398327</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="4"/>
-        <v>0.95179415862001404</v>
+        <v>0.95180371663357199</v>
       </c>
       <c r="R32" s="5">
         <v>194320</v>
@@ -5713,14 +5713,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="5"/>
-        <v>94015</v>
+        <v>94017</v>
       </c>
       <c r="U32" s="5">
-        <v>186164</v>
+        <v>186166</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="6"/>
-        <v>0.95802799505969538</v>
+        <v>0.9580382873610539</v>
       </c>
       <c r="W32" s="5">
         <v>198209</v>
@@ -5730,14 +5730,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="7"/>
-        <v>97015</v>
+        <v>97018</v>
       </c>
       <c r="Z32" s="5">
-        <v>190195</v>
+        <v>190198</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="8"/>
-        <v>0.95956793082049752</v>
+        <v>0.95958306635924706</v>
       </c>
       <c r="AB32" s="5">
         <v>426405</v>
@@ -5747,14 +5747,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="9"/>
-        <v>243319</v>
+        <v>243324</v>
       </c>
       <c r="AE32" s="5">
-        <v>418618</v>
+        <v>418623</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="10"/>
-        <v>0.98173801901947677</v>
+        <v>0.98174974496077672</v>
       </c>
       <c r="AG32" s="5">
         <v>199136</v>
@@ -5764,14 +5764,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="11"/>
-        <v>82203</v>
+        <v>82205</v>
       </c>
       <c r="AJ32" s="5">
-        <v>194593</v>
+        <v>194595</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="12"/>
-        <v>0.97718644544431943</v>
+        <v>0.97719648883175314</v>
       </c>
       <c r="AL32" s="5">
         <v>204506</v>
@@ -5781,14 +5781,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="13"/>
-        <v>84506</v>
+        <v>84508</v>
       </c>
       <c r="AO32" s="5">
-        <v>199088</v>
+        <v>199090</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="14"/>
-        <v>0.97350688977340516</v>
+        <v>0.97351666943757154</v>
       </c>
       <c r="AQ32" s="3">
         <v>435626</v>
@@ -5798,14 +5798,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="15"/>
-        <v>206034</v>
+        <v>206038</v>
       </c>
       <c r="AT32" s="3">
-        <v>427426</v>
+        <v>427430</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="16"/>
-        <v>0.98117651379853366</v>
+        <v>0.98118569598692451</v>
       </c>
       <c r="AV32" s="5">
         <v>208760</v>
@@ -5815,14 +5815,14 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="17"/>
-        <v>78085</v>
+        <v>78088</v>
       </c>
       <c r="AY32" s="5">
-        <v>198444</v>
+        <v>198447</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="18"/>
-        <v>0.95058440314236448</v>
+        <v>0.95059877371143897</v>
       </c>
       <c r="BA32" s="10">
         <v>206539</v>
@@ -5832,14 +5832,14 @@
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="19"/>
-        <v>86622</v>
+        <v>86625</v>
       </c>
       <c r="BD32" s="5">
-        <v>203319</v>
+        <v>203322</v>
       </c>
       <c r="BE32" s="4">
         <f t="shared" si="20"/>
-        <v>0.98440972407148286</v>
+        <v>0.98442424917327964</v>
       </c>
       <c r="BF32" s="10">
         <v>435831</v>
@@ -5849,14 +5849,14 @@
       </c>
       <c r="BH32" s="3">
         <f t="shared" si="21"/>
-        <v>241646</v>
+        <v>241653</v>
       </c>
       <c r="BI32" s="5">
-        <v>436067</v>
+        <v>436074</v>
       </c>
       <c r="BJ32" s="4">
         <f t="shared" si="22"/>
-        <v>1.000541494294807</v>
+        <v>1.0005575555662631</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5874,14 +5874,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>112229</v>
+        <v>112233</v>
       </c>
       <c r="F33" s="5">
-        <v>577919</v>
+        <v>577923</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>0.98535737851381144</v>
+        <v>0.98536419855176494</v>
       </c>
       <c r="H33" s="5">
         <v>594451</v>
@@ -5891,14 +5891,14 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>102372</v>
+        <v>102376</v>
       </c>
       <c r="K33" s="5">
-        <v>588532</v>
+        <v>588536</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="3"/>
-        <v>0.99004291354543938</v>
+        <v>0.99004964244319549</v>
       </c>
       <c r="M33" s="9">
         <v>1006436</v>
@@ -5910,11 +5910,11 @@
         <v>989274</v>
       </c>
       <c r="P33" s="5">
-        <v>989976</v>
+        <v>989985</v>
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="4"/>
-        <v>0.9836452591123529</v>
+        <v>0.98365420155876782</v>
       </c>
       <c r="R33" s="5">
         <v>599279</v>
@@ -5924,14 +5924,14 @@
       </c>
       <c r="T33" s="3">
         <f t="shared" si="5"/>
-        <v>115337</v>
+        <v>115341</v>
       </c>
       <c r="U33" s="5">
-        <v>590804</v>
+        <v>590808</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="6"/>
-        <v>0.98585800603725482</v>
+        <v>0.98586468072467082</v>
       </c>
       <c r="W33" s="5">
         <v>608923</v>
@@ -5941,14 +5941,14 @@
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="7"/>
-        <v>119609</v>
+        <v>119615</v>
       </c>
       <c r="Z33" s="5">
-        <v>598465</v>
+        <v>598471</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" si="8"/>
-        <v>0.98282541470760676</v>
+        <v>0.98283526817019562</v>
       </c>
       <c r="AB33" s="5">
         <v>1019860</v>
@@ -5958,14 +5958,14 @@
       </c>
       <c r="AD33" s="3">
         <f t="shared" si="9"/>
-        <v>208785</v>
+        <v>208795</v>
       </c>
       <c r="AE33" s="5">
-        <v>1007581</v>
+        <v>1007591</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="10"/>
-        <v>0.98796011217225899</v>
+        <v>0.98796991743964857</v>
       </c>
       <c r="AG33" s="5">
         <v>610453</v>
@@ -5975,14 +5975,14 @@
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="11"/>
-        <v>103198</v>
+        <v>103203</v>
       </c>
       <c r="AJ33" s="5">
-        <v>601255</v>
+        <v>601260</v>
       </c>
       <c r="AK33" s="4">
         <f t="shared" si="12"/>
-        <v>0.98493250094601881</v>
+        <v>0.98494069158477393</v>
       </c>
       <c r="AL33" s="5">
         <v>617988</v>
@@ -5992,14 +5992,14 @@
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="13"/>
-        <v>97615</v>
+        <v>97620</v>
       </c>
       <c r="AO33" s="5">
-        <v>607246</v>
+        <v>607251</v>
       </c>
       <c r="AP33" s="4">
         <f t="shared" si="14"/>
-        <v>0.98261778545861733</v>
+        <v>0.98262587623060638</v>
       </c>
       <c r="AQ33" s="3">
         <v>1027609</v>
@@ -6009,14 +6009,14 @@
       </c>
       <c r="AS33" s="3">
         <f t="shared" si="15"/>
-        <v>158958</v>
+        <v>158968</v>
       </c>
       <c r="AT33" s="3">
-        <v>1016479</v>
+        <v>1016489</v>
       </c>
       <c r="AU33" s="4">
         <f t="shared" si="16"/>
-        <v>0.98916903219025909</v>
+        <v>0.98917876351803069</v>
       </c>
       <c r="AV33" s="5">
         <v>625585</v>
@@ -6026,14 +6026,14 @@
       </c>
       <c r="AX33" s="3">
         <f t="shared" si="17"/>
-        <v>80334</v>
+        <v>80339</v>
       </c>
       <c r="AY33" s="5">
-        <v>609863</v>
+        <v>609868</v>
       </c>
       <c r="AZ33" s="4">
         <f t="shared" si="18"/>
-        <v>0.97486832324943851</v>
+        <v>0.97487631576844069</v>
       </c>
       <c r="BA33" s="10">
         <v>617039</v>
@@ -6043,14 +6043,14 @@
       </c>
       <c r="BC33" s="3">
         <f t="shared" si="19"/>
-        <v>85338</v>
+        <v>85341</v>
       </c>
       <c r="BD33" s="5">
-        <v>616843</v>
+        <v>616846</v>
       </c>
       <c r="BE33" s="4">
         <f t="shared" si="20"/>
-        <v>0.99968235395169514</v>
+        <v>0.99968721588100595</v>
       </c>
       <c r="BF33" s="10">
         <v>1025594</v>
@@ -6060,14 +6060,14 @@
       </c>
       <c r="BH33" s="3">
         <f t="shared" si="21"/>
-        <v>198090</v>
+        <v>198100</v>
       </c>
       <c r="BI33" s="5">
-        <v>1029951</v>
+        <v>1029961</v>
       </c>
       <c r="BJ33" s="4">
         <f t="shared" si="22"/>
-        <v>1.0042482697831696</v>
+        <v>1.0042580202302276</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6484,14 +6484,14 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="0"/>
-        <v>280724</v>
+        <v>280740</v>
       </c>
       <c r="F36" s="5">
-        <v>767010</v>
+        <v>767026</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="1"/>
-        <v>0.95381340071702947</v>
+        <v>0.95383329747771251</v>
       </c>
       <c r="H36" s="5">
         <v>814447</v>
@@ -6501,14 +6501,14 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="2"/>
-        <v>265449</v>
+        <v>265466</v>
       </c>
       <c r="K36" s="5">
-        <v>778859</v>
+        <v>778876</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="3"/>
-        <v>0.95630409345236711</v>
+        <v>0.95632496651101917</v>
       </c>
       <c r="M36" s="9">
         <v>1485608</v>
@@ -6520,11 +6520,11 @@
         <v>1417521</v>
       </c>
       <c r="P36" s="5">
-        <v>1419967</v>
+        <v>1419999</v>
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="4"/>
-        <v>0.95581539679377059</v>
+        <v>0.9558369367962477</v>
       </c>
       <c r="R36" s="5">
         <v>815623</v>
@@ -6534,14 +6534,14 @@
       </c>
       <c r="T36" s="3">
         <f t="shared" si="5"/>
-        <v>268163</v>
+        <v>268182</v>
       </c>
       <c r="U36" s="5">
-        <v>778518</v>
+        <v>778537</v>
       </c>
       <c r="V36" s="4">
         <f t="shared" si="6"/>
-        <v>0.95450716814018244</v>
+        <v>0.95453046321646151</v>
       </c>
       <c r="W36" s="5">
         <v>826349</v>
@@ -6551,14 +6551,14 @@
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="7"/>
-        <v>288583</v>
+        <v>288601</v>
       </c>
       <c r="Z36" s="5">
-        <v>788735</v>
+        <v>788753</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="8"/>
-        <v>0.95448170204114724</v>
+        <v>0.95450348460517287</v>
       </c>
       <c r="AB36" s="5">
         <v>1500292</v>
@@ -6568,14 +6568,14 @@
       </c>
       <c r="AD36" s="3">
         <f t="shared" si="9"/>
-        <v>549384</v>
+        <v>549408</v>
       </c>
       <c r="AE36" s="5">
-        <v>1455700</v>
+        <v>1455724</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="10"/>
-        <v>0.97027778592434011</v>
+        <v>0.97029378281027956</v>
       </c>
       <c r="AG36" s="5">
         <v>833041</v>
@@ -6585,14 +6585,14 @@
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="11"/>
-        <v>255469</v>
+        <v>255487</v>
       </c>
       <c r="AJ36" s="5">
-        <v>802854</v>
+        <v>802872</v>
       </c>
       <c r="AK36" s="4">
         <f t="shared" si="12"/>
-        <v>0.96376288802111776</v>
+        <v>0.96378449560105683</v>
       </c>
       <c r="AL36" s="5">
         <v>845911</v>
@@ -6602,14 +6602,14 @@
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="13"/>
-        <v>252944</v>
+        <v>252963</v>
       </c>
       <c r="AO36" s="5">
-        <v>815179</v>
+        <v>815198</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="14"/>
-        <v>0.96366993690825631</v>
+        <v>0.96369239790001548</v>
       </c>
       <c r="AQ36" s="3">
         <v>1519147</v>
@@ -6619,14 +6619,14 @@
       </c>
       <c r="AS36" s="3">
         <f t="shared" si="15"/>
-        <v>450213</v>
+        <v>450240</v>
       </c>
       <c r="AT36" s="3">
-        <v>1477353</v>
+        <v>1477380</v>
       </c>
       <c r="AU36" s="4">
         <f t="shared" si="16"/>
-        <v>0.97248850835370115</v>
+        <v>0.97250628148559681</v>
       </c>
       <c r="AV36" s="5">
         <v>864672</v>
@@ -6636,14 +6636,14 @@
       </c>
       <c r="AX36" s="3">
         <f t="shared" si="17"/>
-        <v>218857</v>
+        <v>218876</v>
       </c>
       <c r="AY36" s="5">
-        <v>817718</v>
+        <v>817737</v>
       </c>
       <c r="AZ36" s="4">
         <f t="shared" si="18"/>
-        <v>0.94569732800414497</v>
+        <v>0.94571930165426887</v>
       </c>
       <c r="BA36" s="10">
         <v>838532</v>
@@ -6653,14 +6653,14 @@
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="19"/>
-        <v>226503</v>
+        <v>226523</v>
       </c>
       <c r="BD36" s="5">
-        <v>830257</v>
+        <v>830277</v>
       </c>
       <c r="BE36" s="4">
         <f t="shared" si="20"/>
-        <v>0.99013156325578511</v>
+        <v>0.99015541446241762</v>
       </c>
       <c r="BF36" s="10">
         <v>1502094</v>
@@ -6670,14 +6670,14 @@
       </c>
       <c r="BH36" s="3">
         <f t="shared" si="23"/>
-        <v>507824</v>
+        <v>507854</v>
       </c>
       <c r="BI36" s="5">
-        <v>1498474</v>
+        <v>1498504</v>
       </c>
       <c r="BJ36" s="4">
         <f t="shared" si="24"/>
-        <v>0.99759003098341381</v>
+        <v>0.99761000310233583</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6695,14 +6695,14 @@
       </c>
       <c r="E37" s="3">
         <f t="shared" si="0"/>
-        <v>268679</v>
+        <v>268690</v>
       </c>
       <c r="F37" s="5">
-        <v>609896</v>
+        <v>609907</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="1"/>
-        <v>0.9373829032163864</v>
+        <v>0.93739980972493109</v>
       </c>
       <c r="H37" s="5">
         <v>656039</v>
@@ -6712,14 +6712,14 @@
       </c>
       <c r="J37" s="3">
         <f t="shared" si="2"/>
-        <v>249917</v>
+        <v>249928</v>
       </c>
       <c r="K37" s="5">
-        <v>615186</v>
+        <v>615197</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="3"/>
-        <v>0.93772778752482699</v>
+        <v>0.93774455482067376</v>
       </c>
       <c r="M37" s="9">
         <v>844882</v>
@@ -6731,11 +6731,11 @@
         <v>786859</v>
       </c>
       <c r="P37" s="5">
-        <v>789053</v>
+        <v>789067</v>
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="4"/>
-        <v>0.93392094990779773</v>
+        <v>0.93393752026910271</v>
       </c>
       <c r="R37" s="5">
         <v>664863</v>
@@ -6745,14 +6745,14 @@
       </c>
       <c r="T37" s="3">
         <f t="shared" si="5"/>
-        <v>256832</v>
+        <v>256844</v>
       </c>
       <c r="U37" s="5">
-        <v>621959</v>
+        <v>621971</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="6"/>
-        <v>0.93546941249550664</v>
+        <v>0.9354874613266192</v>
       </c>
       <c r="W37" s="5">
         <v>670009</v>
@@ -6762,14 +6762,14 @@
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="7"/>
-        <v>275152</v>
+        <v>275163</v>
       </c>
       <c r="Z37" s="5">
-        <v>628397</v>
+        <v>628408</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="8"/>
-        <v>0.93789337158157582</v>
+        <v>0.93790978927148738</v>
       </c>
       <c r="AB37" s="5">
         <v>858143</v>
@@ -6779,14 +6779,14 @@
       </c>
       <c r="AD37" s="3">
         <f t="shared" si="9"/>
-        <v>383144</v>
+        <v>383155</v>
       </c>
       <c r="AE37" s="5">
-        <v>819515</v>
+        <v>819526</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="10"/>
-        <v>0.9549865232251501</v>
+        <v>0.95499934160157451</v>
       </c>
       <c r="AG37" s="5">
         <v>675943</v>
@@ -6796,14 +6796,14 @@
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="11"/>
-        <v>251690</v>
+        <v>251699</v>
       </c>
       <c r="AJ37" s="5">
-        <v>644667</v>
+        <v>644676</v>
       </c>
       <c r="AK37" s="4">
         <f t="shared" si="12"/>
-        <v>0.95372982633151016</v>
+        <v>0.95374314106366953</v>
       </c>
       <c r="AL37" s="5">
         <v>678429</v>
@@ -6813,14 +6813,14 @@
       </c>
       <c r="AN37" s="3">
         <f t="shared" si="13"/>
-        <v>248261</v>
+        <v>248269</v>
       </c>
       <c r="AO37" s="5">
-        <v>650779</v>
+        <v>650787</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="14"/>
-        <v>0.95924407712524085</v>
+        <v>0.95925586907399296</v>
       </c>
       <c r="AQ37" s="3">
         <v>865622</v>
@@ -6830,14 +6830,14 @@
       </c>
       <c r="AS37" s="3">
         <f t="shared" si="15"/>
-        <v>314978</v>
+        <v>314989</v>
       </c>
       <c r="AT37" s="3">
-        <v>834222</v>
+        <v>834233</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="16"/>
-        <v>0.96372550605229534</v>
+        <v>0.96373821367756363</v>
       </c>
       <c r="AV37" s="5">
         <v>690116</v>
@@ -6847,14 +6847,14 @@
       </c>
       <c r="AX37" s="3">
         <f t="shared" si="17"/>
-        <v>235049</v>
+        <v>235057</v>
       </c>
       <c r="AY37" s="5">
-        <v>658575</v>
+        <v>658583</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="18"/>
-        <v>0.95429608935309429</v>
+        <v>0.95430768160715007</v>
       </c>
       <c r="BA37" s="10">
         <v>673244</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="19"/>
-        <v>241632</v>
+        <v>241641</v>
       </c>
       <c r="BD37" s="5">
-        <v>665199</v>
+        <v>665208</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="20"/>
-        <v>0.98805039480485535</v>
+        <v>0.9880637629150798</v>
       </c>
       <c r="BF37" s="10">
         <v>856336</v>
@@ -6881,14 +6881,14 @@
       </c>
       <c r="BH37" s="3">
         <f t="shared" si="23"/>
-        <v>356942</v>
+        <v>356959</v>
       </c>
       <c r="BI37" s="5">
-        <v>848325</v>
+        <v>848342</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="24"/>
-        <v>0.99064502718559067</v>
+        <v>0.99066487920629287</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -6906,14 +6906,14 @@
       </c>
       <c r="E38" s="3">
         <f t="shared" si="0"/>
-        <v>9844</v>
+        <v>9845</v>
       </c>
       <c r="F38" s="5">
-        <v>20901</v>
+        <v>20902</v>
       </c>
       <c r="G38" s="4">
         <f t="shared" si="1"/>
-        <v>0.83477114785525997</v>
+        <v>0.83481108714753571</v>
       </c>
       <c r="H38" s="5">
         <v>25302</v>
@@ -6923,14 +6923,14 @@
       </c>
       <c r="J38" s="3">
         <f t="shared" si="2"/>
-        <v>9366</v>
+        <v>9367</v>
       </c>
       <c r="K38" s="5">
-        <v>21188</v>
+        <v>21189</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" si="3"/>
-        <v>0.83740415777408905</v>
+        <v>0.83744368034147498</v>
       </c>
       <c r="M38" s="9">
         <v>37823</v>
@@ -6942,11 +6942,11 @@
         <v>33105</v>
       </c>
       <c r="P38" s="5">
-        <v>33261</v>
+        <v>33262</v>
       </c>
       <c r="Q38" s="4">
         <f t="shared" si="4"/>
-        <v>0.87938555905137084</v>
+        <v>0.87941199799064063</v>
       </c>
       <c r="R38" s="5">
         <v>25469</v>
@@ -6956,14 +6956,14 @@
       </c>
       <c r="T38" s="3">
         <f t="shared" si="5"/>
-        <v>9424</v>
+        <v>9425</v>
       </c>
       <c r="U38" s="5">
-        <v>21280</v>
+        <v>21281</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" si="6"/>
-        <v>0.83552554085358677</v>
+        <v>0.83556480427185986</v>
       </c>
       <c r="W38" s="5">
         <v>25404</v>
@@ -6973,14 +6973,14 @@
       </c>
       <c r="Y38" s="3">
         <f t="shared" si="7"/>
-        <v>10221</v>
+        <v>10222</v>
       </c>
       <c r="Z38" s="5">
-        <v>21496</v>
+        <v>21497</v>
       </c>
       <c r="AA38" s="4">
         <f t="shared" si="8"/>
-        <v>0.84616595811683204</v>
+        <v>0.84620532199653598</v>
       </c>
       <c r="AB38" s="5">
         <v>37238</v>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="AD38" s="3">
         <f t="shared" si="9"/>
-        <v>15116</v>
+        <v>15118</v>
       </c>
       <c r="AE38" s="5">
-        <v>34044</v>
+        <v>34046</v>
       </c>
       <c r="AF38" s="4">
         <f t="shared" si="10"/>
-        <v>0.91422740211611797</v>
+        <v>0.9142811106933777</v>
       </c>
       <c r="AG38" s="5">
         <v>24904</v>
@@ -7007,14 +7007,14 @@
       </c>
       <c r="AI38" s="3">
         <f t="shared" si="11"/>
-        <v>8883</v>
+        <v>8885</v>
       </c>
       <c r="AJ38" s="5">
-        <v>21929</v>
+        <v>21931</v>
       </c>
       <c r="AK38" s="4">
         <f t="shared" si="12"/>
-        <v>0.88054127850947639</v>
+        <v>0.88062158689367165</v>
       </c>
       <c r="AL38" s="5">
         <v>25338</v>
@@ -7024,14 +7024,14 @@
       </c>
       <c r="AN38" s="3">
         <f t="shared" si="13"/>
-        <v>9526</v>
+        <v>9527</v>
       </c>
       <c r="AO38" s="5">
-        <v>22351</v>
+        <v>22352</v>
       </c>
       <c r="AP38" s="4">
         <f t="shared" si="14"/>
-        <v>0.88211382113821135</v>
+        <v>0.88215328755229305</v>
       </c>
       <c r="AQ38" s="3">
         <v>38074</v>
@@ -7041,14 +7041,14 @@
       </c>
       <c r="AS38" s="3">
         <f t="shared" si="15"/>
-        <v>13529</v>
+        <v>13530</v>
       </c>
       <c r="AT38" s="3">
-        <v>34923</v>
+        <v>34924</v>
       </c>
       <c r="AU38" s="4">
         <f t="shared" si="16"/>
-        <v>0.91724011136208439</v>
+        <v>0.91726637600462257</v>
       </c>
       <c r="AV38" s="5">
         <v>25812</v>
@@ -7058,14 +7058,14 @@
       </c>
       <c r="AX38" s="3">
         <f t="shared" si="17"/>
-        <v>8505</v>
+        <v>8506</v>
       </c>
       <c r="AY38" s="5">
-        <v>22473</v>
+        <v>22474</v>
       </c>
       <c r="AZ38" s="4">
         <f t="shared" si="18"/>
-        <v>0.87064156206415622</v>
+        <v>0.87068030373469707</v>
       </c>
       <c r="BA38" s="10">
         <v>22633</v>
@@ -7328,14 +7328,14 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="0"/>
-        <v>105540</v>
+        <v>105546</v>
       </c>
       <c r="F40" s="5">
-        <v>258587</v>
+        <v>258593</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="1"/>
-        <v>0.94554609311866722</v>
+        <v>0.94556803264601674</v>
       </c>
       <c r="H40" s="5">
         <v>275367</v>
@@ -7345,14 +7345,14 @@
       </c>
       <c r="J40" s="3">
         <f t="shared" si="2"/>
-        <v>98766</v>
+        <v>98771</v>
       </c>
       <c r="K40" s="5">
-        <v>260328</v>
+        <v>260333</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="3"/>
-        <v>0.94538561265511123</v>
+        <v>0.94540377024116906</v>
       </c>
       <c r="M40" s="9">
         <v>339208</v>
@@ -7364,11 +7364,11 @@
         <v>320573</v>
       </c>
       <c r="P40" s="5">
-        <v>321288</v>
+        <v>321295</v>
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="4"/>
-        <v>0.94717105728638473</v>
+        <v>0.94719169359213229</v>
       </c>
       <c r="R40" s="5">
         <v>277547</v>
@@ -7378,14 +7378,14 @@
       </c>
       <c r="T40" s="3">
         <f t="shared" si="5"/>
-        <v>97289</v>
+        <v>97295</v>
       </c>
       <c r="U40" s="5">
-        <v>262663</v>
+        <v>262669</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" si="6"/>
-        <v>0.946373046727221</v>
+        <v>0.94639466468742228</v>
       </c>
       <c r="W40" s="5">
         <v>278758</v>
@@ -7395,14 +7395,14 @@
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="7"/>
-        <v>125337</v>
+        <v>125343</v>
       </c>
       <c r="Z40" s="5">
-        <v>265211</v>
+        <v>265217</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" si="8"/>
-        <v>0.95140229159342515</v>
+        <v>0.95142381563937184</v>
       </c>
       <c r="AB40" s="5">
         <v>343140</v>
@@ -7412,14 +7412,14 @@
       </c>
       <c r="AD40" s="3">
         <f t="shared" si="9"/>
-        <v>142717</v>
+        <v>142724</v>
       </c>
       <c r="AE40" s="5">
-        <v>328413</v>
+        <v>328420</v>
       </c>
       <c r="AF40" s="4">
         <f t="shared" si="10"/>
-        <v>0.95708165763245323</v>
+        <v>0.95710205746925459</v>
       </c>
       <c r="AG40" s="5">
         <v>282101</v>
@@ -7429,14 +7429,14 @@
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="11"/>
-        <v>100008</v>
+        <v>100015</v>
       </c>
       <c r="AJ40" s="5">
-        <v>268704</v>
+        <v>268711</v>
       </c>
       <c r="AK40" s="4">
         <f t="shared" si="12"/>
-        <v>0.952509916661054</v>
+        <v>0.9525347304688746</v>
       </c>
       <c r="AL40" s="5">
         <v>282756</v>
@@ -7446,14 +7446,14 @@
       </c>
       <c r="AN40" s="3">
         <f t="shared" si="13"/>
-        <v>99011</v>
+        <v>99021</v>
       </c>
       <c r="AO40" s="5">
-        <v>270958</v>
+        <v>270968</v>
       </c>
       <c r="AP40" s="4">
         <f t="shared" si="14"/>
-        <v>0.95827497913395299</v>
+        <v>0.95831034531539561</v>
       </c>
       <c r="AQ40" s="3">
         <v>343988</v>
@@ -7463,14 +7463,14 @@
       </c>
       <c r="AS40" s="3">
         <f t="shared" si="15"/>
-        <v>125843</v>
+        <v>125854</v>
       </c>
       <c r="AT40" s="3">
-        <v>332706</v>
+        <v>332717</v>
       </c>
       <c r="AU40" s="4">
         <f t="shared" si="16"/>
-        <v>0.96720234426782326</v>
+        <v>0.96723432212751603</v>
       </c>
       <c r="AV40" s="5">
         <v>285285</v>
@@ -7480,14 +7480,14 @@
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="17"/>
-        <v>94323</v>
+        <v>94335</v>
       </c>
       <c r="AY40" s="5">
-        <v>273369</v>
+        <v>273381</v>
       </c>
       <c r="AZ40" s="4">
         <f t="shared" si="18"/>
-        <v>0.95823124244176872</v>
+        <v>0.95827330564172675</v>
       </c>
       <c r="BA40" s="10">
         <v>276279</v>
@@ -7497,14 +7497,14 @@
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="19"/>
-        <v>95238</v>
+        <v>95249</v>
       </c>
       <c r="BD40" s="5">
-        <v>275422</v>
+        <v>275433</v>
       </c>
       <c r="BE40" s="4">
         <f t="shared" si="20"/>
-        <v>0.99689806318974661</v>
+        <v>0.99693787801461564</v>
       </c>
       <c r="BF40" s="10">
         <v>339189</v>
@@ -7514,14 +7514,14 @@
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="23"/>
-        <v>141245</v>
+        <v>141261</v>
       </c>
       <c r="BI40" s="5">
-        <v>337546</v>
+        <v>337562</v>
       </c>
       <c r="BJ40" s="4">
         <f t="shared" si="24"/>
-        <v>0.99515609291574902</v>
+        <v>0.99520326425680083</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7539,14 +7539,14 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" si="0"/>
-        <v>326646</v>
+        <v>326695</v>
       </c>
       <c r="F41" s="5">
-        <v>832870</v>
+        <v>832919</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="1"/>
-        <v>0.95437096792675524</v>
+        <v>0.95442711615808595</v>
       </c>
       <c r="H41" s="5">
         <v>878008</v>
@@ -7556,14 +7556,14 @@
       </c>
       <c r="J41" s="3">
         <f t="shared" si="2"/>
-        <v>326459</v>
+        <v>326506</v>
       </c>
       <c r="K41" s="5">
-        <v>839583</v>
+        <v>839630</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="3"/>
-        <v>0.9562361618572951</v>
+        <v>0.95628969212125625</v>
       </c>
       <c r="M41" s="9">
         <v>999035</v>
@@ -7575,11 +7575,11 @@
         <v>948683</v>
       </c>
       <c r="P41" s="5">
-        <v>950931</v>
+        <v>950989</v>
       </c>
       <c r="Q41" s="4">
         <f t="shared" si="4"/>
-        <v>0.95184953480108303</v>
+        <v>0.95190759082514631</v>
       </c>
       <c r="R41" s="5">
         <v>889467</v>
@@ -7589,14 +7589,14 @@
       </c>
       <c r="T41" s="3">
         <f t="shared" si="5"/>
-        <v>328332</v>
+        <v>328387</v>
       </c>
       <c r="U41" s="5">
-        <v>849316</v>
+        <v>849371</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" si="6"/>
-        <v>0.95485948326357251</v>
+        <v>0.95492131804777469</v>
       </c>
       <c r="W41" s="5">
         <v>894020</v>
@@ -7606,14 +7606,14 @@
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="7"/>
-        <v>361274</v>
+        <v>361324</v>
       </c>
       <c r="Z41" s="5">
-        <v>855212</v>
+        <v>855262</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" si="8"/>
-        <v>0.95659157513254733</v>
+        <v>0.95664750229301354</v>
       </c>
       <c r="AB41" s="5">
         <v>1012178</v>
@@ -7623,14 +7623,14 @@
       </c>
       <c r="AD41" s="3">
         <f t="shared" si="9"/>
-        <v>420658</v>
+        <v>420698</v>
       </c>
       <c r="AE41" s="5">
-        <v>977708</v>
+        <v>977748</v>
       </c>
       <c r="AF41" s="4">
         <f t="shared" si="10"/>
-        <v>0.96594472513727825</v>
+        <v>0.96598424387805304</v>
       </c>
       <c r="AG41" s="5">
         <v>904846</v>
@@ -7640,14 +7640,14 @@
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="11"/>
-        <v>322065</v>
+        <v>322106</v>
       </c>
       <c r="AJ41" s="5">
-        <v>873121</v>
+        <v>873162</v>
       </c>
       <c r="AK41" s="4">
         <f t="shared" si="12"/>
-        <v>0.96493878516344223</v>
+        <v>0.9649840967413239</v>
       </c>
       <c r="AL41" s="5">
         <v>910192</v>
@@ -7657,14 +7657,14 @@
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="13"/>
-        <v>324114</v>
+        <v>324158</v>
       </c>
       <c r="AO41" s="5">
-        <v>879089</v>
+        <v>879133</v>
       </c>
       <c r="AP41" s="4">
         <f t="shared" si="14"/>
-        <v>0.96582808901858075</v>
+        <v>0.96587643046741789</v>
       </c>
       <c r="AQ41" s="3">
         <v>1025826</v>
@@ -7674,14 +7674,14 @@
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="15"/>
-        <v>359781</v>
+        <v>359834</v>
       </c>
       <c r="AT41" s="3">
-        <v>993359</v>
+        <v>993412</v>
       </c>
       <c r="AU41" s="4">
         <f t="shared" si="16"/>
-        <v>0.96835038300842446</v>
+        <v>0.96840204869051871</v>
       </c>
       <c r="AV41" s="5">
         <v>923071</v>
@@ -7691,14 +7691,14 @@
       </c>
       <c r="AX41" s="3">
         <f t="shared" si="17"/>
-        <v>308136</v>
+        <v>308181</v>
       </c>
       <c r="AY41" s="5">
-        <v>890862</v>
+        <v>890907</v>
       </c>
       <c r="AZ41" s="4">
         <f t="shared" si="18"/>
-        <v>0.96510669276794525</v>
+        <v>0.96515544308075973</v>
       </c>
       <c r="BA41" s="11">
         <v>907892</v>
@@ -7708,14 +7708,14 @@
       </c>
       <c r="BC41" s="3">
         <f t="shared" si="19"/>
-        <v>315602</v>
+        <v>315646</v>
       </c>
       <c r="BD41" s="5">
-        <v>897910</v>
+        <v>897954</v>
       </c>
       <c r="BE41" s="4">
         <f t="shared" si="20"/>
-        <v>0.98900530018989041</v>
+        <v>0.98905376410410051</v>
       </c>
       <c r="BF41" s="11">
         <v>1023930</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="BH41" s="3">
         <f t="shared" si="23"/>
-        <v>403303</v>
+        <v>403359</v>
       </c>
       <c r="BI41" s="5">
-        <v>1012210</v>
+        <v>1012266</v>
       </c>
       <c r="BJ41" s="4">
         <f t="shared" si="24"/>
-        <v>0.98855390505210317</v>
+        <v>0.98860859629076203</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7786,11 +7786,11 @@
         <v>19316</v>
       </c>
       <c r="P42" s="5">
-        <v>19354</v>
+        <v>19355</v>
       </c>
       <c r="Q42" s="4">
         <f t="shared" si="4"/>
-        <v>0.94557357826851673</v>
+        <v>0.94562243502051979</v>
       </c>
       <c r="R42" s="5">
         <v>18235</v>
@@ -7800,14 +7800,14 @@
       </c>
       <c r="T42" s="3">
         <f t="shared" si="5"/>
-        <v>7832</v>
+        <v>7833</v>
       </c>
       <c r="U42" s="5">
-        <v>17341</v>
+        <v>17342</v>
       </c>
       <c r="V42" s="4">
         <f t="shared" si="6"/>
-        <v>0.9509734027968193</v>
+        <v>0.95102824239100636</v>
       </c>
       <c r="W42" s="5">
         <v>18317</v>
@@ -7817,14 +7817,14 @@
       </c>
       <c r="Y42" s="3">
         <f t="shared" si="7"/>
-        <v>8478</v>
+        <v>8479</v>
       </c>
       <c r="Z42" s="5">
-        <v>17393</v>
+        <v>17394</v>
       </c>
       <c r="AA42" s="4">
         <f t="shared" si="8"/>
-        <v>0.94955505814270891</v>
+        <v>0.9496096522356281</v>
       </c>
       <c r="AB42" s="5">
         <v>20712</v>
@@ -7834,14 +7834,14 @@
       </c>
       <c r="AD42" s="3">
         <f t="shared" si="9"/>
-        <v>9565</v>
+        <v>9566</v>
       </c>
       <c r="AE42" s="5">
-        <v>19842</v>
+        <v>19843</v>
       </c>
       <c r="AF42" s="4">
         <f t="shared" si="10"/>
-        <v>0.95799536500579374</v>
+        <v>0.95804364619544224</v>
       </c>
       <c r="AG42" s="5">
         <v>18585</v>
@@ -7851,14 +7851,14 @@
       </c>
       <c r="AI42" s="3">
         <f t="shared" si="11"/>
-        <v>7691</v>
+        <v>7692</v>
       </c>
       <c r="AJ42" s="5">
-        <v>17753</v>
+        <v>17754</v>
       </c>
       <c r="AK42" s="4">
         <f t="shared" si="12"/>
-        <v>0.95523271455474845</v>
+        <v>0.95528652138821635</v>
       </c>
       <c r="AL42" s="5">
         <v>18498</v>
@@ -7868,14 +7868,14 @@
       </c>
       <c r="AN42" s="3">
         <f t="shared" si="13"/>
-        <v>7818</v>
+        <v>7819</v>
       </c>
       <c r="AO42" s="5">
-        <v>17814</v>
+        <v>17815</v>
       </c>
       <c r="AP42" s="4">
         <f t="shared" si="14"/>
-        <v>0.96302302951670449</v>
+        <v>0.96307708941507186</v>
       </c>
       <c r="AQ42" s="3">
         <v>20775</v>
@@ -7885,14 +7885,14 @@
       </c>
       <c r="AS42" s="3">
         <f t="shared" si="15"/>
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="AT42" s="3">
-        <v>20049</v>
+        <v>20050</v>
       </c>
       <c r="AU42" s="4">
         <f t="shared" si="16"/>
-        <v>0.96505415162454877</v>
+        <v>0.96510228640192541</v>
       </c>
       <c r="AV42" s="5">
         <v>18672</v>
@@ -7902,14 +7902,14 @@
       </c>
       <c r="AX42" s="3">
         <f t="shared" si="17"/>
-        <v>7435</v>
+        <v>7436</v>
       </c>
       <c r="AY42" s="5">
-        <v>17992</v>
+        <v>17993</v>
       </c>
       <c r="AZ42" s="4">
         <f t="shared" si="18"/>
-        <v>0.9635818337617823</v>
+        <v>0.96363538988860331</v>
       </c>
       <c r="BA42" s="10">
         <v>18422</v>
@@ -7919,14 +7919,14 @@
       </c>
       <c r="BC42" s="3">
         <f t="shared" si="19"/>
-        <v>7560</v>
+        <v>7561</v>
       </c>
       <c r="BD42" s="5">
-        <v>18114</v>
+        <v>18115</v>
       </c>
       <c r="BE42" s="4">
         <f t="shared" si="20"/>
-        <v>0.98328085984149383</v>
+        <v>0.9833351427640864</v>
       </c>
       <c r="BF42" s="10">
         <v>20562</v>
@@ -7936,14 +7936,14 @@
       </c>
       <c r="BH42" s="3">
         <f t="shared" si="23"/>
-        <v>9478</v>
+        <v>9479</v>
       </c>
       <c r="BI42" s="5">
-        <v>20430</v>
+        <v>20431</v>
       </c>
       <c r="BJ42" s="4">
         <f t="shared" si="24"/>
-        <v>0.99358039101254747</v>
+        <v>0.9936290244139675</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8172,14 +8172,14 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="0"/>
-        <v>151681</v>
+        <v>151687</v>
       </c>
       <c r="F44" s="5">
-        <v>296313</v>
+        <v>296319</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="1"/>
-        <v>0.87113218696622341</v>
+        <v>0.87114982639858651</v>
       </c>
       <c r="H44" s="5">
         <v>343940</v>
@@ -8189,14 +8189,14 @@
       </c>
       <c r="J44" s="3">
         <f t="shared" si="2"/>
-        <v>148668</v>
+        <v>148673</v>
       </c>
       <c r="K44" s="5">
-        <v>299518</v>
+        <v>299523</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" si="3"/>
-        <v>0.87084375181717744</v>
+        <v>0.87085828923649478</v>
       </c>
       <c r="M44" s="9">
         <v>415294</v>
@@ -8208,11 +8208,11 @@
         <v>362232</v>
       </c>
       <c r="P44" s="5">
-        <v>363086</v>
+        <v>363093</v>
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="4"/>
-        <v>0.87428664993956084</v>
+        <v>0.87430350546841518</v>
       </c>
       <c r="R44" s="5">
         <v>349377</v>
@@ -8222,14 +8222,14 @@
       </c>
       <c r="T44" s="3">
         <f t="shared" si="5"/>
-        <v>152712</v>
+        <v>152718</v>
       </c>
       <c r="U44" s="5">
-        <v>304251</v>
+        <v>304257</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" si="6"/>
-        <v>0.87083866425093814</v>
+        <v>0.87085583767677899</v>
       </c>
       <c r="W44" s="5">
         <v>352323</v>
@@ -8239,14 +8239,14 @@
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="7"/>
-        <v>164132</v>
+        <v>164138</v>
       </c>
       <c r="Z44" s="5">
-        <v>307792</v>
+        <v>307798</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="8"/>
-        <v>0.87360745679390783</v>
+        <v>0.87362448662165115</v>
       </c>
       <c r="AB44" s="5">
         <v>424236</v>
@@ -8256,14 +8256,14 @@
       </c>
       <c r="AD44" s="3">
         <f t="shared" si="9"/>
-        <v>208452</v>
+        <v>208460</v>
       </c>
       <c r="AE44" s="5">
-        <v>382938</v>
+        <v>382946</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="10"/>
-        <v>0.90265324017763693</v>
+        <v>0.90267209760604949</v>
       </c>
       <c r="AG44" s="5">
         <v>358309</v>
@@ -8273,14 +8273,14 @@
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="11"/>
-        <v>154192</v>
+        <v>154197</v>
       </c>
       <c r="AJ44" s="5">
-        <v>319711</v>
+        <v>319716</v>
       </c>
       <c r="AK44" s="4">
         <f t="shared" si="12"/>
-        <v>0.89227733604235449</v>
+        <v>0.89229129047833011</v>
       </c>
       <c r="AL44" s="5">
         <v>359722</v>
@@ -8290,14 +8290,14 @@
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="13"/>
-        <v>150205</v>
+        <v>150211</v>
       </c>
       <c r="AO44" s="5">
-        <v>323546</v>
+        <v>323552</v>
       </c>
       <c r="AP44" s="4">
         <f t="shared" si="14"/>
-        <v>0.89943345138746034</v>
+        <v>0.89945013093444381</v>
       </c>
       <c r="AQ44" s="3">
         <v>432157</v>
@@ -8307,14 +8307,14 @@
       </c>
       <c r="AS44" s="3">
         <f t="shared" si="15"/>
-        <v>178587</v>
+        <v>178594</v>
       </c>
       <c r="AT44" s="3">
-        <v>391654</v>
+        <v>391661</v>
       </c>
       <c r="AU44" s="4">
         <f t="shared" si="16"/>
-        <v>0.90627711688113344</v>
+        <v>0.90629331469813057</v>
       </c>
       <c r="AV44" s="5">
         <v>367733</v>
@@ -8324,14 +8324,14 @@
       </c>
       <c r="AX44" s="3">
         <f t="shared" si="17"/>
-        <v>145682</v>
+        <v>145689</v>
       </c>
       <c r="AY44" s="5">
-        <v>327652</v>
+        <v>327659</v>
       </c>
       <c r="AZ44" s="4">
         <f t="shared" si="18"/>
-        <v>0.89100515863411767</v>
+        <v>0.89102419418436751</v>
       </c>
       <c r="BA44" s="10">
         <v>337773</v>
@@ -8341,14 +8341,14 @@
       </c>
       <c r="BC44" s="3">
         <f t="shared" si="19"/>
-        <v>150745</v>
+        <v>150752</v>
       </c>
       <c r="BD44" s="5">
-        <v>331413</v>
+        <v>331420</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="20"/>
-        <v>0.98117078629730614</v>
+        <v>0.9811915102746519</v>
       </c>
       <c r="BF44" s="10">
         <v>408499</v>
@@ -8358,14 +8358,14 @@
       </c>
       <c r="BH44" s="3">
         <f t="shared" si="23"/>
-        <v>201472</v>
+        <v>201483</v>
       </c>
       <c r="BI44" s="5">
-        <v>400206</v>
+        <v>400217</v>
       </c>
       <c r="BJ44" s="4">
         <f t="shared" si="24"/>
-        <v>0.97969884871199198</v>
+        <v>0.97972577656248849</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8383,14 +8383,14 @@
       </c>
       <c r="E45" s="3">
         <f t="shared" si="0"/>
-        <v>112346</v>
+        <v>112351</v>
       </c>
       <c r="F45" s="5">
-        <v>232570</v>
+        <v>232575</v>
       </c>
       <c r="G45" s="4">
         <f t="shared" si="1"/>
-        <v>0.92964040739970899</v>
+        <v>0.92966039364916941</v>
       </c>
       <c r="H45" s="5">
         <v>249985</v>
@@ -8400,14 +8400,14 @@
       </c>
       <c r="J45" s="3">
         <f t="shared" si="2"/>
-        <v>104743</v>
+        <v>104747</v>
       </c>
       <c r="K45" s="5">
-        <v>234321</v>
+        <v>234325</v>
       </c>
       <c r="L45" s="4">
         <f t="shared" si="3"/>
-        <v>0.93734024041442487</v>
+        <v>0.93735624137448248</v>
       </c>
       <c r="M45" s="9">
         <v>300587</v>
@@ -8419,11 +8419,11 @@
         <v>284476</v>
       </c>
       <c r="P45" s="5">
-        <v>285004</v>
+        <v>285014</v>
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="4"/>
-        <v>0.94815810397655254</v>
+        <v>0.94819137221503258</v>
       </c>
       <c r="R45" s="5">
         <v>247712</v>
@@ -8433,14 +8433,14 @@
       </c>
       <c r="T45" s="3">
         <f t="shared" si="5"/>
-        <v>109586</v>
+        <v>109592</v>
       </c>
       <c r="U45" s="5">
-        <v>235845</v>
+        <v>235851</v>
       </c>
       <c r="V45" s="4">
         <f t="shared" si="6"/>
-        <v>0.95209356026353187</v>
+        <v>0.95211778194031782</v>
       </c>
       <c r="W45" s="5">
         <v>250023</v>
@@ -8450,14 +8450,14 @@
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="7"/>
-        <v>116266</v>
+        <v>116272</v>
       </c>
       <c r="Z45" s="5">
-        <v>237768</v>
+        <v>237774</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="8"/>
-        <v>0.95098450942513291</v>
+        <v>0.95100850721733599</v>
       </c>
       <c r="AB45" s="5">
         <v>306096</v>
@@ -8467,14 +8467,14 @@
       </c>
       <c r="AD45" s="3">
         <f t="shared" si="9"/>
-        <v>151885</v>
+        <v>151896</v>
       </c>
       <c r="AE45" s="5">
-        <v>293851</v>
+        <v>293862</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="10"/>
-        <v>0.95999621033923999</v>
+        <v>0.96003214677748161</v>
       </c>
       <c r="AG45" s="5">
         <v>252706</v>
@@ -8484,14 +8484,14 @@
       </c>
       <c r="AI45" s="3">
         <f t="shared" si="11"/>
-        <v>106713</v>
+        <v>106720</v>
       </c>
       <c r="AJ45" s="5">
-        <v>243703</v>
+        <v>243710</v>
       </c>
       <c r="AK45" s="4">
         <f t="shared" si="12"/>
-        <v>0.96437361993779336</v>
+        <v>0.96440132011111723</v>
       </c>
       <c r="AL45" s="5">
         <v>254538</v>
@@ -8501,14 +8501,14 @@
       </c>
       <c r="AN45" s="3">
         <f t="shared" si="13"/>
-        <v>96689</v>
+        <v>96696</v>
       </c>
       <c r="AO45" s="5">
-        <v>246016</v>
+        <v>246023</v>
       </c>
       <c r="AP45" s="4">
         <f t="shared" si="14"/>
-        <v>0.96651973379220391</v>
+        <v>0.96654723459758463</v>
       </c>
       <c r="AQ45" s="3">
         <v>310997</v>
@@ -8518,14 +8518,14 @@
       </c>
       <c r="AS45" s="3">
         <f t="shared" si="15"/>
-        <v>122770</v>
+        <v>122782</v>
       </c>
       <c r="AT45" s="3">
-        <v>299897</v>
+        <v>299909</v>
       </c>
       <c r="AU45" s="4">
         <f t="shared" si="16"/>
-        <v>0.9643083373794602</v>
+        <v>0.96434692296067159</v>
       </c>
       <c r="AV45" s="5">
         <v>259359</v>
@@ -8535,14 +8535,14 @@
       </c>
       <c r="AX45" s="3">
         <f t="shared" si="17"/>
-        <v>98669</v>
+        <v>98677</v>
       </c>
       <c r="AY45" s="5">
-        <v>248511</v>
+        <v>248519</v>
       </c>
       <c r="AZ45" s="4">
         <f t="shared" si="18"/>
-        <v>0.95817380542028618</v>
+        <v>0.95820465069652494</v>
       </c>
       <c r="BA45" s="10">
         <v>254394</v>
@@ -8552,14 +8552,14 @@
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="19"/>
-        <v>102910</v>
+        <v>102917</v>
       </c>
       <c r="BD45" s="5">
-        <v>250478</v>
+        <v>250485</v>
       </c>
       <c r="BE45" s="4">
         <f t="shared" si="20"/>
-        <v>0.98460655518605</v>
+        <v>0.98463407155829152</v>
       </c>
       <c r="BF45" s="10">
         <v>309142</v>
@@ -8569,14 +8569,14 @@
       </c>
       <c r="BH45" s="3">
         <f t="shared" si="23"/>
-        <v>148064</v>
+        <v>148075</v>
       </c>
       <c r="BI45" s="5">
-        <v>304817</v>
+        <v>304828</v>
       </c>
       <c r="BJ45" s="4">
         <f t="shared" si="24"/>
-        <v>0.98600966546117963</v>
+        <v>0.98604524781491998</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8678,14 +8678,14 @@
       </c>
       <c r="AD46" s="3">
         <f t="shared" si="9"/>
-        <v>4052</v>
+        <v>4053</v>
       </c>
       <c r="AE46" s="5">
-        <v>6172</v>
+        <v>6173</v>
       </c>
       <c r="AF46" s="4">
         <f t="shared" si="10"/>
-        <v>1.0057031122698388</v>
+        <v>1.0058660583346912</v>
       </c>
       <c r="AG46" s="5">
         <v>2383</v>
@@ -8780,14 +8780,14 @@
       </c>
       <c r="BH46" s="3">
         <f t="shared" si="23"/>
-        <v>4302</v>
+        <v>4303</v>
       </c>
       <c r="BI46" s="5">
-        <v>6603</v>
+        <v>6604</v>
       </c>
       <c r="BJ46" s="4">
         <f t="shared" si="24"/>
-        <v>1.0349529780564264</v>
+        <v>1.0351097178683386</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9016,15 +9016,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>2891686</v>
+        <v>2891868</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>6970200</v>
+        <v>6970382</v>
       </c>
       <c r="G48" s="6">
         <f>F48/C48</f>
-        <v>0.9423515091995609</v>
+        <v>0.94237611508958907</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -9036,15 +9036,15 @@
       </c>
       <c r="J48" s="8">
         <f t="shared" ref="J48" si="25">K48-I48</f>
-        <v>2779456</v>
+        <v>2779640</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>7078004</v>
+        <v>7078188</v>
       </c>
       <c r="L48" s="6">
         <f t="shared" ref="L48" si="26">K48/H48</f>
-        <v>0.94429036845714409</v>
+        <v>0.94431491625731434</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -9056,15 +9056,15 @@
       </c>
       <c r="O48" s="7">
         <f t="shared" ref="O48" si="27">P48-N48</f>
-        <v>4722757</v>
+        <v>4723053</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>11175808</v>
+        <v>11176104</v>
       </c>
       <c r="Q48" s="6">
         <f t="shared" ref="Q48" si="28">P48/M48</f>
-        <v>0.94380664805651115</v>
+        <v>0.94383164551242882</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -9076,15 +9076,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>2871118</v>
+        <v>2871327</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>7104173</v>
+        <v>7104382</v>
       </c>
       <c r="V48" s="6">
         <f>U48/R48</f>
-        <v>0.94177071649587107</v>
+        <v>0.94179842275805636</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -9096,15 +9096,15 @@
       </c>
       <c r="Y48" s="8">
         <f t="shared" ref="Y48" si="29">Z48-X48</f>
-        <v>3037493</v>
+        <v>3037697</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>7205068</v>
+        <v>7205272</v>
       </c>
       <c r="AA48" s="6">
         <f t="shared" ref="AA48" si="30">Z48/W48</f>
-        <v>0.9441745829814826</v>
+        <v>0.9442013157777488</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -9116,15 +9116,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>5142845</v>
+        <v>5143089</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>11573656</v>
+        <v>11573900</v>
       </c>
       <c r="AF48" s="6">
         <f>AE48/AB48</f>
-        <v>0.96123341856290423</v>
+        <v>0.96125368363334773</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -9136,15 +9136,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>2802215</v>
+        <v>2802395</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7355959</v>
+        <v>7356139</v>
       </c>
       <c r="AK48" s="6">
         <f>AJ48/AG48</f>
-        <v>0.95450541784758602</v>
+        <v>0.95452877455406204</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -9156,15 +9156,15 @@
       </c>
       <c r="AN48" s="8">
         <f t="shared" ref="AN48" si="31">AO48-AM48</f>
-        <v>2784400</v>
+        <v>2784588</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>7459536</v>
+        <v>7459724</v>
       </c>
       <c r="AP48" s="6">
         <f t="shared" ref="AP48" si="32">AO48/AL48</f>
-        <v>0.95644531017104384</v>
+        <v>0.95646941511782768</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -9176,15 +9176,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>4439709</v>
+        <v>4439999</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>11780655</v>
+        <v>11780945</v>
       </c>
       <c r="AU48" s="6">
         <f>AT48/AQ48</f>
-        <v>0.96323902101436842</v>
+        <v>0.96326273271088225</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -9196,15 +9196,15 @@
       </c>
       <c r="AX48" s="8">
         <f t="shared" ref="AX48" si="33">AY48-AW48</f>
-        <v>2608064</v>
+        <v>2608272</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>7516830</v>
+        <v>7517038</v>
       </c>
       <c r="AZ48" s="6">
         <f t="shared" ref="AZ48" si="34">AY48/AV48</f>
-        <v>0.94120509281478781</v>
+        <v>0.94123113712592765</v>
       </c>
       <c r="BA48" s="7">
         <f>SUM(BA10:BA47)</f>
@@ -9216,15 +9216,15 @@
       </c>
       <c r="BC48" s="8">
         <f t="shared" ref="BC48" si="35">BD48-BB48</f>
-        <v>2771325</v>
+        <v>2771531</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>7629694</v>
+        <v>7629900</v>
       </c>
       <c r="BE48" s="6">
         <f t="shared" ref="BE48" si="36">BD48/BA48</f>
-        <v>0.98811648379087247</v>
+        <v>0.98814316271084768</v>
       </c>
       <c r="BF48" s="7">
         <f>SUM(BF10:BF47)</f>
@@ -9236,15 +9236,15 @@
       </c>
       <c r="BH48" s="8">
         <f>BI48-BG48</f>
-        <v>5013310</v>
+        <v>5013702</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>12005691</v>
+        <v>12006083</v>
       </c>
       <c r="BJ48" s="6">
         <f>BI48/BF48</f>
-        <v>0.99488523347961988</v>
+        <v>0.99491771765829184</v>
       </c>
     </row>
   </sheetData>

--- a/gstdatabase/GSTR-1-2022-2023.xlsx
+++ b/gstdatabase/GSTR-1-2022-2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DD1C8E-6DDE-4076-AA9A-3787F9261610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CA6A26-24CC-4ABA-B380-BC6D0B0A75CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -182,10 +182,10 @@
     <t>Gujarat</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -365,9 +365,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -385,6 +382,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -701,10 +701,10 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="22"/>
+      <c r="B3" s="21"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -731,100 +731,100 @@
       <c r="BF5" s="12"/>
     </row>
     <row r="8" spans="1:62" s="13" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="18">
         <v>44652</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="19">
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="18">
         <v>44682</v>
       </c>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="19">
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="18">
         <v>44713</v>
       </c>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="19">
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="18">
         <v>44743</v>
       </c>
-      <c r="S8" s="20"/>
-      <c r="T8" s="20"/>
-      <c r="U8" s="20"/>
-      <c r="V8" s="21"/>
-      <c r="W8" s="19">
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="18">
         <v>44774</v>
       </c>
-      <c r="X8" s="20"/>
-      <c r="Y8" s="20"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="21"/>
-      <c r="AB8" s="19">
+      <c r="X8" s="19"/>
+      <c r="Y8" s="19"/>
+      <c r="Z8" s="19"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="18">
         <v>44805</v>
       </c>
-      <c r="AC8" s="20"/>
-      <c r="AD8" s="20"/>
-      <c r="AE8" s="20"/>
-      <c r="AF8" s="21"/>
-      <c r="AG8" s="19">
+      <c r="AC8" s="19"/>
+      <c r="AD8" s="19"/>
+      <c r="AE8" s="19"/>
+      <c r="AF8" s="20"/>
+      <c r="AG8" s="18">
         <v>44835</v>
       </c>
-      <c r="AH8" s="20"/>
-      <c r="AI8" s="20"/>
-      <c r="AJ8" s="20"/>
-      <c r="AK8" s="21"/>
-      <c r="AL8" s="19">
+      <c r="AH8" s="19"/>
+      <c r="AI8" s="19"/>
+      <c r="AJ8" s="19"/>
+      <c r="AK8" s="20"/>
+      <c r="AL8" s="18">
         <v>44866</v>
       </c>
-      <c r="AM8" s="20"/>
-      <c r="AN8" s="20"/>
-      <c r="AO8" s="20"/>
-      <c r="AP8" s="21"/>
-      <c r="AQ8" s="19">
+      <c r="AM8" s="19"/>
+      <c r="AN8" s="19"/>
+      <c r="AO8" s="19"/>
+      <c r="AP8" s="20"/>
+      <c r="AQ8" s="18">
         <v>44896</v>
       </c>
-      <c r="AR8" s="20"/>
-      <c r="AS8" s="20"/>
-      <c r="AT8" s="20"/>
-      <c r="AU8" s="21"/>
-      <c r="AV8" s="19">
+      <c r="AR8" s="19"/>
+      <c r="AS8" s="19"/>
+      <c r="AT8" s="19"/>
+      <c r="AU8" s="20"/>
+      <c r="AV8" s="18">
         <v>44927</v>
       </c>
-      <c r="AW8" s="20"/>
-      <c r="AX8" s="20"/>
-      <c r="AY8" s="20"/>
-      <c r="AZ8" s="21"/>
-      <c r="BA8" s="19">
+      <c r="AW8" s="19"/>
+      <c r="AX8" s="19"/>
+      <c r="AY8" s="19"/>
+      <c r="AZ8" s="20"/>
+      <c r="BA8" s="18">
         <v>44958</v>
       </c>
-      <c r="BB8" s="20"/>
-      <c r="BC8" s="20"/>
-      <c r="BD8" s="20"/>
-      <c r="BE8" s="21"/>
-      <c r="BF8" s="19">
+      <c r="BB8" s="19"/>
+      <c r="BC8" s="19"/>
+      <c r="BD8" s="19"/>
+      <c r="BE8" s="20"/>
+      <c r="BF8" s="18">
         <v>44986</v>
       </c>
-      <c r="BG8" s="20"/>
-      <c r="BH8" s="20"/>
-      <c r="BI8" s="20"/>
-      <c r="BJ8" s="21"/>
+      <c r="BG8" s="19"/>
+      <c r="BH8" s="19"/>
+      <c r="BI8" s="19"/>
+      <c r="BJ8" s="20"/>
     </row>
     <row r="9" spans="1:62" s="13" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
-      <c r="B9" s="24"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="23"/>
       <c r="C9" s="14" t="s">
         <v>3</v>
       </c>
@@ -1268,11 +1268,11 @@
         <v>95308</v>
       </c>
       <c r="P11" s="5">
-        <v>95538</v>
+        <v>95539</v>
       </c>
       <c r="Q11" s="4">
         <f t="shared" ref="Q11:Q47" si="4">P11/M11</f>
-        <v>0.96536184144049475</v>
+        <v>0.96537194592082132</v>
       </c>
       <c r="R11" s="5">
         <v>44504</v>
@@ -1316,14 +1316,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD47" si="9">AE11-AC11</f>
-        <v>49059</v>
+        <v>49060</v>
       </c>
       <c r="AE11" s="5">
-        <v>97565</v>
+        <v>97566</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF47" si="10">AE11/AB11</f>
-        <v>0.97674395322761498</v>
+        <v>0.97675396444017304</v>
       </c>
       <c r="AG11" s="5">
         <v>44744</v>
@@ -1367,14 +1367,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS47" si="15">AT11-AR11</f>
-        <v>43286</v>
+        <v>43287</v>
       </c>
       <c r="AT11" s="3">
-        <v>98529</v>
+        <v>98530</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU47" si="16">AT11/AQ11</f>
-        <v>0.97777094146017129</v>
+        <v>0.97778086514701945</v>
       </c>
       <c r="AV11" s="5">
         <v>46153</v>
@@ -1479,11 +1479,11 @@
         <v>324491</v>
       </c>
       <c r="P12" s="5">
-        <v>324809</v>
+        <v>324810</v>
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="4"/>
-        <v>0.94848868006622888</v>
+        <v>0.94849160020908219</v>
       </c>
       <c r="R12" s="5">
         <v>167538</v>
@@ -1527,14 +1527,14 @@
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="9"/>
-        <v>94417</v>
+        <v>94418</v>
       </c>
       <c r="AE12" s="5">
-        <v>332062</v>
+        <v>332063</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="10"/>
-        <v>0.95695928206872105</v>
+        <v>0.95696216393801681</v>
       </c>
       <c r="AG12" s="5">
         <v>170493</v>
@@ -1865,14 +1865,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>34890</v>
+        <v>34891</v>
       </c>
       <c r="F14" s="5">
-        <v>77291</v>
+        <v>77292</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>0.9334661835748792</v>
+        <v>0.9334782608695652</v>
       </c>
       <c r="H14" s="5">
         <v>84757</v>
@@ -1882,14 +1882,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>34523</v>
+        <v>34525</v>
       </c>
       <c r="K14" s="5">
-        <v>79134</v>
+        <v>79136</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.93365739702915396</v>
+        <v>0.93368099390020887</v>
       </c>
       <c r="M14" s="9">
         <v>154914</v>
@@ -1901,11 +1901,11 @@
         <v>144482</v>
       </c>
       <c r="P14" s="5">
-        <v>145045</v>
+        <v>145048</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="4"/>
-        <v>0.93629368552874503</v>
+        <v>0.93631305111223007</v>
       </c>
       <c r="R14" s="5">
         <v>85475</v>
@@ -1915,14 +1915,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="5"/>
-        <v>36055</v>
+        <v>36056</v>
       </c>
       <c r="U14" s="5">
-        <v>78724</v>
+        <v>78725</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="6"/>
-        <v>0.92101784147411525</v>
+        <v>0.92102954080140387</v>
       </c>
       <c r="W14" s="5">
         <v>86445</v>
@@ -1932,14 +1932,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="7"/>
-        <v>36736</v>
+        <v>36738</v>
       </c>
       <c r="Z14" s="5">
-        <v>80015</v>
+        <v>80017</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="8"/>
-        <v>0.92561744461796513</v>
+        <v>0.92564058071606226</v>
       </c>
       <c r="AB14" s="5">
         <v>156524</v>
@@ -1949,14 +1949,14 @@
       </c>
       <c r="AD14" s="3">
         <f t="shared" si="9"/>
-        <v>77498</v>
+        <v>77501</v>
       </c>
       <c r="AE14" s="5">
-        <v>149298</v>
+        <v>149301</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="10"/>
-        <v>0.95383455572308395</v>
+        <v>0.95385372211290287</v>
       </c>
       <c r="AG14" s="5">
         <v>86459</v>
@@ -1966,14 +1966,14 @@
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="11"/>
-        <v>34526</v>
+        <v>34528</v>
       </c>
       <c r="AJ14" s="5">
-        <v>81194</v>
+        <v>81196</v>
       </c>
       <c r="AK14" s="4">
         <f t="shared" si="12"/>
-        <v>0.93910408401670153</v>
+        <v>0.93912721636845209</v>
       </c>
       <c r="AL14" s="5">
         <v>87786</v>
@@ -1983,14 +1983,14 @@
       </c>
       <c r="AN14" s="3">
         <f t="shared" si="13"/>
-        <v>34698</v>
+        <v>34700</v>
       </c>
       <c r="AO14" s="5">
-        <v>82761</v>
+        <v>82763</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="14"/>
-        <v>0.94275852641651292</v>
+        <v>0.94278130909256597</v>
       </c>
       <c r="AQ14" s="3">
         <v>158597</v>
@@ -2000,14 +2000,14 @@
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="15"/>
-        <v>69820</v>
+        <v>69823</v>
       </c>
       <c r="AT14" s="3">
-        <v>151813</v>
+        <v>151816</v>
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="16"/>
-        <v>0.95722491598201731</v>
+        <v>0.95724383185053941</v>
       </c>
       <c r="AV14" s="5">
         <v>90863</v>
@@ -2017,14 +2017,14 @@
       </c>
       <c r="AX14" s="3">
         <f t="shared" si="17"/>
-        <v>32101</v>
+        <v>32103</v>
       </c>
       <c r="AY14" s="5">
-        <v>83342</v>
+        <v>83344</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="18"/>
-        <v>0.91722703410629192</v>
+        <v>0.91724904526594986</v>
       </c>
       <c r="BA14" s="10">
         <v>86219</v>
@@ -2034,14 +2034,14 @@
       </c>
       <c r="BC14" s="3">
         <f t="shared" si="19"/>
-        <v>35287</v>
+        <v>35289</v>
       </c>
       <c r="BD14" s="5">
-        <v>85165</v>
+        <v>85167</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="20"/>
-        <v>0.98777531634558513</v>
+        <v>0.98779851308876232</v>
       </c>
       <c r="BF14" s="10">
         <v>155639</v>
@@ -2051,14 +2051,14 @@
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="21"/>
-        <v>76837</v>
+        <v>76840</v>
       </c>
       <c r="BI14" s="5">
-        <v>155149</v>
+        <v>155152</v>
       </c>
       <c r="BJ14" s="4">
         <f t="shared" si="22"/>
-        <v>0.99685168884405584</v>
+        <v>0.99687096421847998</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2287,14 +2287,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>106337</v>
+        <v>106339</v>
       </c>
       <c r="F16" s="5">
-        <v>390221</v>
+        <v>390223</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.95110436236539742</v>
+        <v>0.95110923706133832</v>
       </c>
       <c r="H16" s="5">
         <v>416018</v>
@@ -2304,14 +2304,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>103643</v>
+        <v>103645</v>
       </c>
       <c r="K16" s="5">
-        <v>398184</v>
+        <v>398186</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.95713166257229254</v>
+        <v>0.95713647005658409</v>
       </c>
       <c r="M16" s="9">
         <v>750813</v>
@@ -2323,11 +2323,11 @@
         <v>716590</v>
       </c>
       <c r="P16" s="5">
-        <v>718005</v>
+        <v>718010</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="4"/>
-        <v>0.95630336715000941</v>
+        <v>0.95631002659783459</v>
       </c>
       <c r="R16" s="5">
         <v>419109</v>
@@ -2337,14 +2337,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="5"/>
-        <v>111548</v>
+        <v>111550</v>
       </c>
       <c r="U16" s="5">
-        <v>399091</v>
+        <v>399093</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="6"/>
-        <v>0.95223676895509279</v>
+        <v>0.95224154098337188</v>
       </c>
       <c r="W16" s="5">
         <v>423539</v>
@@ -2354,14 +2354,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="7"/>
-        <v>110434</v>
+        <v>110436</v>
       </c>
       <c r="Z16" s="5">
-        <v>405274</v>
+        <v>405276</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="8"/>
-        <v>0.95687528185125814</v>
+        <v>0.95688000396657691</v>
       </c>
       <c r="AB16" s="5">
         <v>762171</v>
@@ -2371,14 +2371,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="9"/>
-        <v>204088</v>
+        <v>204093</v>
       </c>
       <c r="AE16" s="5">
-        <v>732822</v>
+        <v>732827</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="10"/>
-        <v>0.96149289332708798</v>
+        <v>0.96149945353470545</v>
       </c>
       <c r="AG16" s="5">
         <v>429452</v>
@@ -2388,14 +2388,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="11"/>
-        <v>106273</v>
+        <v>106277</v>
       </c>
       <c r="AJ16" s="5">
-        <v>410498</v>
+        <v>410502</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="12"/>
-        <v>0.95586468336391495</v>
+        <v>0.95587399755968072</v>
       </c>
       <c r="AL16" s="5">
         <v>434676</v>
@@ -2405,14 +2405,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="13"/>
-        <v>110265</v>
+        <v>110269</v>
       </c>
       <c r="AO16" s="5">
-        <v>416376</v>
+        <v>416380</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="14"/>
-        <v>0.95789967700080059</v>
+        <v>0.95790887925719381</v>
       </c>
       <c r="AQ16" s="3">
         <v>772632</v>
@@ -2422,14 +2422,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="15"/>
-        <v>180837</v>
+        <v>180843</v>
       </c>
       <c r="AT16" s="3">
-        <v>743481</v>
+        <v>743487</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="16"/>
-        <v>0.9622705246482155</v>
+        <v>0.96227829031155843</v>
       </c>
       <c r="AV16" s="5">
         <v>448203</v>
@@ -2439,14 +2439,14 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="17"/>
-        <v>98396</v>
+        <v>98402</v>
       </c>
       <c r="AY16" s="5">
-        <v>418475</v>
+        <v>418481</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="18"/>
-        <v>0.93367291160478627</v>
+        <v>0.93368629839603934</v>
       </c>
       <c r="BA16" s="10">
         <v>429555</v>
@@ -2456,14 +2456,14 @@
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="19"/>
-        <v>103418</v>
+        <v>103424</v>
       </c>
       <c r="BD16" s="5">
-        <v>424692</v>
+        <v>424698</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="20"/>
-        <v>0.98867898173691382</v>
+        <v>0.98869294968048327</v>
       </c>
       <c r="BF16" s="10">
         <v>753579</v>
@@ -2473,14 +2473,14 @@
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="21"/>
-        <v>197234</v>
+        <v>197242</v>
       </c>
       <c r="BI16" s="5">
-        <v>753318</v>
+        <v>753326</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="22"/>
-        <v>0.99965365276898643</v>
+        <v>0.99966426877606729</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2498,14 +2498,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>97170</v>
+        <v>97175</v>
       </c>
       <c r="F17" s="5">
-        <v>273148</v>
+        <v>273153</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.96562744148392732</v>
+        <v>0.96564511738566339</v>
       </c>
       <c r="H17" s="5">
         <v>290053</v>
@@ -2515,14 +2515,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>89048</v>
+        <v>89054</v>
       </c>
       <c r="K17" s="5">
-        <v>281339</v>
+        <v>281345</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.96995721471593122</v>
+        <v>0.96997790059058175</v>
       </c>
       <c r="M17" s="9">
         <v>666005</v>
@@ -2534,11 +2534,11 @@
         <v>640256</v>
       </c>
       <c r="P17" s="5">
-        <v>641491</v>
+        <v>641498</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="4"/>
-        <v>0.96319246852501106</v>
+        <v>0.96320297895661444</v>
       </c>
       <c r="R17" s="5">
         <v>287981</v>
@@ -2548,14 +2548,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="5"/>
-        <v>96338</v>
+        <v>96344</v>
       </c>
       <c r="U17" s="5">
-        <v>276610</v>
+        <v>276616</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="6"/>
-        <v>0.96051475618183146</v>
+        <v>0.96053559088967677</v>
       </c>
       <c r="W17" s="5">
         <v>293004</v>
@@ -2565,14 +2565,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="7"/>
-        <v>99046</v>
+        <v>99053</v>
       </c>
       <c r="Z17" s="5">
-        <v>283312</v>
+        <v>283319</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="8"/>
-        <v>0.96692195328391417</v>
+        <v>0.9669458437427475</v>
       </c>
       <c r="AB17" s="5">
         <v>677720</v>
@@ -2582,14 +2582,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="9"/>
-        <v>263381</v>
+        <v>263389</v>
       </c>
       <c r="AE17" s="5">
-        <v>660016</v>
+        <v>660024</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="10"/>
-        <v>0.97387711739361393</v>
+        <v>0.97388892167856933</v>
       </c>
       <c r="AG17" s="5">
         <v>295677</v>
@@ -2599,14 +2599,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="11"/>
-        <v>86959</v>
+        <v>86964</v>
       </c>
       <c r="AJ17" s="5">
-        <v>286410</v>
+        <v>286415</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="12"/>
-        <v>0.96865836706947106</v>
+        <v>0.96867527741420534</v>
       </c>
       <c r="AL17" s="5">
         <v>303084</v>
@@ -2616,14 +2616,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="13"/>
-        <v>89238</v>
+        <v>89243</v>
       </c>
       <c r="AO17" s="5">
-        <v>294595</v>
+        <v>294600</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="14"/>
-        <v>0.97199126314817019</v>
+        <v>0.97200776022488811</v>
       </c>
       <c r="AQ17" s="3">
         <v>690105</v>
@@ -2633,14 +2633,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="15"/>
-        <v>218594</v>
+        <v>218601</v>
       </c>
       <c r="AT17" s="3">
-        <v>674475</v>
+        <v>674482</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="16"/>
-        <v>0.97735127263242549</v>
+        <v>0.97736141601640325</v>
       </c>
       <c r="AV17" s="5">
         <v>311697</v>
@@ -2650,14 +2650,14 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="17"/>
-        <v>74897</v>
+        <v>74901</v>
       </c>
       <c r="AY17" s="5">
-        <v>292915</v>
+        <v>292919</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="18"/>
-        <v>0.93974276300381465</v>
+        <v>0.9397555959794287</v>
       </c>
       <c r="BA17" s="10">
         <v>307540</v>
@@ -2667,14 +2667,14 @@
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="19"/>
-        <v>81873</v>
+        <v>81877</v>
       </c>
       <c r="BD17" s="5">
-        <v>300841</v>
+        <v>300845</v>
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="20"/>
-        <v>0.97821746764648498</v>
+        <v>0.9782304740846719</v>
       </c>
       <c r="BF17" s="10">
         <v>689646</v>
@@ -2684,14 +2684,14 @@
       </c>
       <c r="BH17" s="3">
         <f t="shared" si="21"/>
-        <v>257504</v>
+        <v>257511</v>
       </c>
       <c r="BI17" s="5">
-        <v>688744</v>
+        <v>688751</v>
       </c>
       <c r="BJ17" s="4">
         <f t="shared" si="22"/>
-        <v>0.99869208260469866</v>
+        <v>0.99870223273969538</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2709,14 +2709,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>397885</v>
+        <v>397889</v>
       </c>
       <c r="F18" s="5">
-        <v>804248</v>
+        <v>804252</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>0.95686966908943383</v>
+        <v>0.95687442816707691</v>
       </c>
       <c r="H18" s="5">
         <v>861805</v>
@@ -2726,14 +2726,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>381245</v>
+        <v>381249</v>
       </c>
       <c r="K18" s="5">
-        <v>819362</v>
+        <v>819366</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.95075103996843835</v>
+        <v>0.9507556813896415</v>
       </c>
       <c r="M18" s="9">
         <v>1358945</v>
@@ -2745,11 +2745,11 @@
         <v>1272521</v>
       </c>
       <c r="P18" s="5">
-        <v>1276372</v>
+        <v>1276378</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="4"/>
-        <v>0.93923742314810388</v>
+        <v>0.93924183833782826</v>
       </c>
       <c r="R18" s="5">
         <v>869959</v>
@@ -2759,14 +2759,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="5"/>
-        <v>402920</v>
+        <v>402924</v>
       </c>
       <c r="U18" s="5">
-        <v>822380</v>
+        <v>822384</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="6"/>
-        <v>0.94530891685700136</v>
+        <v>0.94531351477483416</v>
       </c>
       <c r="W18" s="5">
         <v>883450</v>
@@ -2776,14 +2776,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="7"/>
-        <v>412759</v>
+        <v>412762</v>
       </c>
       <c r="Z18" s="5">
-        <v>838155</v>
+        <v>838158</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="8"/>
-        <v>0.94872941309638348</v>
+        <v>0.94873280887429967</v>
       </c>
       <c r="AB18" s="5">
         <v>1397129</v>
@@ -2793,14 +2793,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="9"/>
-        <v>718457</v>
+        <v>718461</v>
       </c>
       <c r="AE18" s="5">
-        <v>1341452</v>
+        <v>1341456</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="10"/>
-        <v>0.9601489912527762</v>
+        <v>0.96015185426685723</v>
       </c>
       <c r="AG18" s="5">
         <v>899515</v>
@@ -2810,14 +2810,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="11"/>
-        <v>400328</v>
+        <v>400331</v>
       </c>
       <c r="AJ18" s="5">
-        <v>863727</v>
+        <v>863730</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="12"/>
-        <v>0.9602141153844016</v>
+        <v>0.96021745051499974</v>
       </c>
       <c r="AL18" s="5">
         <v>914748</v>
@@ -2827,14 +2827,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="13"/>
-        <v>398131</v>
+        <v>398134</v>
       </c>
       <c r="AO18" s="5">
-        <v>880108</v>
+        <v>880111</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="14"/>
-        <v>0.96213164718589161</v>
+        <v>0.962134926777648</v>
       </c>
       <c r="AQ18" s="3">
         <v>1436617</v>
@@ -2844,14 +2844,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="15"/>
-        <v>655862</v>
+        <v>655868</v>
       </c>
       <c r="AT18" s="3">
-        <v>1378601</v>
+        <v>1378607</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="16"/>
-        <v>0.95961623731307644</v>
+        <v>0.95962041379156726</v>
       </c>
       <c r="AV18" s="5">
         <v>954168</v>
@@ -2861,14 +2861,14 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="17"/>
-        <v>385901</v>
+        <v>385905</v>
       </c>
       <c r="AY18" s="5">
-        <v>892995</v>
+        <v>892999</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="18"/>
-        <v>0.93588864853987974</v>
+        <v>0.93589284067375977</v>
       </c>
       <c r="BA18" s="10">
         <v>922519</v>
@@ -2878,14 +2878,14 @@
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="19"/>
-        <v>429129</v>
+        <v>429133</v>
       </c>
       <c r="BD18" s="5">
-        <v>910829</v>
+        <v>910833</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" si="20"/>
-        <v>0.98732817427066544</v>
+        <v>0.98733251022472168</v>
       </c>
       <c r="BF18" s="10">
         <v>1428140</v>
@@ -2895,14 +2895,14 @@
       </c>
       <c r="BH18" s="3">
         <f t="shared" si="21"/>
-        <v>725116</v>
+        <v>725123</v>
       </c>
       <c r="BI18" s="5">
-        <v>1417099</v>
+        <v>1417106</v>
       </c>
       <c r="BJ18" s="4">
         <f t="shared" si="22"/>
-        <v>0.99226896522749874</v>
+        <v>0.99227386670774576</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -2920,14 +2920,14 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>162681</v>
+        <v>162685</v>
       </c>
       <c r="F19" s="5">
-        <v>236282</v>
+        <v>236286</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>0.85469448584202679</v>
+        <v>0.85470895489994647</v>
       </c>
       <c r="H19" s="5">
         <v>280982</v>
@@ -2937,14 +2937,14 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>160627</v>
+        <v>160631</v>
       </c>
       <c r="K19" s="5">
-        <v>240910</v>
+        <v>240914</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="3"/>
-        <v>0.85738588236968916</v>
+        <v>0.85740011815703498</v>
       </c>
       <c r="M19" s="9">
         <v>470659</v>
@@ -2956,11 +2956,11 @@
         <v>406179</v>
       </c>
       <c r="P19" s="5">
-        <v>408672</v>
+        <v>408678</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="4"/>
-        <v>0.86829742977399771</v>
+        <v>0.86831017785700471</v>
       </c>
       <c r="R19" s="5">
         <v>282327</v>
@@ -2970,14 +2970,14 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" si="5"/>
-        <v>164073</v>
+        <v>164077</v>
       </c>
       <c r="U19" s="5">
-        <v>240711</v>
+        <v>240715</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="6"/>
-        <v>0.85259645729951439</v>
+        <v>0.85261062526786313</v>
       </c>
       <c r="W19" s="5">
         <v>286093</v>
@@ -2987,14 +2987,14 @@
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="7"/>
-        <v>167494</v>
+        <v>167498</v>
       </c>
       <c r="Z19" s="5">
-        <v>245967</v>
+        <v>245971</v>
       </c>
       <c r="AA19" s="4">
         <f t="shared" si="8"/>
-        <v>0.85974490812428128</v>
+        <v>0.85975888959184599</v>
       </c>
       <c r="AB19" s="5">
         <v>481143</v>
@@ -3004,14 +3004,14 @@
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="9"/>
-        <v>316659</v>
+        <v>316663</v>
       </c>
       <c r="AE19" s="5">
-        <v>436094</v>
+        <v>436098</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="10"/>
-        <v>0.90637087103002645</v>
+        <v>0.90637918456675037</v>
       </c>
       <c r="AG19" s="5">
         <v>287213</v>
@@ -3021,14 +3021,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="11"/>
-        <v>164978</v>
+        <v>164981</v>
       </c>
       <c r="AJ19" s="5">
-        <v>254428</v>
+        <v>254431</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="12"/>
-        <v>0.88585126717801765</v>
+        <v>0.88586171238767042</v>
       </c>
       <c r="AL19" s="5">
         <v>292666</v>
@@ -3038,14 +3038,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="13"/>
-        <v>159535</v>
+        <v>159539</v>
       </c>
       <c r="AO19" s="5">
-        <v>260131</v>
+        <v>260135</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="14"/>
-        <v>0.88883232080255303</v>
+        <v>0.88884598825965433</v>
       </c>
       <c r="AQ19" s="3">
         <v>495564</v>
@@ -3055,14 +3055,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="15"/>
-        <v>290904</v>
+        <v>290909</v>
       </c>
       <c r="AT19" s="3">
-        <v>448264</v>
+        <v>448269</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="16"/>
-        <v>0.90455319595450845</v>
+        <v>0.90456328546867815</v>
       </c>
       <c r="AV19" s="5">
         <v>310298</v>
@@ -3072,14 +3072,14 @@
       </c>
       <c r="AX19" s="3">
         <f t="shared" si="17"/>
-        <v>162867</v>
+        <v>162871</v>
       </c>
       <c r="AY19" s="5">
-        <v>263966</v>
+        <v>263970</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="18"/>
-        <v>0.85068547009648787</v>
+        <v>0.85069836093046036</v>
       </c>
       <c r="BA19" s="10">
         <v>280202</v>
@@ -3089,14 +3089,14 @@
       </c>
       <c r="BC19" s="3">
         <f t="shared" si="19"/>
-        <v>182663</v>
+        <v>182669</v>
       </c>
       <c r="BD19" s="5">
-        <v>272732</v>
+        <v>272738</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="20"/>
-        <v>0.97334066138000441</v>
+        <v>0.97336207450339396</v>
       </c>
       <c r="BF19" s="10">
         <v>473091</v>
@@ -3106,14 +3106,14 @@
       </c>
       <c r="BH19" s="3">
         <f t="shared" si="21"/>
-        <v>327681</v>
+        <v>327689</v>
       </c>
       <c r="BI19" s="5">
-        <v>464745</v>
+        <v>464753</v>
       </c>
       <c r="BJ19" s="4">
         <f t="shared" si="22"/>
-        <v>0.98235857372048929</v>
+        <v>0.98237548378641737</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3131,14 +3131,14 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>3107</v>
+        <v>3108</v>
       </c>
       <c r="F20" s="5">
-        <v>5061</v>
+        <v>5062</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="1"/>
-        <v>0.83846918489065603</v>
+        <v>0.83863485752153744</v>
       </c>
       <c r="H20" s="5">
         <v>6124</v>
@@ -3148,14 +3148,14 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" si="2"/>
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="K20" s="5">
-        <v>5127</v>
+        <v>5128</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="3"/>
-        <v>0.83719790986283471</v>
+        <v>0.83736120182886997</v>
       </c>
       <c r="M20" s="9">
         <v>9262</v>
@@ -3167,11 +3167,11 @@
         <v>7959</v>
       </c>
       <c r="P20" s="5">
-        <v>8083</v>
+        <v>8085</v>
       </c>
       <c r="Q20" s="4">
         <f t="shared" si="4"/>
-        <v>0.87270567911898078</v>
+        <v>0.87292161520190026</v>
       </c>
       <c r="R20" s="5">
         <v>6202</v>
@@ -3181,14 +3181,14 @@
       </c>
       <c r="T20" s="3">
         <f t="shared" si="5"/>
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="U20" s="5">
-        <v>5198</v>
+        <v>5199</v>
       </c>
       <c r="V20" s="4">
         <f t="shared" si="6"/>
-        <v>0.83811673653660113</v>
+        <v>0.83827797484682365</v>
       </c>
       <c r="W20" s="5">
         <v>6226</v>
@@ -3198,14 +3198,14 @@
       </c>
       <c r="Y20" s="3">
         <f t="shared" si="7"/>
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="Z20" s="5">
-        <v>5268</v>
+        <v>5269</v>
       </c>
       <c r="AA20" s="4">
         <f t="shared" si="8"/>
-        <v>0.84612913588178607</v>
+        <v>0.8462897526501767</v>
       </c>
       <c r="AB20" s="5">
         <v>9386</v>
@@ -3342,14 +3342,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>6071</v>
+        <v>6072</v>
       </c>
       <c r="F21" s="5">
-        <v>8306</v>
+        <v>8307</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>0.78233022511067152</v>
+        <v>0.78242441367617976</v>
       </c>
       <c r="H21" s="5">
         <v>10811</v>
@@ -3359,14 +3359,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>5869</v>
+        <v>5871</v>
       </c>
       <c r="K21" s="5">
-        <v>8432</v>
+        <v>8434</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>0.77994635093885856</v>
+        <v>0.78013134770141523</v>
       </c>
       <c r="M21" s="9">
         <v>14133</v>
@@ -3378,11 +3378,11 @@
         <v>11192</v>
       </c>
       <c r="P21" s="5">
-        <v>11400</v>
+        <v>11402</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="4"/>
-        <v>0.80662279770749312</v>
+        <v>0.80676431047902075</v>
       </c>
       <c r="R21" s="5">
         <v>11019</v>
@@ -3392,14 +3392,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="5"/>
-        <v>6085</v>
+        <v>6087</v>
       </c>
       <c r="U21" s="5">
-        <v>8627</v>
+        <v>8629</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="6"/>
-        <v>0.78292041020056269</v>
+        <v>0.78310191487430802</v>
       </c>
       <c r="W21" s="5">
         <v>11175</v>
@@ -3409,14 +3409,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="7"/>
-        <v>6282</v>
+        <v>6284</v>
       </c>
       <c r="Z21" s="5">
-        <v>8798</v>
+        <v>8800</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="8"/>
-        <v>0.78729306487695749</v>
+        <v>0.78747203579418346</v>
       </c>
       <c r="AB21" s="5">
         <v>14571</v>
@@ -3426,14 +3426,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="9"/>
-        <v>9104</v>
+        <v>9107</v>
       </c>
       <c r="AE21" s="5">
-        <v>12221</v>
+        <v>12224</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="10"/>
-        <v>0.83872074668862806</v>
+        <v>0.83892663509711074</v>
       </c>
       <c r="AG21" s="5">
         <v>11345</v>
@@ -3443,14 +3443,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="11"/>
-        <v>6293</v>
+        <v>6296</v>
       </c>
       <c r="AJ21" s="5">
-        <v>9221</v>
+        <v>9224</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="12"/>
-        <v>0.81278096077567208</v>
+        <v>0.81304539444689294</v>
       </c>
       <c r="AL21" s="5">
         <v>11441</v>
@@ -3460,14 +3460,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="13"/>
-        <v>6140</v>
+        <v>6143</v>
       </c>
       <c r="AO21" s="5">
-        <v>9332</v>
+        <v>9335</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="14"/>
-        <v>0.81566296652390524</v>
+        <v>0.81592518136526526</v>
       </c>
       <c r="AQ21" s="3">
         <v>14790</v>
@@ -3477,14 +3477,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="15"/>
-        <v>8838</v>
+        <v>8843</v>
       </c>
       <c r="AT21" s="3">
-        <v>12528</v>
+        <v>12533</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="16"/>
-        <v>0.84705882352941175</v>
+        <v>0.84739688979039896</v>
       </c>
       <c r="AV21" s="5">
         <v>11740</v>
@@ -3494,14 +3494,14 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="17"/>
-        <v>6327</v>
+        <v>6331</v>
       </c>
       <c r="AY21" s="5">
-        <v>9472</v>
+        <v>9476</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="18"/>
-        <v>0.80681431005110738</v>
+        <v>0.8071550255536627</v>
       </c>
       <c r="BA21" s="10">
         <v>9242</v>
@@ -3511,14 +3511,14 @@
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="19"/>
-        <v>6590</v>
+        <v>6594</v>
       </c>
       <c r="BD21" s="5">
-        <v>9581</v>
+        <v>9585</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="20"/>
-        <v>1.0366803722138065</v>
+        <v>1.0371131789655919</v>
       </c>
       <c r="BF21" s="10">
         <v>12544</v>
@@ -3528,14 +3528,14 @@
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="21"/>
-        <v>9734</v>
+        <v>9739</v>
       </c>
       <c r="BI21" s="5">
-        <v>12925</v>
+        <v>12930</v>
       </c>
       <c r="BJ21" s="4">
         <f t="shared" si="22"/>
-        <v>1.0303730867346939</v>
+        <v>1.0307716836734695</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3553,14 +3553,14 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>3776</v>
+        <v>3777</v>
       </c>
       <c r="F22" s="5">
-        <v>5530</v>
+        <v>5531</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>0.90566655748444158</v>
+        <v>0.90583033082214215</v>
       </c>
       <c r="H22" s="5">
         <v>6184</v>
@@ -3570,14 +3570,14 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>3784</v>
+        <v>3785</v>
       </c>
       <c r="K22" s="5">
-        <v>5606</v>
+        <v>5607</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="3"/>
-        <v>0.90653298835705043</v>
+        <v>0.90669469598965069</v>
       </c>
       <c r="M22" s="9">
         <v>7446</v>
@@ -3589,11 +3589,11 @@
         <v>6697</v>
       </c>
       <c r="P22" s="5">
-        <v>6763</v>
+        <v>6764</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="4"/>
-        <v>0.90827289820037604</v>
+        <v>0.90840719849583673</v>
       </c>
       <c r="R22" s="5">
         <v>6325</v>
@@ -3603,14 +3603,14 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" si="5"/>
-        <v>3918</v>
+        <v>3919</v>
       </c>
       <c r="U22" s="5">
-        <v>5738</v>
+        <v>5739</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="6"/>
-        <v>0.90719367588932809</v>
+        <v>0.90735177865612648</v>
       </c>
       <c r="W22" s="5">
         <v>6418</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="7"/>
-        <v>4044</v>
+        <v>4045</v>
       </c>
       <c r="Z22" s="5">
-        <v>5824</v>
+        <v>5825</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" si="8"/>
-        <v>0.90744780305391093</v>
+        <v>0.90760361483328145</v>
       </c>
       <c r="AB22" s="5">
         <v>7662</v>
@@ -3637,14 +3637,14 @@
       </c>
       <c r="AD22" s="3">
         <f t="shared" si="9"/>
-        <v>5027</v>
+        <v>5028</v>
       </c>
       <c r="AE22" s="5">
-        <v>7108</v>
+        <v>7109</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="10"/>
-        <v>0.92769511876794575</v>
+        <v>0.92782563299399634</v>
       </c>
       <c r="AG22" s="5">
         <v>6546</v>
@@ -3654,14 +3654,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="11"/>
-        <v>4112</v>
+        <v>4113</v>
       </c>
       <c r="AJ22" s="5">
-        <v>6016</v>
+        <v>6017</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="12"/>
-        <v>0.9190345249007027</v>
+        <v>0.91918728994805987</v>
       </c>
       <c r="AL22" s="5">
         <v>6648</v>
@@ -3671,14 +3671,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="13"/>
-        <v>3818</v>
+        <v>3819</v>
       </c>
       <c r="AO22" s="5">
-        <v>6076</v>
+        <v>6077</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="14"/>
-        <v>0.91395908543922988</v>
+        <v>0.91410950661853185</v>
       </c>
       <c r="AQ22" s="3">
         <v>7880</v>
@@ -3688,14 +3688,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="15"/>
-        <v>4831</v>
+        <v>4833</v>
       </c>
       <c r="AT22" s="3">
-        <v>7287</v>
+        <v>7289</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="16"/>
-        <v>0.92474619289340099</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="AV22" s="5">
         <v>6715</v>
@@ -3705,14 +3705,14 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="17"/>
-        <v>3915</v>
+        <v>3917</v>
       </c>
       <c r="AY22" s="5">
-        <v>6098</v>
+        <v>6100</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="18"/>
-        <v>0.90811615785554733</v>
+        <v>0.90841399851079674</v>
       </c>
       <c r="BA22" s="10">
         <v>6117</v>
@@ -3722,14 +3722,14 @@
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="19"/>
-        <v>4029</v>
+        <v>4030</v>
       </c>
       <c r="BD22" s="5">
-        <v>6146</v>
+        <v>6147</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" si="20"/>
-        <v>1.0047408860552558</v>
+        <v>1.0049043648847473</v>
       </c>
       <c r="BF22" s="10">
         <v>7349</v>
@@ -3739,14 +3739,14 @@
       </c>
       <c r="BH22" s="3">
         <f t="shared" si="21"/>
-        <v>5144</v>
+        <v>5145</v>
       </c>
       <c r="BI22" s="5">
-        <v>7417</v>
+        <v>7418</v>
       </c>
       <c r="BJ22" s="4">
         <f t="shared" si="22"/>
-        <v>1.0092529595863382</v>
+        <v>1.0093890325214314</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -3950,14 +3950,14 @@
       </c>
       <c r="BH23" s="3">
         <f t="shared" si="21"/>
-        <v>7867</v>
+        <v>7868</v>
       </c>
       <c r="BI23" s="5">
-        <v>10636</v>
+        <v>10637</v>
       </c>
       <c r="BJ23" s="4">
         <f t="shared" si="22"/>
-        <v>0.94719031080238669</v>
+        <v>0.94727936592750916</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4397,14 +4397,14 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>7689</v>
+        <v>7691</v>
       </c>
       <c r="F26" s="5">
-        <v>11663</v>
+        <v>11665</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>0.72857321339330339</v>
+        <v>0.72869815092453771</v>
       </c>
       <c r="H26" s="5">
         <v>16365</v>
@@ -4414,14 +4414,14 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>7790</v>
+        <v>7792</v>
       </c>
       <c r="K26" s="5">
-        <v>12088</v>
+        <v>12090</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="3"/>
-        <v>0.7386495569813627</v>
+        <v>0.73877176901924835</v>
       </c>
       <c r="M26" s="9">
         <v>27510</v>
@@ -4433,11 +4433,11 @@
         <v>21793</v>
       </c>
       <c r="P26" s="5">
-        <v>22088</v>
+        <v>22091</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="4"/>
-        <v>0.80290803344238459</v>
+        <v>0.80301708469647404</v>
       </c>
       <c r="R26" s="5">
         <v>16566</v>
@@ -4447,14 +4447,14 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="5"/>
-        <v>7992</v>
+        <v>7994</v>
       </c>
       <c r="U26" s="5">
-        <v>12450</v>
+        <v>12452</v>
       </c>
       <c r="V26" s="4">
         <f t="shared" si="6"/>
-        <v>0.75153929735603042</v>
+        <v>0.75166002656042497</v>
       </c>
       <c r="W26" s="5">
         <v>16728</v>
@@ -4464,14 +4464,14 @@
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="7"/>
-        <v>8686</v>
+        <v>8688</v>
       </c>
       <c r="Z26" s="5">
-        <v>12685</v>
+        <v>12687</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" si="8"/>
-        <v>0.7583094213295074</v>
+        <v>0.75842898134863701</v>
       </c>
       <c r="AB26" s="5">
         <v>28240</v>
@@ -4481,14 +4481,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="9"/>
-        <v>18093</v>
+        <v>18096</v>
       </c>
       <c r="AE26" s="5">
-        <v>24959</v>
+        <v>24962</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="10"/>
-        <v>0.8838172804532578</v>
+        <v>0.8839235127478754</v>
       </c>
       <c r="AG26" s="5">
         <v>16538</v>
@@ -4498,14 +4498,14 @@
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="11"/>
-        <v>8855</v>
+        <v>8857</v>
       </c>
       <c r="AJ26" s="5">
-        <v>13472</v>
+        <v>13474</v>
       </c>
       <c r="AK26" s="4">
         <f t="shared" si="12"/>
-        <v>0.81460877977990087</v>
+        <v>0.81472971338735034</v>
       </c>
       <c r="AL26" s="5">
         <v>16671</v>
@@ -4515,14 +4515,14 @@
       </c>
       <c r="AN26" s="3">
         <f t="shared" si="13"/>
-        <v>8881</v>
+        <v>8883</v>
       </c>
       <c r="AO26" s="5">
-        <v>13575</v>
+        <v>13577</v>
       </c>
       <c r="AP26" s="4">
         <f t="shared" si="14"/>
-        <v>0.81428828504588802</v>
+        <v>0.81440825385399795</v>
       </c>
       <c r="AQ26" s="3">
         <v>28406</v>
@@ -4532,14 +4532,14 @@
       </c>
       <c r="AS26" s="3">
         <f t="shared" si="15"/>
-        <v>17037</v>
+        <v>17041</v>
       </c>
       <c r="AT26" s="3">
-        <v>25111</v>
+        <v>25115</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="16"/>
-        <v>0.88400337956769692</v>
+        <v>0.8841441948884039</v>
       </c>
       <c r="AV26" s="5">
         <v>16717</v>
@@ -4549,14 +4549,14 @@
       </c>
       <c r="AX26" s="3">
         <f t="shared" si="17"/>
-        <v>8244</v>
+        <v>8247</v>
       </c>
       <c r="AY26" s="5">
-        <v>13274</v>
+        <v>13277</v>
       </c>
       <c r="AZ26" s="4">
         <f t="shared" si="18"/>
-        <v>0.79404199318059465</v>
+        <v>0.79422145121732368</v>
       </c>
       <c r="BA26" s="10">
         <v>13719</v>
@@ -4566,14 +4566,14 @@
       </c>
       <c r="BC26" s="3">
         <f t="shared" si="19"/>
-        <v>8537</v>
+        <v>8540</v>
       </c>
       <c r="BD26" s="5">
-        <v>13371</v>
+        <v>13374</v>
       </c>
       <c r="BE26" s="4">
         <f t="shared" si="20"/>
-        <v>0.97463371965886725</v>
+        <v>0.97485239448939431</v>
       </c>
       <c r="BF26" s="10">
         <v>25779</v>
@@ -4583,14 +4583,14 @@
       </c>
       <c r="BH26" s="3">
         <f t="shared" si="21"/>
-        <v>17872</v>
+        <v>17877</v>
       </c>
       <c r="BI26" s="5">
-        <v>25157</v>
+        <v>25162</v>
       </c>
       <c r="BJ26" s="4">
         <f t="shared" si="22"/>
-        <v>0.97587183366305907</v>
+        <v>0.97606578998409554</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4608,14 +4608,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>70244</v>
+        <v>70249</v>
       </c>
       <c r="F27" s="5">
-        <v>109134</v>
+        <v>109139</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>0.9209153966887752</v>
+        <v>0.92095758864530064</v>
       </c>
       <c r="H27" s="5">
         <v>121212</v>
@@ -4625,14 +4625,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>66311</v>
+        <v>66316</v>
       </c>
       <c r="K27" s="5">
-        <v>111208</v>
+        <v>111213</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.91746691746691744</v>
+        <v>0.91750816750816755</v>
       </c>
       <c r="M27" s="9">
         <v>178312</v>
@@ -4644,11 +4644,11 @@
         <v>161829</v>
       </c>
       <c r="P27" s="5">
-        <v>163118</v>
+        <v>163124</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="4"/>
-        <v>0.91478980663107368</v>
+        <v>0.91482345551617394</v>
       </c>
       <c r="R27" s="5">
         <v>121489</v>
@@ -4658,14 +4658,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="5"/>
-        <v>67700</v>
+        <v>67705</v>
       </c>
       <c r="U27" s="5">
-        <v>111728</v>
+        <v>111733</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="6"/>
-        <v>0.91965527743252473</v>
+        <v>0.91969643342195595</v>
       </c>
       <c r="W27" s="5">
         <v>123451</v>
@@ -4675,14 +4675,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="7"/>
-        <v>70984</v>
+        <v>70989</v>
       </c>
       <c r="Z27" s="5">
-        <v>113710</v>
+        <v>113715</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="8"/>
-        <v>0.921094199317948</v>
+        <v>0.92113470121748708</v>
       </c>
       <c r="AB27" s="5">
         <v>182601</v>
@@ -4692,14 +4692,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="9"/>
-        <v>117971</v>
+        <v>117977</v>
       </c>
       <c r="AE27" s="5">
-        <v>173243</v>
+        <v>173249</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="10"/>
-        <v>0.94875164977190707</v>
+        <v>0.94878450829951644</v>
       </c>
       <c r="AG27" s="5">
         <v>124689</v>
@@ -4709,14 +4709,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="11"/>
-        <v>69016</v>
+        <v>69021</v>
       </c>
       <c r="AJ27" s="5">
-        <v>117347</v>
+        <v>117352</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="12"/>
-        <v>0.94111750034084807</v>
+        <v>0.94115760010907135</v>
       </c>
       <c r="AL27" s="5">
         <v>127177</v>
@@ -4726,14 +4726,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" si="13"/>
-        <v>69454</v>
+        <v>69460</v>
       </c>
       <c r="AO27" s="5">
-        <v>119041</v>
+        <v>119047</v>
       </c>
       <c r="AP27" s="4">
         <f t="shared" si="14"/>
-        <v>0.93602616825369367</v>
+        <v>0.93607334659568953</v>
       </c>
       <c r="AQ27" s="3">
         <v>185152</v>
@@ -4743,14 +4743,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" si="15"/>
-        <v>105614</v>
+        <v>105622</v>
       </c>
       <c r="AT27" s="3">
-        <v>176810</v>
+        <v>176818</v>
       </c>
       <c r="AU27" s="4">
         <f t="shared" si="16"/>
-        <v>0.95494512616660909</v>
+        <v>0.9549883339094366</v>
       </c>
       <c r="AV27" s="5">
         <v>127611</v>
@@ -4760,14 +4760,14 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" si="17"/>
-        <v>66562</v>
+        <v>66569</v>
       </c>
       <c r="AY27" s="5">
-        <v>119109</v>
+        <v>119116</v>
       </c>
       <c r="AZ27" s="4">
         <f t="shared" si="18"/>
-        <v>0.93337564943460982</v>
+        <v>0.93343050363996838</v>
       </c>
       <c r="BA27" s="10">
         <v>122070</v>
@@ -4777,14 +4777,14 @@
       </c>
       <c r="BC27" s="3">
         <f t="shared" si="19"/>
-        <v>69506</v>
+        <v>69512</v>
       </c>
       <c r="BD27" s="5">
-        <v>120771</v>
+        <v>120777</v>
       </c>
       <c r="BE27" s="4">
         <f t="shared" si="20"/>
-        <v>0.98935856475792583</v>
+        <v>0.98940771688375517</v>
       </c>
       <c r="BF27" s="10">
         <v>180737</v>
@@ -4794,14 +4794,14 @@
       </c>
       <c r="BH27" s="3">
         <f t="shared" si="21"/>
-        <v>116068</v>
+        <v>116077</v>
       </c>
       <c r="BI27" s="5">
-        <v>179733</v>
+        <v>179742</v>
       </c>
       <c r="BJ27" s="4">
         <f t="shared" si="22"/>
-        <v>0.99444496699624318</v>
+        <v>0.99449476310882667</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4819,14 +4819,14 @@
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>155503</v>
+        <v>155505</v>
       </c>
       <c r="F28" s="5">
-        <v>342705</v>
+        <v>342707</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>0.94056702162696237</v>
+        <v>0.94057251070369963</v>
       </c>
       <c r="H28" s="5">
         <v>368904</v>
@@ -4836,14 +4836,14 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>152906</v>
+        <v>152908</v>
       </c>
       <c r="K28" s="5">
-        <v>347628</v>
+        <v>347630</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="3"/>
-        <v>0.94232645891614075</v>
+        <v>0.94233188038080373</v>
       </c>
       <c r="M28" s="9">
         <v>633580</v>
@@ -4855,11 +4855,11 @@
         <v>594498</v>
       </c>
       <c r="P28" s="5">
-        <v>595743</v>
+        <v>595745</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="4"/>
-        <v>0.94028062754506136</v>
+        <v>0.94028378421036019</v>
       </c>
       <c r="R28" s="5">
         <v>370844</v>
@@ -4869,14 +4869,14 @@
       </c>
       <c r="T28" s="3">
         <f t="shared" si="5"/>
-        <v>152907</v>
+        <v>152909</v>
       </c>
       <c r="U28" s="5">
-        <v>350176</v>
+        <v>350178</v>
       </c>
       <c r="V28" s="4">
         <f t="shared" si="6"/>
-        <v>0.94426767050296079</v>
+        <v>0.94427306360626029</v>
       </c>
       <c r="W28" s="5">
         <v>375522</v>
@@ -4886,14 +4886,14 @@
       </c>
       <c r="Y28" s="3">
         <f t="shared" si="7"/>
-        <v>159771</v>
+        <v>159774</v>
       </c>
       <c r="Z28" s="5">
-        <v>355202</v>
+        <v>355205</v>
       </c>
       <c r="AA28" s="4">
         <f t="shared" si="8"/>
-        <v>0.94588865632373065</v>
+        <v>0.94589664520321048</v>
       </c>
       <c r="AB28" s="5">
         <v>643156</v>
@@ -4903,14 +4903,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="9"/>
-        <v>319754</v>
+        <v>319758</v>
       </c>
       <c r="AE28" s="5">
-        <v>621201</v>
+        <v>621205</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="10"/>
-        <v>0.96586364738881392</v>
+        <v>0.96586986671973829</v>
       </c>
       <c r="AG28" s="5">
         <v>378725</v>
@@ -4920,14 +4920,14 @@
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="11"/>
-        <v>153060</v>
+        <v>153063</v>
       </c>
       <c r="AJ28" s="5">
-        <v>362799</v>
+        <v>362802</v>
       </c>
       <c r="AK28" s="4">
         <f t="shared" si="12"/>
-        <v>0.95794837943098554</v>
+        <v>0.95795630074592386</v>
       </c>
       <c r="AL28" s="5">
         <v>382864</v>
@@ -4937,14 +4937,14 @@
       </c>
       <c r="AN28" s="3">
         <f t="shared" si="13"/>
-        <v>155544</v>
+        <v>155546</v>
       </c>
       <c r="AO28" s="5">
-        <v>368177</v>
+        <v>368179</v>
       </c>
       <c r="AP28" s="4">
         <f t="shared" si="14"/>
-        <v>0.96163911989636008</v>
+        <v>0.96164434368339669</v>
       </c>
       <c r="AQ28" s="3">
         <v>653033</v>
@@ -4954,14 +4954,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="15"/>
-        <v>268767</v>
+        <v>268771</v>
       </c>
       <c r="AT28" s="3">
-        <v>629784</v>
+        <v>629788</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" si="16"/>
-        <v>0.96439843009465065</v>
+        <v>0.96440455535937697</v>
       </c>
       <c r="AV28" s="5">
         <v>393378</v>
@@ -4971,14 +4971,14 @@
       </c>
       <c r="AX28" s="3">
         <f t="shared" si="17"/>
-        <v>145235</v>
+        <v>145237</v>
       </c>
       <c r="AY28" s="5">
-        <v>371026</v>
+        <v>371028</v>
       </c>
       <c r="AZ28" s="4">
         <f t="shared" si="18"/>
-        <v>0.94317933387225517</v>
+        <v>0.94318441804066322</v>
       </c>
       <c r="BA28" s="10">
         <v>381893</v>
@@ -4988,14 +4988,14 @@
       </c>
       <c r="BC28" s="3">
         <f t="shared" si="19"/>
-        <v>155336</v>
+        <v>155338</v>
       </c>
       <c r="BD28" s="5">
-        <v>376422</v>
+        <v>376424</v>
       </c>
       <c r="BE28" s="4">
         <f t="shared" si="20"/>
-        <v>0.98567399769045261</v>
+        <v>0.9856792347594745</v>
       </c>
       <c r="BF28" s="10">
         <v>643514</v>
@@ -5005,14 +5005,14 @@
       </c>
       <c r="BH28" s="3">
         <f t="shared" si="21"/>
-        <v>301321</v>
+        <v>301325</v>
       </c>
       <c r="BI28" s="5">
-        <v>640670</v>
+        <v>640674</v>
       </c>
       <c r="BJ28" s="4">
         <f t="shared" si="22"/>
-        <v>0.99558051573081552</v>
+        <v>0.99558673160179889</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5066,11 +5066,11 @@
         <v>159082</v>
       </c>
       <c r="P29" s="5">
-        <v>159522</v>
+        <v>159523</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="4"/>
-        <v>0.94449279738538872</v>
+        <v>0.94449871815366759</v>
       </c>
       <c r="R29" s="5">
         <v>122532</v>
@@ -5114,14 +5114,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="9"/>
-        <v>96104</v>
+        <v>96105</v>
       </c>
       <c r="AE29" s="5">
-        <v>166282</v>
+        <v>166283</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="10"/>
-        <v>0.96298784407521731</v>
+        <v>0.96299363536858684</v>
       </c>
       <c r="AG29" s="5">
         <v>125793</v>
@@ -5165,14 +5165,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="15"/>
-        <v>84973</v>
+        <v>84974</v>
       </c>
       <c r="AT29" s="3">
-        <v>169373</v>
+        <v>169374</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="16"/>
-        <v>0.96325511562041466</v>
+        <v>0.96326080280264337</v>
       </c>
       <c r="AV29" s="5">
         <v>130198</v>
@@ -5199,14 +5199,14 @@
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="19"/>
-        <v>63484</v>
+        <v>63485</v>
       </c>
       <c r="BD29" s="5">
-        <v>125565</v>
+        <v>125566</v>
       </c>
       <c r="BE29" s="4">
         <f t="shared" si="20"/>
-        <v>0.98447606727037518</v>
+        <v>0.98448390764044058</v>
       </c>
       <c r="BF29" s="10">
         <v>174166</v>
@@ -5216,14 +5216,14 @@
       </c>
       <c r="BH29" s="3">
         <f t="shared" si="21"/>
-        <v>93438</v>
+        <v>93439</v>
       </c>
       <c r="BI29" s="5">
-        <v>172941</v>
+        <v>172942</v>
       </c>
       <c r="BJ29" s="4">
         <f t="shared" si="22"/>
-        <v>0.99296648025446987</v>
+        <v>0.99297222190324175</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>88711</v>
+        <v>88712</v>
       </c>
       <c r="F30" s="5">
-        <v>147123</v>
+        <v>147124</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>0.92748351468233459</v>
+        <v>0.92748981881910908</v>
       </c>
       <c r="H30" s="5">
         <v>160653</v>
@@ -5258,14 +5258,14 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>85766</v>
+        <v>85767</v>
       </c>
       <c r="K30" s="5">
-        <v>150117</v>
+        <v>150118</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="3"/>
-        <v>0.93441765793355869</v>
+        <v>0.93442388252942676</v>
       </c>
       <c r="M30" s="9">
         <v>275749</v>
@@ -5277,11 +5277,11 @@
         <v>254361</v>
       </c>
       <c r="P30" s="5">
-        <v>255525</v>
+        <v>255527</v>
       </c>
       <c r="Q30" s="4">
         <f t="shared" si="4"/>
-        <v>0.92665793892271597</v>
+        <v>0.92666519189552821</v>
       </c>
       <c r="R30" s="5">
         <v>161454</v>
@@ -5291,14 +5291,14 @@
       </c>
       <c r="T30" s="3">
         <f t="shared" si="5"/>
-        <v>89018</v>
+        <v>89019</v>
       </c>
       <c r="U30" s="5">
-        <v>150303</v>
+        <v>150304</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" si="6"/>
-        <v>0.9309338882901631</v>
+        <v>0.93094008200478151</v>
       </c>
       <c r="W30" s="5">
         <v>163696</v>
@@ -5308,14 +5308,14 @@
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="7"/>
-        <v>91670</v>
+        <v>91671</v>
       </c>
       <c r="Z30" s="5">
-        <v>153487</v>
+        <v>153488</v>
       </c>
       <c r="AA30" s="4">
         <f t="shared" si="8"/>
-        <v>0.9376343954647639</v>
+        <v>0.93764050434952595</v>
       </c>
       <c r="AB30" s="5">
         <v>281667</v>
@@ -5325,14 +5325,14 @@
       </c>
       <c r="AD30" s="3">
         <f t="shared" si="9"/>
-        <v>177385</v>
+        <v>177388</v>
       </c>
       <c r="AE30" s="5">
-        <v>271175</v>
+        <v>271178</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="10"/>
-        <v>0.96275033994042614</v>
+        <v>0.96276099081539546</v>
       </c>
       <c r="AG30" s="5">
         <v>165324</v>
@@ -5342,14 +5342,14 @@
       </c>
       <c r="AI30" s="3">
         <f t="shared" si="11"/>
-        <v>90153</v>
+        <v>90154</v>
       </c>
       <c r="AJ30" s="5">
-        <v>158270</v>
+        <v>158271</v>
       </c>
       <c r="AK30" s="4">
         <f t="shared" si="12"/>
-        <v>0.95733226875710731</v>
+        <v>0.95733831748566456</v>
       </c>
       <c r="AL30" s="5">
         <v>168552</v>
@@ -5359,14 +5359,14 @@
       </c>
       <c r="AN30" s="3">
         <f t="shared" si="13"/>
-        <v>88490</v>
+        <v>88491</v>
       </c>
       <c r="AO30" s="5">
-        <v>161677</v>
+        <v>161678</v>
       </c>
       <c r="AP30" s="4">
         <f t="shared" si="14"/>
-        <v>0.95921140063600552</v>
+        <v>0.95921733352318572</v>
       </c>
       <c r="AQ30" s="3">
         <v>288456</v>
@@ -5376,14 +5376,14 @@
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="15"/>
-        <v>160992</v>
+        <v>160994</v>
       </c>
       <c r="AT30" s="3">
-        <v>277799</v>
+        <v>277801</v>
       </c>
       <c r="AU30" s="4">
         <f t="shared" si="16"/>
-        <v>0.96305502398979392</v>
+        <v>0.96306195745624978</v>
       </c>
       <c r="AV30" s="5">
         <v>173481</v>
@@ -5393,14 +5393,14 @@
       </c>
       <c r="AX30" s="3">
         <f t="shared" si="17"/>
-        <v>85702</v>
+        <v>85703</v>
       </c>
       <c r="AY30" s="5">
-        <v>162672</v>
+        <v>162673</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="18"/>
-        <v>0.9376934649904024</v>
+        <v>0.93769922931041438</v>
       </c>
       <c r="BA30" s="10">
         <v>168414</v>
@@ -5410,14 +5410,14 @@
       </c>
       <c r="BC30" s="3">
         <f t="shared" si="19"/>
-        <v>90663</v>
+        <v>90664</v>
       </c>
       <c r="BD30" s="5">
-        <v>165614</v>
+        <v>165615</v>
       </c>
       <c r="BE30" s="4">
         <f t="shared" si="20"/>
-        <v>0.98337430379897162</v>
+        <v>0.98338024154761483</v>
       </c>
       <c r="BF30" s="10">
         <v>284492</v>
@@ -5427,14 +5427,14 @@
       </c>
       <c r="BH30" s="3">
         <f t="shared" si="21"/>
-        <v>173856</v>
+        <v>173859</v>
       </c>
       <c r="BI30" s="5">
-        <v>283719</v>
+        <v>283722</v>
       </c>
       <c r="BJ30" s="4">
         <f t="shared" si="22"/>
-        <v>0.99728287614414468</v>
+        <v>0.99729342125613374</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5452,14 +5452,14 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>37120</v>
+        <v>37121</v>
       </c>
       <c r="F31" s="5">
-        <v>70031</v>
+        <v>70032</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>0.94190988567585743</v>
+        <v>0.9419233355749832</v>
       </c>
       <c r="H31" s="5">
         <v>75353</v>
@@ -5469,14 +5469,14 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>35313</v>
+        <v>35314</v>
       </c>
       <c r="K31" s="5">
-        <v>71151</v>
+        <v>71152</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="3"/>
-        <v>0.94423579684949499</v>
+        <v>0.94424906772125861</v>
       </c>
       <c r="M31" s="9">
         <v>132153</v>
@@ -5488,11 +5488,11 @@
         <v>124102</v>
       </c>
       <c r="P31" s="5">
-        <v>124749</v>
+        <v>124755</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="4"/>
-        <v>0.94397403010147329</v>
+        <v>0.94401943202197458</v>
       </c>
       <c r="R31" s="5">
         <v>74474</v>
@@ -5502,14 +5502,14 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="5"/>
-        <v>35658</v>
+        <v>35660</v>
       </c>
       <c r="U31" s="5">
-        <v>70001</v>
+        <v>70003</v>
       </c>
       <c r="V31" s="4">
         <f t="shared" si="6"/>
-        <v>0.93993877057765129</v>
+        <v>0.93996562558745334</v>
       </c>
       <c r="W31" s="5">
         <v>75697</v>
@@ -5519,14 +5519,14 @@
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="7"/>
-        <v>36677</v>
+        <v>36678</v>
       </c>
       <c r="Z31" s="5">
-        <v>71281</v>
+        <v>71282</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" si="8"/>
-        <v>0.94166215305758483</v>
+        <v>0.9416753636207511</v>
       </c>
       <c r="AB31" s="5">
         <v>133809</v>
@@ -5536,14 +5536,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="9"/>
-        <v>73406</v>
+        <v>73411</v>
       </c>
       <c r="AE31" s="5">
-        <v>129292</v>
+        <v>129297</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="10"/>
-        <v>0.96624292835310033</v>
+        <v>0.9662802950474183</v>
       </c>
       <c r="AG31" s="5">
         <v>75434</v>
@@ -5553,14 +5553,14 @@
       </c>
       <c r="AI31" s="3">
         <f t="shared" si="11"/>
-        <v>33307</v>
+        <v>33310</v>
       </c>
       <c r="AJ31" s="5">
-        <v>72074</v>
+        <v>72077</v>
       </c>
       <c r="AK31" s="4">
         <f t="shared" si="12"/>
-        <v>0.95545775114669773</v>
+        <v>0.95549752101174534</v>
       </c>
       <c r="AL31" s="5">
         <v>76990</v>
@@ -5570,14 +5570,14 @@
       </c>
       <c r="AN31" s="3">
         <f t="shared" si="13"/>
-        <v>33572</v>
+        <v>33576</v>
       </c>
       <c r="AO31" s="5">
-        <v>73089</v>
+        <v>73093</v>
       </c>
       <c r="AP31" s="4">
         <f t="shared" si="14"/>
-        <v>0.94933108195869598</v>
+        <v>0.94938303675802049</v>
       </c>
       <c r="AQ31" s="3">
         <v>135546</v>
@@ -5587,14 +5587,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="15"/>
-        <v>64949</v>
+        <v>64955</v>
       </c>
       <c r="AT31" s="3">
-        <v>131241</v>
+        <v>131247</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="16"/>
-        <v>0.96823956442831216</v>
+        <v>0.96828382984374306</v>
       </c>
       <c r="AV31" s="5">
         <v>78435</v>
@@ -5604,14 +5604,14 @@
       </c>
       <c r="AX31" s="3">
         <f t="shared" si="17"/>
-        <v>30760</v>
+        <v>30762</v>
       </c>
       <c r="AY31" s="5">
-        <v>73084</v>
+        <v>73086</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="18"/>
-        <v>0.9317779052718812</v>
+        <v>0.93180340409256068</v>
       </c>
       <c r="BA31" s="10">
         <v>76166</v>
@@ -5621,14 +5621,14 @@
       </c>
       <c r="BC31" s="3">
         <f t="shared" si="19"/>
-        <v>33774</v>
+        <v>33776</v>
       </c>
       <c r="BD31" s="5">
-        <v>74311</v>
+        <v>74313</v>
       </c>
       <c r="BE31" s="4">
         <f t="shared" si="20"/>
-        <v>0.97564530105296321</v>
+        <v>0.97567155948848572</v>
       </c>
       <c r="BF31" s="10">
         <v>132970</v>
@@ -5638,14 +5638,14 @@
       </c>
       <c r="BH31" s="3">
         <f t="shared" si="21"/>
-        <v>74225</v>
+        <v>74229</v>
       </c>
       <c r="BI31" s="5">
-        <v>133200</v>
+        <v>133204</v>
       </c>
       <c r="BJ31" s="4">
         <f t="shared" si="22"/>
-        <v>1.0017297134692036</v>
+        <v>1.001759795442581</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5663,14 +5663,14 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>91610</v>
+        <v>91611</v>
       </c>
       <c r="F32" s="5">
-        <v>184444</v>
+        <v>184445</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>0.96065584016500172</v>
+        <v>0.96066104855258905</v>
       </c>
       <c r="H32" s="5">
         <v>196288</v>
@@ -5699,11 +5699,11 @@
         <v>397306</v>
       </c>
       <c r="P32" s="5">
-        <v>398327</v>
+        <v>398330</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="4"/>
-        <v>0.95180371663357199</v>
+        <v>0.95181088514374057</v>
       </c>
       <c r="R32" s="5">
         <v>194320</v>
@@ -5713,14 +5713,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="5"/>
-        <v>94017</v>
+        <v>94018</v>
       </c>
       <c r="U32" s="5">
-        <v>186166</v>
+        <v>186167</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="6"/>
-        <v>0.9580382873610539</v>
+        <v>0.95804343351173327</v>
       </c>
       <c r="W32" s="5">
         <v>198209</v>
@@ -5730,14 +5730,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="7"/>
-        <v>97018</v>
+        <v>97019</v>
       </c>
       <c r="Z32" s="5">
-        <v>190198</v>
+        <v>190199</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="8"/>
-        <v>0.95958306635924706</v>
+        <v>0.95958811153883028</v>
       </c>
       <c r="AB32" s="5">
         <v>426405</v>
@@ -5747,14 +5747,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="9"/>
-        <v>243324</v>
+        <v>243326</v>
       </c>
       <c r="AE32" s="5">
-        <v>418623</v>
+        <v>418625</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="10"/>
-        <v>0.98174974496077672</v>
+        <v>0.98175443533729667</v>
       </c>
       <c r="AG32" s="5">
         <v>199136</v>
@@ -5764,14 +5764,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="11"/>
-        <v>82205</v>
+        <v>82207</v>
       </c>
       <c r="AJ32" s="5">
-        <v>194595</v>
+        <v>194597</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="12"/>
-        <v>0.97719648883175314</v>
+        <v>0.97720653221918685</v>
       </c>
       <c r="AL32" s="5">
         <v>204506</v>
@@ -5781,14 +5781,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="13"/>
-        <v>84508</v>
+        <v>84510</v>
       </c>
       <c r="AO32" s="5">
-        <v>199090</v>
+        <v>199092</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="14"/>
-        <v>0.97351666943757154</v>
+        <v>0.9735264491017378</v>
       </c>
       <c r="AQ32" s="3">
         <v>435626</v>
@@ -5798,14 +5798,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="15"/>
-        <v>206038</v>
+        <v>206039</v>
       </c>
       <c r="AT32" s="3">
-        <v>427430</v>
+        <v>427431</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="16"/>
-        <v>0.98118569598692451</v>
+        <v>0.98118799153402225</v>
       </c>
       <c r="AV32" s="5">
         <v>208760</v>
@@ -5815,14 +5815,14 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="17"/>
-        <v>78088</v>
+        <v>78089</v>
       </c>
       <c r="AY32" s="5">
-        <v>198447</v>
+        <v>198448</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="18"/>
-        <v>0.95059877371143897</v>
+        <v>0.95060356390113043</v>
       </c>
       <c r="BA32" s="10">
         <v>206539</v>
@@ -5832,14 +5832,14 @@
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="19"/>
-        <v>86625</v>
+        <v>86626</v>
       </c>
       <c r="BD32" s="5">
-        <v>203322</v>
+        <v>203323</v>
       </c>
       <c r="BE32" s="4">
         <f t="shared" si="20"/>
-        <v>0.98442424917327964</v>
+        <v>0.98442909087387853</v>
       </c>
       <c r="BF32" s="10">
         <v>435831</v>
@@ -5849,14 +5849,14 @@
       </c>
       <c r="BH32" s="3">
         <f t="shared" si="21"/>
-        <v>241653</v>
+        <v>241654</v>
       </c>
       <c r="BI32" s="5">
-        <v>436074</v>
+        <v>436075</v>
       </c>
       <c r="BJ32" s="4">
         <f t="shared" si="22"/>
-        <v>1.0005575555662631</v>
+        <v>1.0005598500336139</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5874,14 +5874,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>112233</v>
+        <v>112234</v>
       </c>
       <c r="F33" s="5">
-        <v>577923</v>
+        <v>577924</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>0.98536419855176494</v>
+        <v>0.98536590356125331</v>
       </c>
       <c r="H33" s="5">
         <v>594451</v>
@@ -5891,14 +5891,14 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>102376</v>
+        <v>102377</v>
       </c>
       <c r="K33" s="5">
-        <v>588536</v>
+        <v>588537</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="3"/>
-        <v>0.99004964244319549</v>
+        <v>0.99005132466763446</v>
       </c>
       <c r="M33" s="9">
         <v>1006436</v>
@@ -5910,11 +5910,11 @@
         <v>989274</v>
       </c>
       <c r="P33" s="5">
-        <v>989985</v>
+        <v>989987</v>
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="4"/>
-        <v>0.98365420155876782</v>
+        <v>0.98365618876908223</v>
       </c>
       <c r="R33" s="5">
         <v>599279</v>
@@ -5924,14 +5924,14 @@
       </c>
       <c r="T33" s="3">
         <f t="shared" si="5"/>
-        <v>115341</v>
+        <v>115342</v>
       </c>
       <c r="U33" s="5">
-        <v>590808</v>
+        <v>590809</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="6"/>
-        <v>0.98586468072467082</v>
+        <v>0.98586634939652484</v>
       </c>
       <c r="W33" s="5">
         <v>608923</v>
@@ -5941,14 +5941,14 @@
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="7"/>
-        <v>119615</v>
+        <v>119616</v>
       </c>
       <c r="Z33" s="5">
-        <v>598471</v>
+        <v>598472</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" si="8"/>
-        <v>0.98283526817019562</v>
+        <v>0.98283691041396037</v>
       </c>
       <c r="AB33" s="5">
         <v>1019860</v>
@@ -5958,14 +5958,14 @@
       </c>
       <c r="AD33" s="3">
         <f t="shared" si="9"/>
-        <v>208795</v>
+        <v>208796</v>
       </c>
       <c r="AE33" s="5">
-        <v>1007591</v>
+        <v>1007592</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="10"/>
-        <v>0.98796991743964857</v>
+        <v>0.9879708979663876</v>
       </c>
       <c r="AG33" s="5">
         <v>610453</v>
@@ -5975,14 +5975,14 @@
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="11"/>
-        <v>103203</v>
+        <v>103204</v>
       </c>
       <c r="AJ33" s="5">
-        <v>601260</v>
+        <v>601261</v>
       </c>
       <c r="AK33" s="4">
         <f t="shared" si="12"/>
-        <v>0.98494069158477393</v>
+        <v>0.98494232971252493</v>
       </c>
       <c r="AL33" s="5">
         <v>617988</v>
@@ -5992,14 +5992,14 @@
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="13"/>
-        <v>97620</v>
+        <v>97621</v>
       </c>
       <c r="AO33" s="5">
-        <v>607251</v>
+        <v>607252</v>
       </c>
       <c r="AP33" s="4">
         <f t="shared" si="14"/>
-        <v>0.98262587623060638</v>
+        <v>0.98262749438500419</v>
       </c>
       <c r="AQ33" s="3">
         <v>1027609</v>
@@ -6009,14 +6009,14 @@
       </c>
       <c r="AS33" s="3">
         <f t="shared" si="15"/>
-        <v>158968</v>
+        <v>158969</v>
       </c>
       <c r="AT33" s="3">
-        <v>1016489</v>
+        <v>1016490</v>
       </c>
       <c r="AU33" s="4">
         <f t="shared" si="16"/>
-        <v>0.98917876351803069</v>
+        <v>0.98917973665080783</v>
       </c>
       <c r="AV33" s="5">
         <v>625585</v>
@@ -6026,14 +6026,14 @@
       </c>
       <c r="AX33" s="3">
         <f t="shared" si="17"/>
-        <v>80339</v>
+        <v>80340</v>
       </c>
       <c r="AY33" s="5">
-        <v>609868</v>
+        <v>609869</v>
       </c>
       <c r="AZ33" s="4">
         <f t="shared" si="18"/>
-        <v>0.97487631576844069</v>
+        <v>0.97487791427224113</v>
       </c>
       <c r="BA33" s="10">
         <v>617039</v>
@@ -6043,14 +6043,14 @@
       </c>
       <c r="BC33" s="3">
         <f t="shared" si="19"/>
-        <v>85341</v>
+        <v>85342</v>
       </c>
       <c r="BD33" s="5">
-        <v>616846</v>
+        <v>616847</v>
       </c>
       <c r="BE33" s="4">
         <f t="shared" si="20"/>
-        <v>0.99968721588100595</v>
+        <v>0.99968883652410945</v>
       </c>
       <c r="BF33" s="10">
         <v>1025594</v>
@@ -6060,14 +6060,14 @@
       </c>
       <c r="BH33" s="3">
         <f t="shared" si="21"/>
-        <v>198100</v>
+        <v>198101</v>
       </c>
       <c r="BI33" s="5">
-        <v>1029961</v>
+        <v>1029962</v>
       </c>
       <c r="BJ33" s="4">
         <f t="shared" si="22"/>
-        <v>1.0042580202302276</v>
+        <v>1.0042589952749335</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6484,14 +6484,14 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="0"/>
-        <v>280740</v>
+        <v>280751</v>
       </c>
       <c r="F36" s="5">
-        <v>767026</v>
+        <v>767037</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="1"/>
-        <v>0.95383329747771251</v>
+        <v>0.95384697650068206</v>
       </c>
       <c r="H36" s="5">
         <v>814447</v>
@@ -6501,14 +6501,14 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="2"/>
-        <v>265466</v>
+        <v>265476</v>
       </c>
       <c r="K36" s="5">
-        <v>778876</v>
+        <v>778886</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="3"/>
-        <v>0.95632496651101917</v>
+        <v>0.9563372447808145</v>
       </c>
       <c r="M36" s="9">
         <v>1485608</v>
@@ -6520,11 +6520,11 @@
         <v>1417521</v>
       </c>
       <c r="P36" s="5">
-        <v>1419999</v>
+        <v>1420019</v>
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="4"/>
-        <v>0.9558369367962477</v>
+        <v>0.95585039929779592</v>
       </c>
       <c r="R36" s="5">
         <v>815623</v>
@@ -6534,14 +6534,14 @@
       </c>
       <c r="T36" s="3">
         <f t="shared" si="5"/>
-        <v>268182</v>
+        <v>268193</v>
       </c>
       <c r="U36" s="5">
-        <v>778537</v>
+        <v>778548</v>
       </c>
       <c r="V36" s="4">
         <f t="shared" si="6"/>
-        <v>0.95453046321646151</v>
+        <v>0.95454394983957047</v>
       </c>
       <c r="W36" s="5">
         <v>826349</v>
@@ -6551,14 +6551,14 @@
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="7"/>
-        <v>288601</v>
+        <v>288615</v>
       </c>
       <c r="Z36" s="5">
-        <v>788753</v>
+        <v>788767</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="8"/>
-        <v>0.95450348460517287</v>
+        <v>0.95452042659941505</v>
       </c>
       <c r="AB36" s="5">
         <v>1500292</v>
@@ -6568,14 +6568,14 @@
       </c>
       <c r="AD36" s="3">
         <f t="shared" si="9"/>
-        <v>549408</v>
+        <v>549426</v>
       </c>
       <c r="AE36" s="5">
-        <v>1455724</v>
+        <v>1455742</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="10"/>
-        <v>0.97029378281027956</v>
+        <v>0.97030578047473426</v>
       </c>
       <c r="AG36" s="5">
         <v>833041</v>
@@ -6585,14 +6585,14 @@
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="11"/>
-        <v>255487</v>
+        <v>255498</v>
       </c>
       <c r="AJ36" s="5">
-        <v>802872</v>
+        <v>802883</v>
       </c>
       <c r="AK36" s="4">
         <f t="shared" si="12"/>
-        <v>0.96378449560105683</v>
+        <v>0.96379770023324185</v>
       </c>
       <c r="AL36" s="5">
         <v>845911</v>
@@ -6602,14 +6602,14 @@
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="13"/>
-        <v>252963</v>
+        <v>252974</v>
       </c>
       <c r="AO36" s="5">
-        <v>815198</v>
+        <v>815209</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="14"/>
-        <v>0.96369239790001548</v>
+        <v>0.96370540163208662</v>
       </c>
       <c r="AQ36" s="3">
         <v>1519147</v>
@@ -6619,14 +6619,14 @@
       </c>
       <c r="AS36" s="3">
         <f t="shared" si="15"/>
-        <v>450240</v>
+        <v>450259</v>
       </c>
       <c r="AT36" s="3">
-        <v>1477380</v>
+        <v>1477399</v>
       </c>
       <c r="AU36" s="4">
         <f t="shared" si="16"/>
-        <v>0.97250628148559681</v>
+        <v>0.97251878850433826</v>
       </c>
       <c r="AV36" s="5">
         <v>864672</v>
@@ -6636,14 +6636,14 @@
       </c>
       <c r="AX36" s="3">
         <f t="shared" si="17"/>
-        <v>218876</v>
+        <v>218887</v>
       </c>
       <c r="AY36" s="5">
-        <v>817737</v>
+        <v>817748</v>
       </c>
       <c r="AZ36" s="4">
         <f t="shared" si="18"/>
-        <v>0.94571930165426887</v>
+        <v>0.94573202324118277</v>
       </c>
       <c r="BA36" s="10">
         <v>838532</v>
@@ -6653,14 +6653,14 @@
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="19"/>
-        <v>226523</v>
+        <v>226531</v>
       </c>
       <c r="BD36" s="5">
-        <v>830277</v>
+        <v>830285</v>
       </c>
       <c r="BE36" s="4">
         <f t="shared" si="20"/>
-        <v>0.99015541446241762</v>
+        <v>0.99016495494507062</v>
       </c>
       <c r="BF36" s="10">
         <v>1502094</v>
@@ -6670,14 +6670,14 @@
       </c>
       <c r="BH36" s="3">
         <f t="shared" si="23"/>
-        <v>507854</v>
+        <v>507869</v>
       </c>
       <c r="BI36" s="5">
-        <v>1498504</v>
+        <v>1498519</v>
       </c>
       <c r="BJ36" s="4">
         <f t="shared" si="24"/>
-        <v>0.99761000310233583</v>
+        <v>0.99761998916179684</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6695,14 +6695,14 @@
       </c>
       <c r="E37" s="3">
         <f t="shared" si="0"/>
-        <v>268690</v>
+        <v>268698</v>
       </c>
       <c r="F37" s="5">
-        <v>609907</v>
+        <v>609915</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="1"/>
-        <v>0.93739980972493109</v>
+        <v>0.93741210536750907</v>
       </c>
       <c r="H37" s="5">
         <v>656039</v>
@@ -6712,14 +6712,14 @@
       </c>
       <c r="J37" s="3">
         <f t="shared" si="2"/>
-        <v>249928</v>
+        <v>249937</v>
       </c>
       <c r="K37" s="5">
-        <v>615197</v>
+        <v>615206</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="3"/>
-        <v>0.93774455482067376</v>
+        <v>0.9377582735172757</v>
       </c>
       <c r="M37" s="9">
         <v>844882</v>
@@ -6731,11 +6731,11 @@
         <v>786859</v>
       </c>
       <c r="P37" s="5">
-        <v>789067</v>
+        <v>789079</v>
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="4"/>
-        <v>0.93393752026910271</v>
+        <v>0.93395172343593547</v>
       </c>
       <c r="R37" s="5">
         <v>664863</v>
@@ -6745,14 +6745,14 @@
       </c>
       <c r="T37" s="3">
         <f t="shared" si="5"/>
-        <v>256844</v>
+        <v>256853</v>
       </c>
       <c r="U37" s="5">
-        <v>621971</v>
+        <v>621980</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="6"/>
-        <v>0.9354874613266192</v>
+        <v>0.93550099794995356</v>
       </c>
       <c r="W37" s="5">
         <v>670009</v>
@@ -6762,14 +6762,14 @@
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="7"/>
-        <v>275163</v>
+        <v>275174</v>
       </c>
       <c r="Z37" s="5">
-        <v>628408</v>
+        <v>628419</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="8"/>
-        <v>0.93790978927148738</v>
+        <v>0.93792620696139906</v>
       </c>
       <c r="AB37" s="5">
         <v>858143</v>
@@ -6779,14 +6779,14 @@
       </c>
       <c r="AD37" s="3">
         <f t="shared" si="9"/>
-        <v>383155</v>
+        <v>383164</v>
       </c>
       <c r="AE37" s="5">
-        <v>819526</v>
+        <v>819535</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="10"/>
-        <v>0.95499934160157451</v>
+        <v>0.95500982936410361</v>
       </c>
       <c r="AG37" s="5">
         <v>675943</v>
@@ -6796,14 +6796,14 @@
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="11"/>
-        <v>251699</v>
+        <v>251708</v>
       </c>
       <c r="AJ37" s="5">
-        <v>644676</v>
+        <v>644685</v>
       </c>
       <c r="AK37" s="4">
         <f t="shared" si="12"/>
-        <v>0.95374314106366953</v>
+        <v>0.95375645579582891</v>
       </c>
       <c r="AL37" s="5">
         <v>678429</v>
@@ -6813,14 +6813,14 @@
       </c>
       <c r="AN37" s="3">
         <f t="shared" si="13"/>
-        <v>248269</v>
+        <v>248277</v>
       </c>
       <c r="AO37" s="5">
-        <v>650787</v>
+        <v>650795</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="14"/>
-        <v>0.95925586907399296</v>
+        <v>0.95926766102274519</v>
       </c>
       <c r="AQ37" s="3">
         <v>865622</v>
@@ -6830,14 +6830,14 @@
       </c>
       <c r="AS37" s="3">
         <f t="shared" si="15"/>
-        <v>314989</v>
+        <v>314997</v>
       </c>
       <c r="AT37" s="3">
-        <v>834233</v>
+        <v>834241</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="16"/>
-        <v>0.96373821367756363</v>
+        <v>0.96374745558684971</v>
       </c>
       <c r="AV37" s="5">
         <v>690116</v>
@@ -6847,14 +6847,14 @@
       </c>
       <c r="AX37" s="3">
         <f t="shared" si="17"/>
-        <v>235057</v>
+        <v>235066</v>
       </c>
       <c r="AY37" s="5">
-        <v>658583</v>
+        <v>658592</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="18"/>
-        <v>0.95430768160715007</v>
+        <v>0.95432072289296288</v>
       </c>
       <c r="BA37" s="10">
         <v>673244</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="19"/>
-        <v>241641</v>
+        <v>241650</v>
       </c>
       <c r="BD37" s="5">
-        <v>665208</v>
+        <v>665217</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="20"/>
-        <v>0.9880637629150798</v>
+        <v>0.98807713102530437</v>
       </c>
       <c r="BF37" s="10">
         <v>856336</v>
@@ -6881,14 +6881,14 @@
       </c>
       <c r="BH37" s="3">
         <f t="shared" si="23"/>
-        <v>356959</v>
+        <v>356969</v>
       </c>
       <c r="BI37" s="5">
-        <v>848342</v>
+        <v>848352</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="24"/>
-        <v>0.99066487920629287</v>
+        <v>0.99067655686552947</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -6942,11 +6942,11 @@
         <v>33105</v>
       </c>
       <c r="P38" s="5">
-        <v>33262</v>
+        <v>33263</v>
       </c>
       <c r="Q38" s="4">
         <f t="shared" si="4"/>
-        <v>0.87941199799064063</v>
+        <v>0.87943843692991042</v>
       </c>
       <c r="R38" s="5">
         <v>25469</v>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="AD38" s="3">
         <f t="shared" si="9"/>
-        <v>15118</v>
+        <v>15119</v>
       </c>
       <c r="AE38" s="5">
-        <v>34046</v>
+        <v>34047</v>
       </c>
       <c r="AF38" s="4">
         <f t="shared" si="10"/>
-        <v>0.9142811106933777</v>
+        <v>0.91430796498200761</v>
       </c>
       <c r="AG38" s="5">
         <v>24904</v>
@@ -7041,14 +7041,14 @@
       </c>
       <c r="AS38" s="3">
         <f t="shared" si="15"/>
-        <v>13530</v>
+        <v>13531</v>
       </c>
       <c r="AT38" s="3">
-        <v>34924</v>
+        <v>34925</v>
       </c>
       <c r="AU38" s="4">
         <f t="shared" si="16"/>
-        <v>0.91726637600462257</v>
+        <v>0.91729264064716076</v>
       </c>
       <c r="AV38" s="5">
         <v>25812</v>
@@ -7092,14 +7092,14 @@
       </c>
       <c r="BH38" s="3">
         <f t="shared" si="23"/>
-        <v>15323</v>
+        <v>15324</v>
       </c>
       <c r="BI38" s="5">
-        <v>35546</v>
+        <v>35547</v>
       </c>
       <c r="BJ38" s="4">
         <f t="shared" si="24"/>
-        <v>1.0003377047334947</v>
+        <v>1.0003658467946193</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7328,14 +7328,14 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="0"/>
-        <v>105546</v>
+        <v>105547</v>
       </c>
       <c r="F40" s="5">
-        <v>258593</v>
+        <v>258594</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="1"/>
-        <v>0.94556803264601674</v>
+        <v>0.94557168923390822</v>
       </c>
       <c r="H40" s="5">
         <v>275367</v>
@@ -7345,14 +7345,14 @@
       </c>
       <c r="J40" s="3">
         <f t="shared" si="2"/>
-        <v>98771</v>
+        <v>98772</v>
       </c>
       <c r="K40" s="5">
-        <v>260333</v>
+        <v>260334</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="3"/>
-        <v>0.94540377024116906</v>
+        <v>0.94540740175838067</v>
       </c>
       <c r="M40" s="9">
         <v>339208</v>
@@ -7364,11 +7364,11 @@
         <v>320573</v>
       </c>
       <c r="P40" s="5">
-        <v>321295</v>
+        <v>321299</v>
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="4"/>
-        <v>0.94719169359213229</v>
+        <v>0.9472034857668451</v>
       </c>
       <c r="R40" s="5">
         <v>277547</v>
@@ -7378,14 +7378,14 @@
       </c>
       <c r="T40" s="3">
         <f t="shared" si="5"/>
-        <v>97295</v>
+        <v>97299</v>
       </c>
       <c r="U40" s="5">
-        <v>262669</v>
+        <v>262673</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" si="6"/>
-        <v>0.94639466468742228</v>
+        <v>0.94640907666088991</v>
       </c>
       <c r="W40" s="5">
         <v>278758</v>
@@ -7395,14 +7395,14 @@
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="7"/>
-        <v>125343</v>
+        <v>125348</v>
       </c>
       <c r="Z40" s="5">
-        <v>265217</v>
+        <v>265222</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" si="8"/>
-        <v>0.95142381563937184</v>
+        <v>0.95144175234432737</v>
       </c>
       <c r="AB40" s="5">
         <v>343140</v>
@@ -7412,14 +7412,14 @@
       </c>
       <c r="AD40" s="3">
         <f t="shared" si="9"/>
-        <v>142724</v>
+        <v>142729</v>
       </c>
       <c r="AE40" s="5">
-        <v>328420</v>
+        <v>328425</v>
       </c>
       <c r="AF40" s="4">
         <f t="shared" si="10"/>
-        <v>0.95710205746925459</v>
+        <v>0.95711662878125547</v>
       </c>
       <c r="AG40" s="5">
         <v>282101</v>
@@ -7429,14 +7429,14 @@
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="11"/>
-        <v>100015</v>
+        <v>100019</v>
       </c>
       <c r="AJ40" s="5">
-        <v>268711</v>
+        <v>268715</v>
       </c>
       <c r="AK40" s="4">
         <f t="shared" si="12"/>
-        <v>0.9525347304688746</v>
+        <v>0.95254890978762929</v>
       </c>
       <c r="AL40" s="5">
         <v>282756</v>
@@ -7446,14 +7446,14 @@
       </c>
       <c r="AN40" s="3">
         <f t="shared" si="13"/>
-        <v>99021</v>
+        <v>99025</v>
       </c>
       <c r="AO40" s="5">
-        <v>270968</v>
+        <v>270972</v>
       </c>
       <c r="AP40" s="4">
         <f t="shared" si="14"/>
-        <v>0.95831034531539561</v>
+        <v>0.95832449178797263</v>
       </c>
       <c r="AQ40" s="3">
         <v>343988</v>
@@ -7463,14 +7463,14 @@
       </c>
       <c r="AS40" s="3">
         <f t="shared" si="15"/>
-        <v>125854</v>
+        <v>125860</v>
       </c>
       <c r="AT40" s="3">
-        <v>332717</v>
+        <v>332723</v>
       </c>
       <c r="AU40" s="4">
         <f t="shared" si="16"/>
-        <v>0.96723432212751603</v>
+        <v>0.96725176459643936</v>
       </c>
       <c r="AV40" s="5">
         <v>285285</v>
@@ -7480,14 +7480,14 @@
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="17"/>
-        <v>94335</v>
+        <v>94340</v>
       </c>
       <c r="AY40" s="5">
-        <v>273381</v>
+        <v>273386</v>
       </c>
       <c r="AZ40" s="4">
         <f t="shared" si="18"/>
-        <v>0.95827330564172675</v>
+        <v>0.9582908319750425</v>
       </c>
       <c r="BA40" s="10">
         <v>276279</v>
@@ -7497,14 +7497,14 @@
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="19"/>
-        <v>95249</v>
+        <v>95256</v>
       </c>
       <c r="BD40" s="5">
-        <v>275433</v>
+        <v>275440</v>
       </c>
       <c r="BE40" s="4">
         <f t="shared" si="20"/>
-        <v>0.99693787801461564</v>
+        <v>0.99696321472135052</v>
       </c>
       <c r="BF40" s="10">
         <v>339189</v>
@@ -7514,14 +7514,14 @@
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="23"/>
-        <v>141261</v>
+        <v>141269</v>
       </c>
       <c r="BI40" s="5">
-        <v>337562</v>
+        <v>337570</v>
       </c>
       <c r="BJ40" s="4">
         <f t="shared" si="24"/>
-        <v>0.99520326425680083</v>
+        <v>0.99522684992732668</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7539,14 +7539,14 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" si="0"/>
-        <v>326695</v>
+        <v>326713</v>
       </c>
       <c r="F41" s="5">
-        <v>832919</v>
+        <v>832937</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="1"/>
-        <v>0.95442711615808595</v>
+        <v>0.95444774203898286</v>
       </c>
       <c r="H41" s="5">
         <v>878008</v>
@@ -7556,14 +7556,14 @@
       </c>
       <c r="J41" s="3">
         <f t="shared" si="2"/>
-        <v>326506</v>
+        <v>326520</v>
       </c>
       <c r="K41" s="5">
-        <v>839630</v>
+        <v>839644</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="3"/>
-        <v>0.95628969212125625</v>
+        <v>0.95630563730626605</v>
       </c>
       <c r="M41" s="9">
         <v>999035</v>
@@ -7575,11 +7575,11 @@
         <v>948683</v>
       </c>
       <c r="P41" s="5">
-        <v>950989</v>
+        <v>951004</v>
       </c>
       <c r="Q41" s="4">
         <f t="shared" si="4"/>
-        <v>0.95190759082514631</v>
+        <v>0.95192260531412809</v>
       </c>
       <c r="R41" s="5">
         <v>889467</v>
@@ -7589,14 +7589,14 @@
       </c>
       <c r="T41" s="3">
         <f t="shared" si="5"/>
-        <v>328387</v>
+        <v>328403</v>
       </c>
       <c r="U41" s="5">
-        <v>849371</v>
+        <v>849387</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" si="6"/>
-        <v>0.95492131804777469</v>
+        <v>0.95493930634863355</v>
       </c>
       <c r="W41" s="5">
         <v>894020</v>
@@ -7606,14 +7606,14 @@
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="7"/>
-        <v>361324</v>
+        <v>361341</v>
       </c>
       <c r="Z41" s="5">
-        <v>855262</v>
+        <v>855279</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" si="8"/>
-        <v>0.95664750229301354</v>
+        <v>0.95666651752757204</v>
       </c>
       <c r="AB41" s="5">
         <v>1012178</v>
@@ -7623,14 +7623,14 @@
       </c>
       <c r="AD41" s="3">
         <f t="shared" si="9"/>
-        <v>420698</v>
+        <v>420712</v>
       </c>
       <c r="AE41" s="5">
-        <v>977748</v>
+        <v>977762</v>
       </c>
       <c r="AF41" s="4">
         <f t="shared" si="10"/>
-        <v>0.96598424387805304</v>
+        <v>0.9659980754373243</v>
       </c>
       <c r="AG41" s="5">
         <v>904846</v>
@@ -7640,14 +7640,14 @@
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="11"/>
-        <v>322106</v>
+        <v>322116</v>
       </c>
       <c r="AJ41" s="5">
-        <v>873162</v>
+        <v>873172</v>
       </c>
       <c r="AK41" s="4">
         <f t="shared" si="12"/>
-        <v>0.9649840967413239</v>
+        <v>0.96499514834568534</v>
       </c>
       <c r="AL41" s="5">
         <v>910192</v>
@@ -7657,14 +7657,14 @@
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="13"/>
-        <v>324158</v>
+        <v>324170</v>
       </c>
       <c r="AO41" s="5">
-        <v>879133</v>
+        <v>879145</v>
       </c>
       <c r="AP41" s="4">
         <f t="shared" si="14"/>
-        <v>0.96587643046741789</v>
+        <v>0.96588961449891886</v>
       </c>
       <c r="AQ41" s="3">
         <v>1025826</v>
@@ -7674,14 +7674,14 @@
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="15"/>
-        <v>359834</v>
+        <v>359853</v>
       </c>
       <c r="AT41" s="3">
-        <v>993412</v>
+        <v>993431</v>
       </c>
       <c r="AU41" s="4">
         <f t="shared" si="16"/>
-        <v>0.96840204869051871</v>
+        <v>0.9684205703501374</v>
       </c>
       <c r="AV41" s="5">
         <v>923071</v>
@@ -7691,14 +7691,14 @@
       </c>
       <c r="AX41" s="3">
         <f t="shared" si="17"/>
-        <v>308181</v>
+        <v>308194</v>
       </c>
       <c r="AY41" s="5">
-        <v>890907</v>
+        <v>890920</v>
       </c>
       <c r="AZ41" s="4">
         <f t="shared" si="18"/>
-        <v>0.96515544308075973</v>
+        <v>0.96516952650446175</v>
       </c>
       <c r="BA41" s="11">
         <v>907892</v>
@@ -7708,14 +7708,14 @@
       </c>
       <c r="BC41" s="3">
         <f t="shared" si="19"/>
-        <v>315646</v>
+        <v>315658</v>
       </c>
       <c r="BD41" s="5">
-        <v>897954</v>
+        <v>897966</v>
       </c>
       <c r="BE41" s="4">
         <f t="shared" si="20"/>
-        <v>0.98905376410410051</v>
+        <v>0.98906698153524863</v>
       </c>
       <c r="BF41" s="11">
         <v>1023930</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="BH41" s="3">
         <f t="shared" si="23"/>
-        <v>403359</v>
+        <v>403376</v>
       </c>
       <c r="BI41" s="5">
-        <v>1012266</v>
+        <v>1012283</v>
       </c>
       <c r="BJ41" s="4">
         <f t="shared" si="24"/>
-        <v>0.98860859629076203</v>
+        <v>0.98862519898821211</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7834,14 +7834,14 @@
       </c>
       <c r="AD42" s="3">
         <f t="shared" si="9"/>
-        <v>9566</v>
+        <v>9567</v>
       </c>
       <c r="AE42" s="5">
-        <v>19843</v>
+        <v>19844</v>
       </c>
       <c r="AF42" s="4">
         <f t="shared" si="10"/>
-        <v>0.95804364619544224</v>
+        <v>0.95809192738509075</v>
       </c>
       <c r="AG42" s="5">
         <v>18585</v>
@@ -7851,14 +7851,14 @@
       </c>
       <c r="AI42" s="3">
         <f t="shared" si="11"/>
-        <v>7692</v>
+        <v>7693</v>
       </c>
       <c r="AJ42" s="5">
-        <v>17754</v>
+        <v>17755</v>
       </c>
       <c r="AK42" s="4">
         <f t="shared" si="12"/>
-        <v>0.95528652138821635</v>
+        <v>0.95534032822168413</v>
       </c>
       <c r="AL42" s="5">
         <v>18498</v>
@@ -7868,14 +7868,14 @@
       </c>
       <c r="AN42" s="3">
         <f t="shared" si="13"/>
-        <v>7819</v>
+        <v>7820</v>
       </c>
       <c r="AO42" s="5">
-        <v>17815</v>
+        <v>17816</v>
       </c>
       <c r="AP42" s="4">
         <f t="shared" si="14"/>
-        <v>0.96307708941507186</v>
+        <v>0.96313114931343924</v>
       </c>
       <c r="AQ42" s="3">
         <v>20775</v>
@@ -7885,14 +7885,14 @@
       </c>
       <c r="AS42" s="3">
         <f t="shared" si="15"/>
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="AT42" s="3">
-        <v>20050</v>
+        <v>20051</v>
       </c>
       <c r="AU42" s="4">
         <f t="shared" si="16"/>
-        <v>0.96510228640192541</v>
+        <v>0.96515042117930205</v>
       </c>
       <c r="AV42" s="5">
         <v>18672</v>
@@ -7902,14 +7902,14 @@
       </c>
       <c r="AX42" s="3">
         <f t="shared" si="17"/>
-        <v>7436</v>
+        <v>7437</v>
       </c>
       <c r="AY42" s="5">
-        <v>17993</v>
+        <v>17994</v>
       </c>
       <c r="AZ42" s="4">
         <f t="shared" si="18"/>
-        <v>0.96363538988860331</v>
+        <v>0.96368894601542421</v>
       </c>
       <c r="BA42" s="10">
         <v>18422</v>
@@ -7919,14 +7919,14 @@
       </c>
       <c r="BC42" s="3">
         <f t="shared" si="19"/>
-        <v>7561</v>
+        <v>7562</v>
       </c>
       <c r="BD42" s="5">
-        <v>18115</v>
+        <v>18116</v>
       </c>
       <c r="BE42" s="4">
         <f t="shared" si="20"/>
-        <v>0.9833351427640864</v>
+        <v>0.98338942568667898</v>
       </c>
       <c r="BF42" s="10">
         <v>20562</v>
@@ -7961,14 +7961,14 @@
       </c>
       <c r="E43" s="3">
         <f t="shared" si="0"/>
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="F43" s="5">
-        <v>3156</v>
+        <v>3157</v>
       </c>
       <c r="G43" s="4">
         <f t="shared" si="1"/>
-        <v>0.94040524433849826</v>
+        <v>0.94070321811680568</v>
       </c>
       <c r="H43" s="5">
         <v>3369</v>
@@ -7978,14 +7978,14 @@
       </c>
       <c r="J43" s="3">
         <f t="shared" si="2"/>
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="K43" s="5">
-        <v>3201</v>
+        <v>3202</v>
       </c>
       <c r="L43" s="4">
         <f t="shared" si="3"/>
-        <v>0.95013357079252003</v>
+        <v>0.95043039477589786</v>
       </c>
       <c r="M43" s="9">
         <v>4189</v>
@@ -7997,11 +7997,11 @@
         <v>4005</v>
       </c>
       <c r="P43" s="5">
-        <v>4013</v>
+        <v>4014</v>
       </c>
       <c r="Q43" s="4">
         <f t="shared" si="4"/>
-        <v>0.95798519933158277</v>
+        <v>0.95822391978992605</v>
       </c>
       <c r="R43" s="5">
         <v>3398</v>
@@ -8011,14 +8011,14 @@
       </c>
       <c r="T43" s="3">
         <f t="shared" si="5"/>
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="U43" s="5">
-        <v>3262</v>
+        <v>3263</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" si="6"/>
-        <v>0.95997645673925835</v>
+        <v>0.96027074749852859</v>
       </c>
       <c r="W43" s="5">
         <v>3433</v>
@@ -8028,14 +8028,14 @@
       </c>
       <c r="Y43" s="3">
         <f t="shared" si="7"/>
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="Z43" s="5">
-        <v>3320</v>
+        <v>3321</v>
       </c>
       <c r="AA43" s="4">
         <f t="shared" si="8"/>
-        <v>0.96708418293038156</v>
+        <v>0.96737547334692686</v>
       </c>
       <c r="AB43" s="5">
         <v>4306</v>
@@ -8045,14 +8045,14 @@
       </c>
       <c r="AD43" s="3">
         <f t="shared" si="9"/>
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="AE43" s="5">
-        <v>4184</v>
+        <v>4185</v>
       </c>
       <c r="AF43" s="4">
         <f t="shared" si="10"/>
-        <v>0.97166744078030653</v>
+        <v>0.97189967487227125</v>
       </c>
       <c r="AG43" s="5">
         <v>3505</v>
@@ -8062,14 +8062,14 @@
       </c>
       <c r="AI43" s="3">
         <f t="shared" si="11"/>
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="AJ43" s="5">
-        <v>3339</v>
+        <v>3340</v>
       </c>
       <c r="AK43" s="4">
         <f t="shared" si="12"/>
-        <v>0.95263908701854494</v>
+        <v>0.95292439372325255</v>
       </c>
       <c r="AL43" s="5">
         <v>3511</v>
@@ -8079,14 +8079,14 @@
       </c>
       <c r="AN43" s="3">
         <f t="shared" si="13"/>
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="AO43" s="5">
-        <v>3372</v>
+        <v>3373</v>
       </c>
       <c r="AP43" s="4">
         <f t="shared" si="14"/>
-        <v>0.96041013956137855</v>
+        <v>0.96069495870122468</v>
       </c>
       <c r="AQ43" s="3">
         <v>4405</v>
@@ -8096,14 +8096,14 @@
       </c>
       <c r="AS43" s="3">
         <f t="shared" si="15"/>
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="AT43" s="3">
-        <v>4268</v>
+        <v>4269</v>
       </c>
       <c r="AU43" s="4">
         <f t="shared" si="16"/>
-        <v>0.96889897843359818</v>
+        <v>0.96912599318955728</v>
       </c>
       <c r="AV43" s="5">
         <v>3534</v>
@@ -8113,14 +8113,14 @@
       </c>
       <c r="AX43" s="3">
         <f t="shared" si="17"/>
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="AY43" s="5">
-        <v>3399</v>
+        <v>3400</v>
       </c>
       <c r="AZ43" s="4">
         <f t="shared" si="18"/>
-        <v>0.96179966044142617</v>
+        <v>0.96208262591963778</v>
       </c>
       <c r="BA43" s="10">
         <v>3464</v>
@@ -8130,14 +8130,14 @@
       </c>
       <c r="BC43" s="3">
         <f t="shared" si="19"/>
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="BD43" s="5">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="BE43" s="4">
         <f t="shared" si="20"/>
-        <v>0.99653579676674364</v>
+        <v>0.99682448036951499</v>
       </c>
       <c r="BF43" s="10">
         <v>4361</v>
@@ -8147,14 +8147,14 @@
       </c>
       <c r="BH43" s="3">
         <f t="shared" si="23"/>
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="BI43" s="5">
-        <v>4339</v>
+        <v>4340</v>
       </c>
       <c r="BJ43" s="4">
         <f t="shared" si="24"/>
-        <v>0.99495528548498047</v>
+        <v>0.9951845906902087</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8172,14 +8172,14 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="0"/>
-        <v>151687</v>
+        <v>151688</v>
       </c>
       <c r="F44" s="5">
-        <v>296319</v>
+        <v>296320</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="1"/>
-        <v>0.87114982639858651</v>
+        <v>0.87115276630398031</v>
       </c>
       <c r="H44" s="5">
         <v>343940</v>
@@ -8189,14 +8189,14 @@
       </c>
       <c r="J44" s="3">
         <f t="shared" si="2"/>
-        <v>148673</v>
+        <v>148674</v>
       </c>
       <c r="K44" s="5">
-        <v>299523</v>
+        <v>299524</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" si="3"/>
-        <v>0.87085828923649478</v>
+        <v>0.87086119672035822</v>
       </c>
       <c r="M44" s="9">
         <v>415294</v>
@@ -8208,11 +8208,11 @@
         <v>362232</v>
       </c>
       <c r="P44" s="5">
-        <v>363093</v>
+        <v>363094</v>
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="4"/>
-        <v>0.87430350546841518</v>
+        <v>0.87430591340110864</v>
       </c>
       <c r="R44" s="5">
         <v>349377</v>
@@ -8222,14 +8222,14 @@
       </c>
       <c r="T44" s="3">
         <f t="shared" si="5"/>
-        <v>152718</v>
+        <v>152719</v>
       </c>
       <c r="U44" s="5">
-        <v>304257</v>
+        <v>304258</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" si="6"/>
-        <v>0.87085583767677899</v>
+        <v>0.87085869991441911</v>
       </c>
       <c r="W44" s="5">
         <v>352323</v>
@@ -8239,14 +8239,14 @@
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="7"/>
-        <v>164138</v>
+        <v>164139</v>
       </c>
       <c r="Z44" s="5">
-        <v>307798</v>
+        <v>307799</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="8"/>
-        <v>0.87362448662165115</v>
+        <v>0.87362732492627504</v>
       </c>
       <c r="AB44" s="5">
         <v>424236</v>
@@ -8256,14 +8256,14 @@
       </c>
       <c r="AD44" s="3">
         <f t="shared" si="9"/>
-        <v>208460</v>
+        <v>208462</v>
       </c>
       <c r="AE44" s="5">
-        <v>382946</v>
+        <v>382948</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="10"/>
-        <v>0.90267209760604949</v>
+        <v>0.90267681196315264</v>
       </c>
       <c r="AG44" s="5">
         <v>358309</v>
@@ -8273,14 +8273,14 @@
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="11"/>
-        <v>154197</v>
+        <v>154198</v>
       </c>
       <c r="AJ44" s="5">
-        <v>319716</v>
+        <v>319717</v>
       </c>
       <c r="AK44" s="4">
         <f t="shared" si="12"/>
-        <v>0.89229129047833011</v>
+        <v>0.89229408136552524</v>
       </c>
       <c r="AL44" s="5">
         <v>359722</v>
@@ -8290,14 +8290,14 @@
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="13"/>
-        <v>150211</v>
+        <v>150213</v>
       </c>
       <c r="AO44" s="5">
-        <v>323552</v>
+        <v>323554</v>
       </c>
       <c r="AP44" s="4">
         <f t="shared" si="14"/>
-        <v>0.89945013093444381</v>
+        <v>0.89945569078343834</v>
       </c>
       <c r="AQ44" s="3">
         <v>432157</v>
@@ -8307,14 +8307,14 @@
       </c>
       <c r="AS44" s="3">
         <f t="shared" si="15"/>
-        <v>178594</v>
+        <v>178597</v>
       </c>
       <c r="AT44" s="3">
-        <v>391661</v>
+        <v>391664</v>
       </c>
       <c r="AU44" s="4">
         <f t="shared" si="16"/>
-        <v>0.90629331469813057</v>
+        <v>0.90630025661970071</v>
       </c>
       <c r="AV44" s="5">
         <v>367733</v>
@@ -8324,14 +8324,14 @@
       </c>
       <c r="AX44" s="3">
         <f t="shared" si="17"/>
-        <v>145689</v>
+        <v>145692</v>
       </c>
       <c r="AY44" s="5">
-        <v>327659</v>
+        <v>327662</v>
       </c>
       <c r="AZ44" s="4">
         <f t="shared" si="18"/>
-        <v>0.89102419418436751</v>
+        <v>0.89103235227733169</v>
       </c>
       <c r="BA44" s="10">
         <v>337773</v>
@@ -8341,14 +8341,14 @@
       </c>
       <c r="BC44" s="3">
         <f t="shared" si="19"/>
-        <v>150752</v>
+        <v>150755</v>
       </c>
       <c r="BD44" s="5">
-        <v>331420</v>
+        <v>331423</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="20"/>
-        <v>0.9811915102746519</v>
+        <v>0.9812003919792287</v>
       </c>
       <c r="BF44" s="10">
         <v>408499</v>
@@ -8358,14 +8358,14 @@
       </c>
       <c r="BH44" s="3">
         <f t="shared" si="23"/>
-        <v>201483</v>
+        <v>201486</v>
       </c>
       <c r="BI44" s="5">
-        <v>400217</v>
+        <v>400220</v>
       </c>
       <c r="BJ44" s="4">
         <f t="shared" si="24"/>
-        <v>0.97972577656248849</v>
+        <v>0.97973312052171491</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8383,14 +8383,14 @@
       </c>
       <c r="E45" s="3">
         <f t="shared" si="0"/>
-        <v>112351</v>
+        <v>112352</v>
       </c>
       <c r="F45" s="5">
-        <v>232575</v>
+        <v>232576</v>
       </c>
       <c r="G45" s="4">
         <f t="shared" si="1"/>
-        <v>0.92966039364916941</v>
+        <v>0.9296643908990615</v>
       </c>
       <c r="H45" s="5">
         <v>249985</v>
@@ -8400,14 +8400,14 @@
       </c>
       <c r="J45" s="3">
         <f t="shared" si="2"/>
-        <v>104747</v>
+        <v>104748</v>
       </c>
       <c r="K45" s="5">
-        <v>234325</v>
+        <v>234326</v>
       </c>
       <c r="L45" s="4">
         <f t="shared" si="3"/>
-        <v>0.93735624137448248</v>
+        <v>0.93736024161449683</v>
       </c>
       <c r="M45" s="9">
         <v>300587</v>
@@ -8419,11 +8419,11 @@
         <v>284476</v>
       </c>
       <c r="P45" s="5">
-        <v>285014</v>
+        <v>285015</v>
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="4"/>
-        <v>0.94819137221503258</v>
+        <v>0.94819469903888054</v>
       </c>
       <c r="R45" s="5">
         <v>247712</v>
@@ -8433,14 +8433,14 @@
       </c>
       <c r="T45" s="3">
         <f t="shared" si="5"/>
-        <v>109592</v>
+        <v>109593</v>
       </c>
       <c r="U45" s="5">
-        <v>235851</v>
+        <v>235852</v>
       </c>
       <c r="V45" s="4">
         <f t="shared" si="6"/>
-        <v>0.95211778194031782</v>
+        <v>0.95212181888644876</v>
       </c>
       <c r="W45" s="5">
         <v>250023</v>
@@ -8450,14 +8450,14 @@
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="7"/>
-        <v>116272</v>
+        <v>116273</v>
       </c>
       <c r="Z45" s="5">
-        <v>237774</v>
+        <v>237775</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="8"/>
-        <v>0.95100850721733599</v>
+        <v>0.95101250684936989</v>
       </c>
       <c r="AB45" s="5">
         <v>306096</v>
@@ -8467,14 +8467,14 @@
       </c>
       <c r="AD45" s="3">
         <f t="shared" si="9"/>
-        <v>151896</v>
+        <v>151897</v>
       </c>
       <c r="AE45" s="5">
-        <v>293862</v>
+        <v>293863</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="10"/>
-        <v>0.96003214677748161</v>
+        <v>0.96003541372641266</v>
       </c>
       <c r="AG45" s="5">
         <v>252706</v>
@@ -8501,14 +8501,14 @@
       </c>
       <c r="AN45" s="3">
         <f t="shared" si="13"/>
-        <v>96696</v>
+        <v>96697</v>
       </c>
       <c r="AO45" s="5">
-        <v>246023</v>
+        <v>246024</v>
       </c>
       <c r="AP45" s="4">
         <f t="shared" si="14"/>
-        <v>0.96654723459758463</v>
+        <v>0.96655116328406765</v>
       </c>
       <c r="AQ45" s="3">
         <v>310997</v>
@@ -8535,14 +8535,14 @@
       </c>
       <c r="AX45" s="3">
         <f t="shared" si="17"/>
-        <v>98677</v>
+        <v>98678</v>
       </c>
       <c r="AY45" s="5">
-        <v>248519</v>
+        <v>248520</v>
       </c>
       <c r="AZ45" s="4">
         <f t="shared" si="18"/>
-        <v>0.95820465069652494</v>
+        <v>0.9582085063560547</v>
       </c>
       <c r="BA45" s="10">
         <v>254394</v>
@@ -8552,14 +8552,14 @@
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="19"/>
-        <v>102917</v>
+        <v>102918</v>
       </c>
       <c r="BD45" s="5">
-        <v>250485</v>
+        <v>250486</v>
       </c>
       <c r="BE45" s="4">
         <f t="shared" si="20"/>
-        <v>0.98463407155829152</v>
+        <v>0.98463800246861166</v>
       </c>
       <c r="BF45" s="10">
         <v>309142</v>
@@ -8569,14 +8569,14 @@
       </c>
       <c r="BH45" s="3">
         <f t="shared" si="23"/>
-        <v>148075</v>
+        <v>148076</v>
       </c>
       <c r="BI45" s="5">
-        <v>304828</v>
+        <v>304829</v>
       </c>
       <c r="BJ45" s="4">
         <f t="shared" si="24"/>
-        <v>0.98604524781491998</v>
+        <v>0.98604848257435096</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8594,14 +8594,14 @@
       </c>
       <c r="E46" s="3">
         <f t="shared" si="0"/>
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="F46" s="5">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="G46" s="4">
         <f t="shared" si="1"/>
-        <v>0.92473591549295775</v>
+        <v>0.92517605633802813</v>
       </c>
       <c r="H46" s="5">
         <v>2410</v>
@@ -8611,14 +8611,14 @@
       </c>
       <c r="J46" s="3">
         <f t="shared" si="2"/>
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="K46" s="5">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="L46" s="4">
         <f t="shared" si="3"/>
-        <v>0.9286307053941909</v>
+        <v>0.929045643153527</v>
       </c>
       <c r="M46" s="9">
         <v>5863</v>
@@ -8630,11 +8630,11 @@
         <v>5485</v>
       </c>
       <c r="P46" s="5">
-        <v>5538</v>
+        <v>5539</v>
       </c>
       <c r="Q46" s="4">
         <f t="shared" si="4"/>
-        <v>0.94456762749445677</v>
+        <v>0.94473818864062764</v>
       </c>
       <c r="R46" s="5">
         <v>2354</v>
@@ -8644,14 +8644,14 @@
       </c>
       <c r="T46" s="3">
         <f t="shared" si="5"/>
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="U46" s="5">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="V46" s="4">
         <f t="shared" si="6"/>
-        <v>0.90186915887850472</v>
+        <v>0.90229396771452841</v>
       </c>
       <c r="W46" s="5">
         <v>2487</v>
@@ -8661,14 +8661,14 @@
       </c>
       <c r="Y46" s="3">
         <f t="shared" si="7"/>
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="Z46" s="5">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="AA46" s="4">
         <f t="shared" si="8"/>
-        <v>0.89947728186570164</v>
+        <v>0.89987937273823881</v>
       </c>
       <c r="AB46" s="5">
         <v>6137</v>
@@ -8678,14 +8678,14 @@
       </c>
       <c r="AD46" s="3">
         <f t="shared" si="9"/>
-        <v>4053</v>
+        <v>4054</v>
       </c>
       <c r="AE46" s="5">
-        <v>6173</v>
+        <v>6174</v>
       </c>
       <c r="AF46" s="4">
         <f t="shared" si="10"/>
-        <v>1.0058660583346912</v>
+        <v>1.0060290043995437</v>
       </c>
       <c r="AG46" s="5">
         <v>2383</v>
@@ -8695,14 +8695,14 @@
       </c>
       <c r="AI46" s="3">
         <f t="shared" si="11"/>
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="AJ46" s="5">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="AK46" s="4">
         <f t="shared" si="12"/>
-        <v>0.99790180444817456</v>
+        <v>0.99832144355853969</v>
       </c>
       <c r="AL46" s="5">
         <v>2468</v>
@@ -8712,14 +8712,14 @@
       </c>
       <c r="AN46" s="3">
         <f t="shared" si="13"/>
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="AO46" s="5">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="AP46" s="4">
         <f t="shared" si="14"/>
-        <v>0.99797406807131284</v>
+        <v>0.99837925445705022</v>
       </c>
       <c r="AQ46" s="3">
         <v>6357</v>
@@ -8729,14 +8729,14 @@
       </c>
       <c r="AS46" s="3">
         <f t="shared" si="15"/>
-        <v>3898</v>
+        <v>3899</v>
       </c>
       <c r="AT46" s="3">
-        <v>6393</v>
+        <v>6394</v>
       </c>
       <c r="AU46" s="4">
         <f t="shared" si="16"/>
-        <v>1.005663048607834</v>
+        <v>1.0058203555136072</v>
       </c>
       <c r="AV46" s="5">
         <v>2401</v>
@@ -8746,14 +8746,14 @@
       </c>
       <c r="AX46" s="3">
         <f t="shared" si="17"/>
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="AY46" s="5">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="AZ46" s="4">
         <f t="shared" si="18"/>
-        <v>0.96709704289879217</v>
+        <v>0.96751353602665557</v>
       </c>
       <c r="BA46" s="10">
         <v>2316</v>
@@ -8763,14 +8763,14 @@
       </c>
       <c r="BC46" s="3">
         <f t="shared" si="19"/>
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="BD46" s="5">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="BE46" s="4">
         <f t="shared" si="20"/>
-        <v>1.0341105354058722</v>
+        <v>1.0345423143350605</v>
       </c>
       <c r="BF46" s="10">
         <v>6380</v>
@@ -8780,14 +8780,14 @@
       </c>
       <c r="BH46" s="3">
         <f t="shared" si="23"/>
-        <v>4303</v>
+        <v>4304</v>
       </c>
       <c r="BI46" s="5">
-        <v>6604</v>
+        <v>6605</v>
       </c>
       <c r="BJ46" s="4">
         <f t="shared" si="24"/>
-        <v>1.0351097178683386</v>
+        <v>1.0352664576802508</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9002,10 +9002,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="18" t="s">
+      <c r="A48" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="18"/>
+      <c r="B48" s="24"/>
       <c r="C48" s="7">
         <f>SUM(C10:C47)</f>
         <v>7396603</v>
@@ -9016,15 +9016,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>2891868</v>
+        <v>2891942</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>6970382</v>
+        <v>6970456</v>
       </c>
       <c r="G48" s="6">
         <f>F48/C48</f>
-        <v>0.94237611508958907</v>
+        <v>0.94238611968223795</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -9036,15 +9036,15 @@
       </c>
       <c r="J48" s="8">
         <f t="shared" ref="J48" si="25">K48-I48</f>
-        <v>2779640</v>
+        <v>2779712</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>7078188</v>
+        <v>7078260</v>
       </c>
       <c r="L48" s="6">
         <f t="shared" ref="L48" si="26">K48/H48</f>
-        <v>0.94431491625731434</v>
+        <v>0.94432452191825045</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -9056,15 +9056,15 @@
       </c>
       <c r="O48" s="7">
         <f t="shared" ref="O48" si="27">P48-N48</f>
-        <v>4723053</v>
+        <v>4723168</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>11176104</v>
+        <v>11176219</v>
       </c>
       <c r="Q48" s="6">
         <f t="shared" ref="Q48" si="28">P48/M48</f>
-        <v>0.94383164551242882</v>
+        <v>0.94384135736185637</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -9076,15 +9076,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>2871327</v>
+        <v>2871406</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>7104382</v>
+        <v>7104461</v>
       </c>
       <c r="V48" s="6">
         <f>U48/R48</f>
-        <v>0.94179842275805636</v>
+        <v>0.94180889546003066</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -9096,15 +9096,15 @@
       </c>
       <c r="Y48" s="8">
         <f t="shared" ref="Y48" si="29">Z48-X48</f>
-        <v>3037697</v>
+        <v>3037784</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>7205272</v>
+        <v>7205359</v>
       </c>
       <c r="AA48" s="6">
         <f t="shared" ref="AA48" si="30">Z48/W48</f>
-        <v>0.9442013157777488</v>
+        <v>0.94421271652909755</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -9116,15 +9116,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>5143089</v>
+        <v>5143197</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>11573900</v>
+        <v>11574008</v>
       </c>
       <c r="AF48" s="6">
         <f>AE48/AB48</f>
-        <v>0.96125368363334773</v>
+        <v>0.96126265341862605</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -9136,15 +9136,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>2802395</v>
+        <v>2802471</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7356139</v>
+        <v>7356215</v>
       </c>
       <c r="AK48" s="6">
         <f>AJ48/AG48</f>
-        <v>0.95452877455406204</v>
+        <v>0.95453863627457414</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -9156,15 +9156,15 @@
       </c>
       <c r="AN48" s="8">
         <f t="shared" ref="AN48" si="31">AO48-AM48</f>
-        <v>2784588</v>
+        <v>2784669</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>7459724</v>
+        <v>7459805</v>
       </c>
       <c r="AP48" s="6">
         <f t="shared" ref="AP48" si="32">AO48/AL48</f>
-        <v>0.95646941511782768</v>
+        <v>0.956479800759793</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -9176,15 +9176,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>4439999</v>
+        <v>4440120</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>11780945</v>
+        <v>11781066</v>
       </c>
       <c r="AU48" s="6">
         <f>AT48/AQ48</f>
-        <v>0.96326273271088225</v>
+        <v>0.9632726262118414</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -9196,15 +9196,15 @@
       </c>
       <c r="AX48" s="8">
         <f t="shared" ref="AX48" si="33">AY48-AW48</f>
-        <v>2608272</v>
+        <v>2608360</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>7517038</v>
+        <v>7517126</v>
       </c>
       <c r="AZ48" s="6">
         <f t="shared" ref="AZ48" si="34">AY48/AV48</f>
-        <v>0.94123113712592765</v>
+        <v>0.94124215587294835</v>
       </c>
       <c r="BA48" s="7">
         <f>SUM(BA10:BA47)</f>
@@ -9216,15 +9216,15 @@
       </c>
       <c r="BC48" s="8">
         <f t="shared" ref="BC48" si="35">BD48-BB48</f>
-        <v>2771531</v>
+        <v>2771618</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>7629900</v>
+        <v>7629987</v>
       </c>
       <c r="BE48" s="6">
         <f t="shared" ref="BE48" si="36">BD48/BA48</f>
-        <v>0.98814316271084768</v>
+        <v>0.98815443002171099</v>
       </c>
       <c r="BF48" s="7">
         <f>SUM(BF10:BF47)</f>
@@ -9236,19 +9236,25 @@
       </c>
       <c r="BH48" s="8">
         <f>BI48-BG48</f>
-        <v>5013702</v>
+        <v>5013827</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>12006083</v>
+        <v>12006208</v>
       </c>
       <c r="BJ48" s="6">
         <f>BI48/BF48</f>
-        <v>0.99491771765829184</v>
+        <v>0.99492807613363365</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="AB8:AF8"/>
+    <mergeCell ref="AG8:AK8"/>
+    <mergeCell ref="W8:AA8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="M8:Q8"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A8:A9"/>
@@ -9259,12 +9265,6 @@
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AL8:AP8"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="AB8:AF8"/>
-    <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="W8:AA8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="M8:Q8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-1-2022-2023.xlsx
+++ b/gstdatabase/GSTR-1-2022-2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CA6A26-24CC-4ABA-B380-BC6D0B0A75CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8230C029-726B-4868-85D4-DD85D883443A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -182,10 +182,10 @@
     <t>Gujarat</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -1021,14 +1021,14 @@
       </c>
       <c r="E10" s="3">
         <f>F10-D10</f>
-        <v>38323</v>
+        <v>38324</v>
       </c>
       <c r="F10" s="5">
-        <v>63071</v>
+        <v>63072</v>
       </c>
       <c r="G10" s="4">
         <f>F10/C10</f>
-        <v>0.95075220838734964</v>
+        <v>0.95076728270372934</v>
       </c>
       <c r="H10" s="5">
         <v>68361</v>
@@ -1038,14 +1038,14 @@
       </c>
       <c r="J10" s="3">
         <f>K10-I10</f>
-        <v>36250</v>
+        <v>36251</v>
       </c>
       <c r="K10" s="5">
-        <v>64494</v>
+        <v>64495</v>
       </c>
       <c r="L10" s="4">
         <f>K10/H10</f>
-        <v>0.94343265897222095</v>
+        <v>0.94344728719591575</v>
       </c>
       <c r="M10" s="9">
         <v>109205</v>
@@ -1057,11 +1057,11 @@
         <v>101752</v>
       </c>
       <c r="P10" s="5">
-        <v>102092</v>
+        <v>102093</v>
       </c>
       <c r="Q10" s="4">
         <f>P10/M10</f>
-        <v>0.93486561970605742</v>
+        <v>0.93487477679593423</v>
       </c>
       <c r="R10" s="5">
         <v>68216</v>
@@ -1207,14 +1207,14 @@
       </c>
       <c r="BH10" s="3">
         <f>BI10-BG10</f>
-        <v>74256</v>
+        <v>74257</v>
       </c>
       <c r="BI10" s="5">
-        <v>117782</v>
+        <v>117783</v>
       </c>
       <c r="BJ10" s="4">
         <f>BI10/BF10</f>
-        <v>1.0018628309927444</v>
+        <v>1.0018713370703367</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1316,14 +1316,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD47" si="9">AE11-AC11</f>
-        <v>49060</v>
+        <v>49061</v>
       </c>
       <c r="AE11" s="5">
-        <v>97566</v>
+        <v>97567</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF47" si="10">AE11/AB11</f>
-        <v>0.97675396444017304</v>
+        <v>0.9767639756527311</v>
       </c>
       <c r="AG11" s="5">
         <v>44744</v>
@@ -1367,14 +1367,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS47" si="15">AT11-AR11</f>
-        <v>43287</v>
+        <v>43289</v>
       </c>
       <c r="AT11" s="3">
-        <v>98530</v>
+        <v>98532</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU47" si="16">AT11/AQ11</f>
-        <v>0.97778086514701945</v>
+        <v>0.97780071252071565</v>
       </c>
       <c r="AV11" s="5">
         <v>46153</v>
@@ -1384,14 +1384,14 @@
       </c>
       <c r="AX11" s="3">
         <f t="shared" ref="AX11:AX47" si="17">AY11-AW11</f>
-        <v>14951</v>
+        <v>14952</v>
       </c>
       <c r="AY11" s="5">
-        <v>43456</v>
+        <v>43457</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" ref="AZ11:AZ47" si="18">AY11/AV11</f>
-        <v>0.94156392867202565</v>
+        <v>0.94158559573592182</v>
       </c>
       <c r="BA11" s="10">
         <v>44735</v>
@@ -1401,14 +1401,14 @@
       </c>
       <c r="BC11" s="3">
         <f t="shared" ref="BC11:BC47" si="19">BD11-BB11</f>
-        <v>16368</v>
+        <v>16369</v>
       </c>
       <c r="BD11" s="5">
-        <v>44640</v>
+        <v>44641</v>
       </c>
       <c r="BE11" s="4">
         <f t="shared" ref="BE11:BE47" si="20">BD11/BA11</f>
-        <v>0.99787638314518834</v>
+        <v>0.99789873700681797</v>
       </c>
       <c r="BF11" s="10">
         <v>99991</v>
@@ -1418,14 +1418,14 @@
       </c>
       <c r="BH11" s="3">
         <f t="shared" ref="BH11:BH33" si="21">BI11-BG11</f>
-        <v>49942</v>
+        <v>49944</v>
       </c>
       <c r="BI11" s="5">
-        <v>100935</v>
+        <v>100937</v>
       </c>
       <c r="BJ11" s="4">
         <f t="shared" ref="BJ11:BJ33" si="22">BI11/BF11</f>
-        <v>1.0094408496764709</v>
+        <v>1.009460851476633</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1865,14 +1865,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>34891</v>
+        <v>34893</v>
       </c>
       <c r="F14" s="5">
-        <v>77292</v>
+        <v>77294</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>0.9334782608695652</v>
+        <v>0.9335024154589372</v>
       </c>
       <c r="H14" s="5">
         <v>84757</v>
@@ -1882,14 +1882,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>34525</v>
+        <v>34527</v>
       </c>
       <c r="K14" s="5">
-        <v>79136</v>
+        <v>79138</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.93368099390020887</v>
+        <v>0.93370459077126378</v>
       </c>
       <c r="M14" s="9">
         <v>154914</v>
@@ -1901,11 +1901,11 @@
         <v>144482</v>
       </c>
       <c r="P14" s="5">
-        <v>145048</v>
+        <v>145051</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="4"/>
-        <v>0.93631305111223007</v>
+        <v>0.9363324166957151</v>
       </c>
       <c r="R14" s="5">
         <v>85475</v>
@@ -1915,14 +1915,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="5"/>
-        <v>36056</v>
+        <v>36058</v>
       </c>
       <c r="U14" s="5">
-        <v>78725</v>
+        <v>78727</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="6"/>
-        <v>0.92102954080140387</v>
+        <v>0.92105293945598132</v>
       </c>
       <c r="W14" s="5">
         <v>86445</v>
@@ -1932,14 +1932,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="7"/>
-        <v>36738</v>
+        <v>36740</v>
       </c>
       <c r="Z14" s="5">
-        <v>80017</v>
+        <v>80019</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="8"/>
-        <v>0.92564058071606226</v>
+        <v>0.92566371681415927</v>
       </c>
       <c r="AB14" s="5">
         <v>156524</v>
@@ -1949,14 +1949,14 @@
       </c>
       <c r="AD14" s="3">
         <f t="shared" si="9"/>
-        <v>77501</v>
+        <v>77503</v>
       </c>
       <c r="AE14" s="5">
-        <v>149301</v>
+        <v>149303</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="10"/>
-        <v>0.95385372211290287</v>
+        <v>0.95386649970611537</v>
       </c>
       <c r="AG14" s="5">
         <v>86459</v>
@@ -1966,14 +1966,14 @@
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="11"/>
-        <v>34528</v>
+        <v>34530</v>
       </c>
       <c r="AJ14" s="5">
-        <v>81196</v>
+        <v>81198</v>
       </c>
       <c r="AK14" s="4">
         <f t="shared" si="12"/>
-        <v>0.93912721636845209</v>
+        <v>0.93915034872020264</v>
       </c>
       <c r="AL14" s="5">
         <v>87786</v>
@@ -1983,14 +1983,14 @@
       </c>
       <c r="AN14" s="3">
         <f t="shared" si="13"/>
-        <v>34700</v>
+        <v>34702</v>
       </c>
       <c r="AO14" s="5">
-        <v>82763</v>
+        <v>82765</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="14"/>
-        <v>0.94278130909256597</v>
+        <v>0.94280409176861912</v>
       </c>
       <c r="AQ14" s="3">
         <v>158597</v>
@@ -2000,14 +2000,14 @@
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="15"/>
-        <v>69823</v>
+        <v>69826</v>
       </c>
       <c r="AT14" s="3">
-        <v>151816</v>
+        <v>151819</v>
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="16"/>
-        <v>0.95724383185053941</v>
+        <v>0.9572627477190615</v>
       </c>
       <c r="AV14" s="5">
         <v>90863</v>
@@ -2017,14 +2017,14 @@
       </c>
       <c r="AX14" s="3">
         <f t="shared" si="17"/>
-        <v>32103</v>
+        <v>32105</v>
       </c>
       <c r="AY14" s="5">
-        <v>83344</v>
+        <v>83346</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="18"/>
-        <v>0.91724904526594986</v>
+        <v>0.9172710564256078</v>
       </c>
       <c r="BA14" s="10">
         <v>86219</v>
@@ -2034,14 +2034,14 @@
       </c>
       <c r="BC14" s="3">
         <f t="shared" si="19"/>
-        <v>35289</v>
+        <v>35291</v>
       </c>
       <c r="BD14" s="5">
-        <v>85167</v>
+        <v>85169</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="20"/>
-        <v>0.98779851308876232</v>
+        <v>0.98782170983193962</v>
       </c>
       <c r="BF14" s="10">
         <v>155639</v>
@@ -2051,14 +2051,14 @@
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="21"/>
-        <v>76840</v>
+        <v>76843</v>
       </c>
       <c r="BI14" s="5">
-        <v>155152</v>
+        <v>155155</v>
       </c>
       <c r="BJ14" s="4">
         <f t="shared" si="22"/>
-        <v>0.99687096421847998</v>
+        <v>0.99689023959290413</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2262,14 +2262,14 @@
       </c>
       <c r="BH15" s="3">
         <f t="shared" si="21"/>
-        <v>144900</v>
+        <v>144901</v>
       </c>
       <c r="BI15" s="5">
-        <v>482979</v>
+        <v>482980</v>
       </c>
       <c r="BJ15" s="4">
         <f t="shared" si="22"/>
-        <v>0.9955825544914475</v>
+        <v>0.9955846158285957</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2287,14 +2287,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>106339</v>
+        <v>106341</v>
       </c>
       <c r="F16" s="5">
-        <v>390223</v>
+        <v>390225</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.95110923706133832</v>
+        <v>0.95111411175727911</v>
       </c>
       <c r="H16" s="5">
         <v>416018</v>
@@ -2304,14 +2304,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>103645</v>
+        <v>103647</v>
       </c>
       <c r="K16" s="5">
-        <v>398186</v>
+        <v>398188</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.95713647005658409</v>
+        <v>0.95714127754087563</v>
       </c>
       <c r="M16" s="9">
         <v>750813</v>
@@ -2323,11 +2323,11 @@
         <v>716590</v>
       </c>
       <c r="P16" s="5">
-        <v>718010</v>
+        <v>718013</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="4"/>
-        <v>0.95631002659783459</v>
+        <v>0.95631402226652973</v>
       </c>
       <c r="R16" s="5">
         <v>419109</v>
@@ -2337,14 +2337,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="5"/>
-        <v>111550</v>
+        <v>111554</v>
       </c>
       <c r="U16" s="5">
-        <v>399093</v>
+        <v>399097</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="6"/>
-        <v>0.95224154098337188</v>
+        <v>0.95225108503992995</v>
       </c>
       <c r="W16" s="5">
         <v>423539</v>
@@ -2354,14 +2354,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="7"/>
-        <v>110436</v>
+        <v>110440</v>
       </c>
       <c r="Z16" s="5">
-        <v>405276</v>
+        <v>405280</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="8"/>
-        <v>0.95688000396657691</v>
+        <v>0.95688944819721444</v>
       </c>
       <c r="AB16" s="5">
         <v>762171</v>
@@ -2371,14 +2371,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="9"/>
-        <v>204093</v>
+        <v>204098</v>
       </c>
       <c r="AE16" s="5">
-        <v>732827</v>
+        <v>732832</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="10"/>
-        <v>0.96149945353470545</v>
+        <v>0.96150601374232292</v>
       </c>
       <c r="AG16" s="5">
         <v>429452</v>
@@ -2388,14 +2388,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="11"/>
-        <v>106277</v>
+        <v>106282</v>
       </c>
       <c r="AJ16" s="5">
-        <v>410502</v>
+        <v>410507</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="12"/>
-        <v>0.95587399755968072</v>
+        <v>0.95588564030438794</v>
       </c>
       <c r="AL16" s="5">
         <v>434676</v>
@@ -2405,14 +2405,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="13"/>
-        <v>110269</v>
+        <v>110274</v>
       </c>
       <c r="AO16" s="5">
-        <v>416380</v>
+        <v>416385</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="14"/>
-        <v>0.95790887925719381</v>
+        <v>0.95792038207768548</v>
       </c>
       <c r="AQ16" s="3">
         <v>772632</v>
@@ -2422,14 +2422,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="15"/>
-        <v>180843</v>
+        <v>180850</v>
       </c>
       <c r="AT16" s="3">
-        <v>743487</v>
+        <v>743494</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="16"/>
-        <v>0.96227829031155843</v>
+        <v>0.9622873502521252</v>
       </c>
       <c r="AV16" s="5">
         <v>448203</v>
@@ -2439,14 +2439,14 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="17"/>
-        <v>98402</v>
+        <v>98410</v>
       </c>
       <c r="AY16" s="5">
-        <v>418481</v>
+        <v>418489</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="18"/>
-        <v>0.93368629839603934</v>
+        <v>0.93370414745104335</v>
       </c>
       <c r="BA16" s="10">
         <v>429555</v>
@@ -2456,14 +2456,14 @@
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="19"/>
-        <v>103424</v>
+        <v>103432</v>
       </c>
       <c r="BD16" s="5">
-        <v>424698</v>
+        <v>424706</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="20"/>
-        <v>0.98869294968048327</v>
+        <v>0.98871157360524264</v>
       </c>
       <c r="BF16" s="10">
         <v>753579</v>
@@ -2473,14 +2473,14 @@
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="21"/>
-        <v>197242</v>
+        <v>197250</v>
       </c>
       <c r="BI16" s="5">
-        <v>753326</v>
+        <v>753334</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="22"/>
-        <v>0.99966426877606729</v>
+        <v>0.99967488478314814</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2498,14 +2498,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>97175</v>
+        <v>97180</v>
       </c>
       <c r="F17" s="5">
-        <v>273153</v>
+        <v>273158</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.96564511738566339</v>
+        <v>0.96566279328739957</v>
       </c>
       <c r="H17" s="5">
         <v>290053</v>
@@ -2515,14 +2515,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>89054</v>
+        <v>89059</v>
       </c>
       <c r="K17" s="5">
-        <v>281345</v>
+        <v>281350</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.96997790059058175</v>
+        <v>0.96999513881945709</v>
       </c>
       <c r="M17" s="9">
         <v>666005</v>
@@ -2534,11 +2534,11 @@
         <v>640256</v>
       </c>
       <c r="P17" s="5">
-        <v>641498</v>
+        <v>641511</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="4"/>
-        <v>0.96320297895661444</v>
+        <v>0.96322249832959217</v>
       </c>
       <c r="R17" s="5">
         <v>287981</v>
@@ -2548,14 +2548,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="5"/>
-        <v>96344</v>
+        <v>96348</v>
       </c>
       <c r="U17" s="5">
-        <v>276616</v>
+        <v>276620</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="6"/>
-        <v>0.96053559088967677</v>
+        <v>0.96054948069490698</v>
       </c>
       <c r="W17" s="5">
         <v>293004</v>
@@ -2565,14 +2565,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="7"/>
-        <v>99053</v>
+        <v>99058</v>
       </c>
       <c r="Z17" s="5">
-        <v>283319</v>
+        <v>283324</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="8"/>
-        <v>0.9669458437427475</v>
+        <v>0.96696290835619991</v>
       </c>
       <c r="AB17" s="5">
         <v>677720</v>
@@ -2582,14 +2582,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="9"/>
-        <v>263389</v>
+        <v>263397</v>
       </c>
       <c r="AE17" s="5">
-        <v>660024</v>
+        <v>660032</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="10"/>
-        <v>0.97388892167856933</v>
+        <v>0.97390072596352473</v>
       </c>
       <c r="AG17" s="5">
         <v>295677</v>
@@ -2599,14 +2599,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="11"/>
-        <v>86964</v>
+        <v>86966</v>
       </c>
       <c r="AJ17" s="5">
-        <v>286415</v>
+        <v>286417</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="12"/>
-        <v>0.96867527741420534</v>
+        <v>0.96868204155209903</v>
       </c>
       <c r="AL17" s="5">
         <v>303084</v>
@@ -2616,14 +2616,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="13"/>
-        <v>89243</v>
+        <v>89244</v>
       </c>
       <c r="AO17" s="5">
-        <v>294600</v>
+        <v>294601</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="14"/>
-        <v>0.97200776022488811</v>
+        <v>0.97201105964023171</v>
       </c>
       <c r="AQ17" s="3">
         <v>690105</v>
@@ -2633,14 +2633,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="15"/>
-        <v>218601</v>
+        <v>218609</v>
       </c>
       <c r="AT17" s="3">
-        <v>674482</v>
+        <v>674490</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="16"/>
-        <v>0.97736141601640325</v>
+        <v>0.97737300845523511</v>
       </c>
       <c r="AV17" s="5">
         <v>311697</v>
@@ -2650,14 +2650,14 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="17"/>
-        <v>74901</v>
+        <v>74902</v>
       </c>
       <c r="AY17" s="5">
-        <v>292919</v>
+        <v>292920</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="18"/>
-        <v>0.9397555959794287</v>
+        <v>0.93975880422333224</v>
       </c>
       <c r="BA17" s="10">
         <v>307540</v>
@@ -2667,14 +2667,14 @@
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="19"/>
-        <v>81877</v>
+        <v>81878</v>
       </c>
       <c r="BD17" s="5">
-        <v>300845</v>
+        <v>300846</v>
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="20"/>
-        <v>0.9782304740846719</v>
+        <v>0.97823372569421863</v>
       </c>
       <c r="BF17" s="10">
         <v>689646</v>
@@ -2684,14 +2684,14 @@
       </c>
       <c r="BH17" s="3">
         <f t="shared" si="21"/>
-        <v>257511</v>
+        <v>257521</v>
       </c>
       <c r="BI17" s="5">
-        <v>688751</v>
+        <v>688761</v>
       </c>
       <c r="BJ17" s="4">
         <f t="shared" si="22"/>
-        <v>0.99870223273969538</v>
+        <v>0.99871673293254803</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2709,14 +2709,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>397889</v>
+        <v>397894</v>
       </c>
       <c r="F18" s="5">
-        <v>804252</v>
+        <v>804257</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>0.95687442816707691</v>
+        <v>0.95688037701413087</v>
       </c>
       <c r="H18" s="5">
         <v>861805</v>
@@ -2726,14 +2726,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>381249</v>
+        <v>381254</v>
       </c>
       <c r="K18" s="5">
-        <v>819366</v>
+        <v>819371</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.9507556813896415</v>
+        <v>0.9507614831661455</v>
       </c>
       <c r="M18" s="9">
         <v>1358945</v>
@@ -2745,11 +2745,11 @@
         <v>1272521</v>
       </c>
       <c r="P18" s="5">
-        <v>1276378</v>
+        <v>1276388</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="4"/>
-        <v>0.93924183833782826</v>
+        <v>0.93924919698736886</v>
       </c>
       <c r="R18" s="5">
         <v>869959</v>
@@ -2759,14 +2759,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="5"/>
-        <v>402924</v>
+        <v>402929</v>
       </c>
       <c r="U18" s="5">
-        <v>822384</v>
+        <v>822389</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="6"/>
-        <v>0.94531351477483416</v>
+        <v>0.94531926217212536</v>
       </c>
       <c r="W18" s="5">
         <v>883450</v>
@@ -2776,14 +2776,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="7"/>
-        <v>412762</v>
+        <v>412767</v>
       </c>
       <c r="Z18" s="5">
-        <v>838158</v>
+        <v>838163</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="8"/>
-        <v>0.94873280887429967</v>
+        <v>0.94873846850415988</v>
       </c>
       <c r="AB18" s="5">
         <v>1397129</v>
@@ -2793,14 +2793,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="9"/>
-        <v>718461</v>
+        <v>718469</v>
       </c>
       <c r="AE18" s="5">
-        <v>1341456</v>
+        <v>1341464</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="10"/>
-        <v>0.96015185426685723</v>
+        <v>0.9601575802950193</v>
       </c>
       <c r="AG18" s="5">
         <v>899515</v>
@@ -2810,14 +2810,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="11"/>
-        <v>400331</v>
+        <v>400336</v>
       </c>
       <c r="AJ18" s="5">
-        <v>863730</v>
+        <v>863735</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="12"/>
-        <v>0.96021745051499974</v>
+        <v>0.96022300906599667</v>
       </c>
       <c r="AL18" s="5">
         <v>914748</v>
@@ -2827,14 +2827,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="13"/>
-        <v>398134</v>
+        <v>398139</v>
       </c>
       <c r="AO18" s="5">
-        <v>880111</v>
+        <v>880116</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="14"/>
-        <v>0.962134926777648</v>
+        <v>0.96214039276390873</v>
       </c>
       <c r="AQ18" s="3">
         <v>1436617</v>
@@ -2844,14 +2844,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="15"/>
-        <v>655868</v>
+        <v>655876</v>
       </c>
       <c r="AT18" s="3">
-        <v>1378607</v>
+        <v>1378615</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="16"/>
-        <v>0.95962041379156726</v>
+        <v>0.95962598242955499</v>
       </c>
       <c r="AV18" s="5">
         <v>954168</v>
@@ -2861,14 +2861,14 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="17"/>
-        <v>385905</v>
+        <v>385910</v>
       </c>
       <c r="AY18" s="5">
-        <v>892999</v>
+        <v>893004</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="18"/>
-        <v>0.93589284067375977</v>
+        <v>0.9358980808411097</v>
       </c>
       <c r="BA18" s="10">
         <v>922519</v>
@@ -2878,14 +2878,14 @@
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="19"/>
-        <v>429133</v>
+        <v>429138</v>
       </c>
       <c r="BD18" s="5">
-        <v>910833</v>
+        <v>910838</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" si="20"/>
-        <v>0.98733251022472168</v>
+        <v>0.98733793016729199</v>
       </c>
       <c r="BF18" s="10">
         <v>1428140</v>
@@ -2895,14 +2895,14 @@
       </c>
       <c r="BH18" s="3">
         <f t="shared" si="21"/>
-        <v>725123</v>
+        <v>725133</v>
       </c>
       <c r="BI18" s="5">
-        <v>1417106</v>
+        <v>1417116</v>
       </c>
       <c r="BJ18" s="4">
         <f t="shared" si="22"/>
-        <v>0.99227386670774576</v>
+        <v>0.99228086882238431</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -2956,11 +2956,11 @@
         <v>406179</v>
       </c>
       <c r="P19" s="5">
-        <v>408678</v>
+        <v>408679</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="4"/>
-        <v>0.86831017785700471</v>
+        <v>0.86831230253750591</v>
       </c>
       <c r="R19" s="5">
         <v>282327</v>
@@ -3021,14 +3021,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="11"/>
-        <v>164981</v>
+        <v>164982</v>
       </c>
       <c r="AJ19" s="5">
-        <v>254431</v>
+        <v>254432</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="12"/>
-        <v>0.88586171238767042</v>
+        <v>0.88586519412422138</v>
       </c>
       <c r="AL19" s="5">
         <v>292666</v>
@@ -3038,14 +3038,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="13"/>
-        <v>159539</v>
+        <v>159540</v>
       </c>
       <c r="AO19" s="5">
-        <v>260135</v>
+        <v>260136</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="14"/>
-        <v>0.88884598825965433</v>
+        <v>0.88884940512392963</v>
       </c>
       <c r="AQ19" s="3">
         <v>495564</v>
@@ -3055,14 +3055,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="15"/>
-        <v>290909</v>
+        <v>290910</v>
       </c>
       <c r="AT19" s="3">
-        <v>448269</v>
+        <v>448270</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="16"/>
-        <v>0.90456328546867815</v>
+        <v>0.90456530337151209</v>
       </c>
       <c r="AV19" s="5">
         <v>310298</v>
@@ -3131,14 +3131,14 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>3108</v>
+        <v>3109</v>
       </c>
       <c r="F20" s="5">
-        <v>5062</v>
+        <v>5063</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="1"/>
-        <v>0.83863485752153744</v>
+        <v>0.83880053015241884</v>
       </c>
       <c r="H20" s="5">
         <v>6124</v>
@@ -3148,14 +3148,14 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" si="2"/>
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="K20" s="5">
-        <v>5128</v>
+        <v>5129</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="3"/>
-        <v>0.83736120182886997</v>
+        <v>0.83752449379490534</v>
       </c>
       <c r="M20" s="9">
         <v>9262</v>
@@ -3167,11 +3167,11 @@
         <v>7959</v>
       </c>
       <c r="P20" s="5">
-        <v>8085</v>
+        <v>8086</v>
       </c>
       <c r="Q20" s="4">
         <f t="shared" si="4"/>
-        <v>0.87292161520190026</v>
+        <v>0.87302958324336</v>
       </c>
       <c r="R20" s="5">
         <v>6202</v>
@@ -3181,14 +3181,14 @@
       </c>
       <c r="T20" s="3">
         <f t="shared" si="5"/>
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="U20" s="5">
-        <v>5199</v>
+        <v>5200</v>
       </c>
       <c r="V20" s="4">
         <f t="shared" si="6"/>
-        <v>0.83827797484682365</v>
+        <v>0.83843921315704606</v>
       </c>
       <c r="W20" s="5">
         <v>6226</v>
@@ -3198,14 +3198,14 @@
       </c>
       <c r="Y20" s="3">
         <f t="shared" si="7"/>
-        <v>3158</v>
+        <v>3159</v>
       </c>
       <c r="Z20" s="5">
-        <v>5269</v>
+        <v>5270</v>
       </c>
       <c r="AA20" s="4">
         <f t="shared" si="8"/>
-        <v>0.8462897526501767</v>
+        <v>0.84645036941856733</v>
       </c>
       <c r="AB20" s="5">
         <v>9386</v>
@@ -3215,14 +3215,14 @@
       </c>
       <c r="AD20" s="3">
         <f t="shared" si="9"/>
-        <v>5862</v>
+        <v>5863</v>
       </c>
       <c r="AE20" s="5">
-        <v>8441</v>
+        <v>8442</v>
       </c>
       <c r="AF20" s="4">
         <f t="shared" si="10"/>
-        <v>0.89931813339015554</v>
+        <v>0.89942467504794377</v>
       </c>
       <c r="AG20" s="5">
         <v>6315</v>
@@ -3232,14 +3232,14 @@
       </c>
       <c r="AI20" s="3">
         <f t="shared" si="11"/>
-        <v>3232</v>
+        <v>3233</v>
       </c>
       <c r="AJ20" s="5">
-        <v>5450</v>
+        <v>5451</v>
       </c>
       <c r="AK20" s="4">
         <f t="shared" si="12"/>
-        <v>0.86302454473475854</v>
+        <v>0.86318289786223279</v>
       </c>
       <c r="AL20" s="5">
         <v>6446</v>
@@ -3249,14 +3249,14 @@
       </c>
       <c r="AN20" s="3">
         <f t="shared" si="13"/>
-        <v>3252</v>
+        <v>3253</v>
       </c>
       <c r="AO20" s="5">
-        <v>5547</v>
+        <v>5548</v>
       </c>
       <c r="AP20" s="4">
         <f t="shared" si="14"/>
-        <v>0.86053366428793054</v>
+        <v>0.86068879925535213</v>
       </c>
       <c r="AQ20" s="3">
         <v>9604</v>
@@ -3266,14 +3266,14 @@
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="15"/>
-        <v>5298</v>
+        <v>5299</v>
       </c>
       <c r="AT20" s="3">
-        <v>8627</v>
+        <v>8628</v>
       </c>
       <c r="AU20" s="4">
         <f t="shared" si="16"/>
-        <v>0.89827155351936694</v>
+        <v>0.89837567680133279</v>
       </c>
       <c r="AV20" s="5">
         <v>6642</v>
@@ -3283,14 +3283,14 @@
       </c>
       <c r="AX20" s="3">
         <f t="shared" si="17"/>
-        <v>3118</v>
+        <v>3119</v>
       </c>
       <c r="AY20" s="5">
-        <v>5606</v>
+        <v>5607</v>
       </c>
       <c r="AZ20" s="4">
         <f t="shared" si="18"/>
-        <v>0.84402288467329123</v>
+        <v>0.84417344173441733</v>
       </c>
       <c r="BA20" s="10">
         <v>5628</v>
@@ -3342,14 +3342,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>6072</v>
+        <v>6074</v>
       </c>
       <c r="F21" s="5">
-        <v>8307</v>
+        <v>8309</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>0.78242441367617976</v>
+        <v>0.78261279080719603</v>
       </c>
       <c r="H21" s="5">
         <v>10811</v>
@@ -3359,14 +3359,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>5871</v>
+        <v>5873</v>
       </c>
       <c r="K21" s="5">
-        <v>8434</v>
+        <v>8436</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>0.78013134770141523</v>
+        <v>0.78031634446397191</v>
       </c>
       <c r="M21" s="9">
         <v>14133</v>
@@ -3378,11 +3378,11 @@
         <v>11192</v>
       </c>
       <c r="P21" s="5">
-        <v>11402</v>
+        <v>11404</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="4"/>
-        <v>0.80676431047902075</v>
+        <v>0.80690582325054838</v>
       </c>
       <c r="R21" s="5">
         <v>11019</v>
@@ -3392,14 +3392,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="5"/>
-        <v>6087</v>
+        <v>6089</v>
       </c>
       <c r="U21" s="5">
-        <v>8629</v>
+        <v>8631</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="6"/>
-        <v>0.78310191487430802</v>
+        <v>0.78328341954805336</v>
       </c>
       <c r="W21" s="5">
         <v>11175</v>
@@ -3409,14 +3409,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="7"/>
-        <v>6284</v>
+        <v>6286</v>
       </c>
       <c r="Z21" s="5">
-        <v>8800</v>
+        <v>8802</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="8"/>
-        <v>0.78747203579418346</v>
+        <v>0.78765100671140942</v>
       </c>
       <c r="AB21" s="5">
         <v>14571</v>
@@ -3426,14 +3426,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="9"/>
-        <v>9107</v>
+        <v>9108</v>
       </c>
       <c r="AE21" s="5">
-        <v>12224</v>
+        <v>12225</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="10"/>
-        <v>0.83892663509711074</v>
+        <v>0.83899526456660489</v>
       </c>
       <c r="AG21" s="5">
         <v>11345</v>
@@ -3443,14 +3443,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="11"/>
-        <v>6296</v>
+        <v>6297</v>
       </c>
       <c r="AJ21" s="5">
-        <v>9224</v>
+        <v>9225</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="12"/>
-        <v>0.81304539444689294</v>
+        <v>0.81313353900396645</v>
       </c>
       <c r="AL21" s="5">
         <v>11441</v>
@@ -3460,14 +3460,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="13"/>
-        <v>6143</v>
+        <v>6144</v>
       </c>
       <c r="AO21" s="5">
-        <v>9335</v>
+        <v>9336</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="14"/>
-        <v>0.81592518136526526</v>
+        <v>0.81601258631238527</v>
       </c>
       <c r="AQ21" s="3">
         <v>14790</v>
@@ -3477,14 +3477,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="15"/>
-        <v>8843</v>
+        <v>8844</v>
       </c>
       <c r="AT21" s="3">
-        <v>12533</v>
+        <v>12534</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="16"/>
-        <v>0.84739688979039896</v>
+        <v>0.84746450304259635</v>
       </c>
       <c r="AV21" s="5">
         <v>11740</v>
@@ -3494,14 +3494,14 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="17"/>
-        <v>6331</v>
+        <v>6332</v>
       </c>
       <c r="AY21" s="5">
-        <v>9476</v>
+        <v>9477</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="18"/>
-        <v>0.8071550255536627</v>
+        <v>0.80724020442930156</v>
       </c>
       <c r="BA21" s="10">
         <v>9242</v>
@@ -3511,14 +3511,14 @@
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="19"/>
-        <v>6594</v>
+        <v>6595</v>
       </c>
       <c r="BD21" s="5">
-        <v>9585</v>
+        <v>9586</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="20"/>
-        <v>1.0371131789655919</v>
+        <v>1.0372213806535382</v>
       </c>
       <c r="BF21" s="10">
         <v>12544</v>
@@ -3528,14 +3528,14 @@
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="21"/>
-        <v>9739</v>
+        <v>9740</v>
       </c>
       <c r="BI21" s="5">
-        <v>12930</v>
+        <v>12931</v>
       </c>
       <c r="BJ21" s="4">
         <f t="shared" si="22"/>
-        <v>1.0307716836734695</v>
+        <v>1.0308514030612246</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3589,11 +3589,11 @@
         <v>6697</v>
       </c>
       <c r="P22" s="5">
-        <v>6764</v>
+        <v>6766</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="4"/>
-        <v>0.90840719849583673</v>
+        <v>0.908675799086758</v>
       </c>
       <c r="R22" s="5">
         <v>6325</v>
@@ -3637,14 +3637,14 @@
       </c>
       <c r="AD22" s="3">
         <f t="shared" si="9"/>
-        <v>5028</v>
+        <v>5031</v>
       </c>
       <c r="AE22" s="5">
-        <v>7109</v>
+        <v>7112</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="10"/>
-        <v>0.92782563299399634</v>
+        <v>0.92821717567214823</v>
       </c>
       <c r="AG22" s="5">
         <v>6546</v>
@@ -3654,14 +3654,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="11"/>
-        <v>4113</v>
+        <v>4114</v>
       </c>
       <c r="AJ22" s="5">
-        <v>6017</v>
+        <v>6018</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="12"/>
-        <v>0.91918728994805987</v>
+        <v>0.91934005499541704</v>
       </c>
       <c r="AL22" s="5">
         <v>6648</v>
@@ -3671,14 +3671,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="13"/>
-        <v>3819</v>
+        <v>3820</v>
       </c>
       <c r="AO22" s="5">
-        <v>6077</v>
+        <v>6078</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="14"/>
-        <v>0.91410950661853185</v>
+        <v>0.91425992779783394</v>
       </c>
       <c r="AQ22" s="3">
         <v>7880</v>
@@ -3688,14 +3688,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="15"/>
-        <v>4833</v>
+        <v>4836</v>
       </c>
       <c r="AT22" s="3">
-        <v>7289</v>
+        <v>7292</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="16"/>
-        <v>0.92500000000000004</v>
+        <v>0.92538071065989846</v>
       </c>
       <c r="AV22" s="5">
         <v>6715</v>
@@ -3705,14 +3705,14 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="17"/>
-        <v>3917</v>
+        <v>3918</v>
       </c>
       <c r="AY22" s="5">
-        <v>6100</v>
+        <v>6101</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="18"/>
-        <v>0.90841399851079674</v>
+        <v>0.90856291883842144</v>
       </c>
       <c r="BA22" s="10">
         <v>6117</v>
@@ -3722,14 +3722,14 @@
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="19"/>
-        <v>4030</v>
+        <v>4031</v>
       </c>
       <c r="BD22" s="5">
-        <v>6147</v>
+        <v>6148</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" si="20"/>
-        <v>1.0049043648847473</v>
+        <v>1.0050678437142391</v>
       </c>
       <c r="BF22" s="10">
         <v>7349</v>
@@ -3739,14 +3739,14 @@
       </c>
       <c r="BH22" s="3">
         <f t="shared" si="21"/>
-        <v>5145</v>
+        <v>5148</v>
       </c>
       <c r="BI22" s="5">
-        <v>7418</v>
+        <v>7421</v>
       </c>
       <c r="BJ22" s="4">
         <f t="shared" si="22"/>
-        <v>1.0093890325214314</v>
+        <v>1.0097972513267111</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -3764,14 +3764,14 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>5399</v>
+        <v>5400</v>
       </c>
       <c r="F23" s="5">
-        <v>7275</v>
+        <v>7276</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>0.80725699067909451</v>
+        <v>0.80736795383932536</v>
       </c>
       <c r="H23" s="5">
         <v>9118</v>
@@ -3781,14 +3781,14 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>5298</v>
+        <v>5299</v>
       </c>
       <c r="K23" s="5">
-        <v>7403</v>
+        <v>7404</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="3"/>
-        <v>0.81191050669006359</v>
+        <v>0.81202017986400521</v>
       </c>
       <c r="M23" s="9">
         <v>11079</v>
@@ -3800,11 +3800,11 @@
         <v>9029</v>
       </c>
       <c r="P23" s="5">
-        <v>9124</v>
+        <v>9125</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" si="4"/>
-        <v>0.82354003068869031</v>
+        <v>0.82363029154255796</v>
       </c>
       <c r="R23" s="5">
         <v>9156</v>
@@ -3814,14 +3814,14 @@
       </c>
       <c r="T23" s="3">
         <f t="shared" si="5"/>
-        <v>5372</v>
+        <v>5373</v>
       </c>
       <c r="U23" s="5">
-        <v>7567</v>
+        <v>7568</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="6"/>
-        <v>0.82645259938837923</v>
+        <v>0.82656181738750545</v>
       </c>
       <c r="W23" s="5">
         <v>9166</v>
@@ -3831,14 +3831,14 @@
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="7"/>
-        <v>5709</v>
+        <v>5710</v>
       </c>
       <c r="Z23" s="5">
-        <v>7748</v>
+        <v>7749</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="8"/>
-        <v>0.84529783984289764</v>
+        <v>0.84540693868644989</v>
       </c>
       <c r="AB23" s="5">
         <v>11322</v>
@@ -3848,14 +3848,14 @@
       </c>
       <c r="AD23" s="3">
         <f t="shared" si="9"/>
-        <v>7305</v>
+        <v>7306</v>
       </c>
       <c r="AE23" s="5">
-        <v>10062</v>
+        <v>10063</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="10"/>
-        <v>0.88871224165341811</v>
+        <v>0.88880056527115348</v>
       </c>
       <c r="AG23" s="5">
         <v>9569</v>
@@ -3865,14 +3865,14 @@
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="11"/>
-        <v>5888</v>
+        <v>5889</v>
       </c>
       <c r="AJ23" s="5">
-        <v>8234</v>
+        <v>8235</v>
       </c>
       <c r="AK23" s="4">
         <f t="shared" si="12"/>
-        <v>0.86048698923607481</v>
+        <v>0.86059149336398788</v>
       </c>
       <c r="AL23" s="5">
         <v>9502</v>
@@ -3882,14 +3882,14 @@
       </c>
       <c r="AN23" s="3">
         <f t="shared" si="13"/>
-        <v>6034</v>
+        <v>6035</v>
       </c>
       <c r="AO23" s="5">
-        <v>8360</v>
+        <v>8361</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="14"/>
-        <v>0.87981477583666601</v>
+        <v>0.87992001683856025</v>
       </c>
       <c r="AQ23" s="3">
         <v>11767</v>
@@ -3899,14 +3899,14 @@
       </c>
       <c r="AS23" s="3">
         <f t="shared" si="15"/>
-        <v>7340</v>
+        <v>7341</v>
       </c>
       <c r="AT23" s="3">
-        <v>10376</v>
+        <v>10377</v>
       </c>
       <c r="AU23" s="4">
         <f t="shared" si="16"/>
-        <v>0.88178805132999061</v>
+        <v>0.8818730347582221</v>
       </c>
       <c r="AV23" s="5">
         <v>9805</v>
@@ -3916,14 +3916,14 @@
       </c>
       <c r="AX23" s="3">
         <f t="shared" si="17"/>
-        <v>5855</v>
+        <v>5856</v>
       </c>
       <c r="AY23" s="5">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="AZ23" s="4">
         <f t="shared" si="18"/>
-        <v>0.86180520142784289</v>
+        <v>0.86190719020907702</v>
       </c>
       <c r="BA23" s="10">
         <v>8694</v>
@@ -3933,14 +3933,14 @@
       </c>
       <c r="BC23" s="3">
         <f t="shared" si="19"/>
-        <v>6351</v>
+        <v>6352</v>
       </c>
       <c r="BD23" s="5">
-        <v>8558</v>
+        <v>8559</v>
       </c>
       <c r="BE23" s="4">
         <f t="shared" si="20"/>
-        <v>0.98435702783528867</v>
+        <v>0.98447204968944102</v>
       </c>
       <c r="BF23" s="10">
         <v>11229</v>
@@ -3950,14 +3950,14 @@
       </c>
       <c r="BH23" s="3">
         <f t="shared" si="21"/>
-        <v>7868</v>
+        <v>7869</v>
       </c>
       <c r="BI23" s="5">
-        <v>10637</v>
+        <v>10638</v>
       </c>
       <c r="BJ23" s="4">
         <f t="shared" si="22"/>
-        <v>0.94727936592750916</v>
+        <v>0.94736842105263153</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -3975,14 +3975,14 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="0"/>
-        <v>3726</v>
+        <v>3728</v>
       </c>
       <c r="F24" s="5">
-        <v>4970</v>
+        <v>4972</v>
       </c>
       <c r="G24" s="4">
         <f t="shared" si="1"/>
-        <v>0.78913940933629723</v>
+        <v>0.78945697046681484</v>
       </c>
       <c r="H24" s="5">
         <v>6340</v>
@@ -3992,14 +3992,14 @@
       </c>
       <c r="J24" s="3">
         <f t="shared" si="2"/>
-        <v>3671</v>
+        <v>3673</v>
       </c>
       <c r="K24" s="5">
-        <v>5017</v>
+        <v>5019</v>
       </c>
       <c r="L24" s="4">
         <f t="shared" si="3"/>
-        <v>0.79132492113564668</v>
+        <v>0.79164037854889591</v>
       </c>
       <c r="M24" s="9">
         <v>7252</v>
@@ -4011,11 +4011,11 @@
         <v>5909</v>
       </c>
       <c r="P24" s="5">
-        <v>5943</v>
+        <v>5945</v>
       </c>
       <c r="Q24" s="4">
         <f t="shared" si="4"/>
-        <v>0.81949806949806947</v>
+        <v>0.81977385548814119</v>
       </c>
       <c r="R24" s="5">
         <v>6353</v>
@@ -4025,14 +4025,14 @@
       </c>
       <c r="T24" s="3">
         <f t="shared" si="5"/>
-        <v>3808</v>
+        <v>3810</v>
       </c>
       <c r="U24" s="5">
-        <v>5107</v>
+        <v>5109</v>
       </c>
       <c r="V24" s="4">
         <f t="shared" si="6"/>
-        <v>0.80387218636864477</v>
+        <v>0.80418699826853457</v>
       </c>
       <c r="W24" s="5">
         <v>6421</v>
@@ -4042,14 +4042,14 @@
       </c>
       <c r="Y24" s="3">
         <f t="shared" si="7"/>
-        <v>3897</v>
+        <v>3899</v>
       </c>
       <c r="Z24" s="5">
-        <v>5180</v>
+        <v>5182</v>
       </c>
       <c r="AA24" s="4">
         <f t="shared" si="8"/>
-        <v>0.80672792399937709</v>
+        <v>0.80703940196231116</v>
       </c>
       <c r="AB24" s="5">
         <v>7434</v>
@@ -4059,14 +4059,14 @@
       </c>
       <c r="AD24" s="3">
         <f t="shared" si="9"/>
-        <v>4717</v>
+        <v>4719</v>
       </c>
       <c r="AE24" s="5">
-        <v>6227</v>
+        <v>6229</v>
       </c>
       <c r="AF24" s="4">
         <f t="shared" si="10"/>
-        <v>0.83763788001076134</v>
+        <v>0.83790691417810059</v>
       </c>
       <c r="AG24" s="5">
         <v>6545</v>
@@ -4076,14 +4076,14 @@
       </c>
       <c r="AI24" s="3">
         <f t="shared" si="11"/>
-        <v>3943</v>
+        <v>3945</v>
       </c>
       <c r="AJ24" s="5">
-        <v>5344</v>
+        <v>5346</v>
       </c>
       <c r="AK24" s="4">
         <f t="shared" si="12"/>
-        <v>0.81650114591291056</v>
+        <v>0.81680672268907561</v>
       </c>
       <c r="AL24" s="5">
         <v>6623</v>
@@ -4093,14 +4093,14 @@
       </c>
       <c r="AN24" s="3">
         <f t="shared" si="13"/>
-        <v>4057</v>
+        <v>4059</v>
       </c>
       <c r="AO24" s="5">
-        <v>5429</v>
+        <v>5431</v>
       </c>
       <c r="AP24" s="4">
         <f t="shared" si="14"/>
-        <v>0.81971916050128346</v>
+        <v>0.82002113845689262</v>
       </c>
       <c r="AQ24" s="3">
         <v>7610</v>
@@ -4110,14 +4110,14 @@
       </c>
       <c r="AS24" s="3">
         <f t="shared" si="15"/>
-        <v>4915</v>
+        <v>4917</v>
       </c>
       <c r="AT24" s="3">
-        <v>6398</v>
+        <v>6400</v>
       </c>
       <c r="AU24" s="4">
         <f t="shared" si="16"/>
-        <v>0.8407358738501971</v>
+        <v>0.84099868593955318</v>
       </c>
       <c r="AV24" s="5">
         <v>6365</v>
@@ -4222,11 +4222,11 @@
         <v>24298</v>
       </c>
       <c r="P25" s="5">
-        <v>24428</v>
+        <v>24429</v>
       </c>
       <c r="Q25" s="4">
         <f t="shared" si="4"/>
-        <v>0.91786277898850233</v>
+        <v>0.91790035319756524</v>
       </c>
       <c r="R25" s="5">
         <v>19402</v>
@@ -4236,14 +4236,14 @@
       </c>
       <c r="T25" s="3">
         <f t="shared" si="5"/>
-        <v>9098</v>
+        <v>9099</v>
       </c>
       <c r="U25" s="5">
-        <v>17572</v>
+        <v>17573</v>
       </c>
       <c r="V25" s="4">
         <f t="shared" si="6"/>
-        <v>0.90567982682197712</v>
+        <v>0.90573136790021647</v>
       </c>
       <c r="W25" s="5">
         <v>19474</v>
@@ -4253,14 +4253,14 @@
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="7"/>
-        <v>9546</v>
+        <v>9547</v>
       </c>
       <c r="Z25" s="5">
-        <v>17814</v>
+        <v>17815</v>
       </c>
       <c r="AA25" s="4">
         <f t="shared" si="8"/>
-        <v>0.91475813905720449</v>
+        <v>0.91480948957584474</v>
       </c>
       <c r="AB25" s="5">
         <v>27081</v>
@@ -4270,14 +4270,14 @@
       </c>
       <c r="AD25" s="3">
         <f t="shared" si="9"/>
-        <v>15024</v>
+        <v>15025</v>
       </c>
       <c r="AE25" s="5">
-        <v>25203</v>
+        <v>25204</v>
       </c>
       <c r="AF25" s="4">
         <f t="shared" si="10"/>
-        <v>0.93065248698349401</v>
+        <v>0.93068941324175625</v>
       </c>
       <c r="AG25" s="5">
         <v>19543</v>
@@ -4287,14 +4287,14 @@
       </c>
       <c r="AI25" s="3">
         <f t="shared" si="11"/>
-        <v>8973</v>
+        <v>8974</v>
       </c>
       <c r="AJ25" s="5">
-        <v>18100</v>
+        <v>18101</v>
       </c>
       <c r="AK25" s="4">
         <f t="shared" si="12"/>
-        <v>0.92616282044721898</v>
+        <v>0.92621398966381829</v>
       </c>
       <c r="AL25" s="5">
         <v>19594</v>
@@ -4304,14 +4304,14 @@
       </c>
       <c r="AN25" s="3">
         <f t="shared" si="13"/>
-        <v>9105</v>
+        <v>9106</v>
       </c>
       <c r="AO25" s="5">
-        <v>18273</v>
+        <v>18274</v>
       </c>
       <c r="AP25" s="4">
         <f t="shared" si="14"/>
-        <v>0.93258140247014387</v>
+        <v>0.93263243850158206</v>
       </c>
       <c r="AQ25" s="3">
         <v>26830</v>
@@ -4321,14 +4321,14 @@
       </c>
       <c r="AS25" s="3">
         <f t="shared" si="15"/>
-        <v>13142</v>
+        <v>13143</v>
       </c>
       <c r="AT25" s="3">
-        <v>25472</v>
+        <v>25473</v>
       </c>
       <c r="AU25" s="4">
         <f t="shared" si="16"/>
-        <v>0.94938501677226983</v>
+        <v>0.94942228848304133</v>
       </c>
       <c r="AV25" s="5">
         <v>19719</v>
@@ -4338,14 +4338,14 @@
       </c>
       <c r="AX25" s="3">
         <f t="shared" si="17"/>
-        <v>8711</v>
+        <v>8712</v>
       </c>
       <c r="AY25" s="5">
-        <v>18366</v>
+        <v>18367</v>
       </c>
       <c r="AZ25" s="4">
         <f t="shared" si="18"/>
-        <v>0.9313859729195193</v>
+        <v>0.93143668543029567</v>
       </c>
       <c r="BA25" s="10">
         <v>18241</v>
@@ -4355,14 +4355,14 @@
       </c>
       <c r="BC25" s="3">
         <f t="shared" si="19"/>
-        <v>9437</v>
+        <v>9438</v>
       </c>
       <c r="BD25" s="5">
-        <v>18418</v>
+        <v>18419</v>
       </c>
       <c r="BE25" s="4">
         <f t="shared" si="20"/>
-        <v>1.0097034153829285</v>
+        <v>1.0097582369387643</v>
       </c>
       <c r="BF25" s="10">
         <v>25358</v>
@@ -4372,14 +4372,14 @@
       </c>
       <c r="BH25" s="3">
         <f t="shared" si="21"/>
-        <v>15167</v>
+        <v>15168</v>
       </c>
       <c r="BI25" s="5">
-        <v>25701</v>
+        <v>25702</v>
       </c>
       <c r="BJ25" s="4">
         <f t="shared" si="22"/>
-        <v>1.0135263033362252</v>
+        <v>1.0135657386229198</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4397,14 +4397,14 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>7691</v>
+        <v>7692</v>
       </c>
       <c r="F26" s="5">
-        <v>11665</v>
+        <v>11666</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>0.72869815092453771</v>
+        <v>0.72876061969015493</v>
       </c>
       <c r="H26" s="5">
         <v>16365</v>
@@ -4414,14 +4414,14 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>7792</v>
+        <v>7793</v>
       </c>
       <c r="K26" s="5">
-        <v>12090</v>
+        <v>12091</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="3"/>
-        <v>0.73877176901924835</v>
+        <v>0.73883287503819128</v>
       </c>
       <c r="M26" s="9">
         <v>27510</v>
@@ -4433,11 +4433,11 @@
         <v>21793</v>
       </c>
       <c r="P26" s="5">
-        <v>22091</v>
+        <v>22093</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="4"/>
-        <v>0.80301708469647404</v>
+        <v>0.80308978553253363</v>
       </c>
       <c r="R26" s="5">
         <v>16566</v>
@@ -4464,14 +4464,14 @@
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="7"/>
-        <v>8688</v>
+        <v>8690</v>
       </c>
       <c r="Z26" s="5">
-        <v>12687</v>
+        <v>12689</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" si="8"/>
-        <v>0.75842898134863701</v>
+        <v>0.75854854136776662</v>
       </c>
       <c r="AB26" s="5">
         <v>28240</v>
@@ -4481,14 +4481,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="9"/>
-        <v>18096</v>
+        <v>18097</v>
       </c>
       <c r="AE26" s="5">
-        <v>24962</v>
+        <v>24963</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="10"/>
-        <v>0.8839235127478754</v>
+        <v>0.88395892351274785</v>
       </c>
       <c r="AG26" s="5">
         <v>16538</v>
@@ -4498,14 +4498,14 @@
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="11"/>
-        <v>8857</v>
+        <v>8858</v>
       </c>
       <c r="AJ26" s="5">
-        <v>13474</v>
+        <v>13475</v>
       </c>
       <c r="AK26" s="4">
         <f t="shared" si="12"/>
-        <v>0.81472971338735034</v>
+        <v>0.81479018019107508</v>
       </c>
       <c r="AL26" s="5">
         <v>16671</v>
@@ -4515,14 +4515,14 @@
       </c>
       <c r="AN26" s="3">
         <f t="shared" si="13"/>
-        <v>8883</v>
+        <v>8885</v>
       </c>
       <c r="AO26" s="5">
-        <v>13577</v>
+        <v>13579</v>
       </c>
       <c r="AP26" s="4">
         <f t="shared" si="14"/>
-        <v>0.81440825385399795</v>
+        <v>0.81452822266210789</v>
       </c>
       <c r="AQ26" s="3">
         <v>28406</v>
@@ -4532,14 +4532,14 @@
       </c>
       <c r="AS26" s="3">
         <f t="shared" si="15"/>
-        <v>17041</v>
+        <v>17043</v>
       </c>
       <c r="AT26" s="3">
-        <v>25115</v>
+        <v>25117</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="16"/>
-        <v>0.8841441948884039</v>
+        <v>0.88421460254875728</v>
       </c>
       <c r="AV26" s="5">
         <v>16717</v>
@@ -4549,14 +4549,14 @@
       </c>
       <c r="AX26" s="3">
         <f t="shared" si="17"/>
-        <v>8247</v>
+        <v>8249</v>
       </c>
       <c r="AY26" s="5">
-        <v>13277</v>
+        <v>13279</v>
       </c>
       <c r="AZ26" s="4">
         <f t="shared" si="18"/>
-        <v>0.79422145121732368</v>
+        <v>0.79434108990847641</v>
       </c>
       <c r="BA26" s="10">
         <v>13719</v>
@@ -4566,14 +4566,14 @@
       </c>
       <c r="BC26" s="3">
         <f t="shared" si="19"/>
-        <v>8540</v>
+        <v>8542</v>
       </c>
       <c r="BD26" s="5">
-        <v>13374</v>
+        <v>13376</v>
       </c>
       <c r="BE26" s="4">
         <f t="shared" si="20"/>
-        <v>0.97485239448939431</v>
+        <v>0.97499817770974562</v>
       </c>
       <c r="BF26" s="10">
         <v>25779</v>
@@ -4583,14 +4583,14 @@
       </c>
       <c r="BH26" s="3">
         <f t="shared" si="21"/>
-        <v>17877</v>
+        <v>17879</v>
       </c>
       <c r="BI26" s="5">
-        <v>25162</v>
+        <v>25164</v>
       </c>
       <c r="BJ26" s="4">
         <f t="shared" si="22"/>
-        <v>0.97606578998409554</v>
+        <v>0.97614337251251015</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4608,14 +4608,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>70249</v>
+        <v>70252</v>
       </c>
       <c r="F27" s="5">
-        <v>109139</v>
+        <v>109142</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>0.92095758864530064</v>
+        <v>0.92098290381921588</v>
       </c>
       <c r="H27" s="5">
         <v>121212</v>
@@ -4625,14 +4625,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>66316</v>
+        <v>66320</v>
       </c>
       <c r="K27" s="5">
-        <v>111213</v>
+        <v>111217</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.91750816750816755</v>
+        <v>0.91754116754116755</v>
       </c>
       <c r="M27" s="9">
         <v>178312</v>
@@ -4644,11 +4644,11 @@
         <v>161829</v>
       </c>
       <c r="P27" s="5">
-        <v>163124</v>
+        <v>163129</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="4"/>
-        <v>0.91482345551617394</v>
+        <v>0.9148514962537575</v>
       </c>
       <c r="R27" s="5">
         <v>121489</v>
@@ -4658,14 +4658,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="5"/>
-        <v>67705</v>
+        <v>67709</v>
       </c>
       <c r="U27" s="5">
-        <v>111733</v>
+        <v>111737</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="6"/>
-        <v>0.91969643342195595</v>
+        <v>0.91972935821350077</v>
       </c>
       <c r="W27" s="5">
         <v>123451</v>
@@ -4675,14 +4675,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="7"/>
-        <v>70989</v>
+        <v>70993</v>
       </c>
       <c r="Z27" s="5">
-        <v>113715</v>
+        <v>113719</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="8"/>
-        <v>0.92113470121748708</v>
+        <v>0.92116710273711833</v>
       </c>
       <c r="AB27" s="5">
         <v>182601</v>
@@ -4692,14 +4692,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="9"/>
-        <v>117977</v>
+        <v>117983</v>
       </c>
       <c r="AE27" s="5">
-        <v>173249</v>
+        <v>173255</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="10"/>
-        <v>0.94878450829951644</v>
+        <v>0.94881736682712581</v>
       </c>
       <c r="AG27" s="5">
         <v>124689</v>
@@ -4709,14 +4709,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="11"/>
-        <v>69021</v>
+        <v>69025</v>
       </c>
       <c r="AJ27" s="5">
-        <v>117352</v>
+        <v>117356</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="12"/>
-        <v>0.94115760010907135</v>
+        <v>0.94118967992364999</v>
       </c>
       <c r="AL27" s="5">
         <v>127177</v>
@@ -4726,14 +4726,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" si="13"/>
-        <v>69460</v>
+        <v>69464</v>
       </c>
       <c r="AO27" s="5">
-        <v>119047</v>
+        <v>119051</v>
       </c>
       <c r="AP27" s="4">
         <f t="shared" si="14"/>
-        <v>0.93607334659568953</v>
+        <v>0.93610479882368669</v>
       </c>
       <c r="AQ27" s="3">
         <v>185152</v>
@@ -4743,14 +4743,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" si="15"/>
-        <v>105622</v>
+        <v>105627</v>
       </c>
       <c r="AT27" s="3">
-        <v>176818</v>
+        <v>176823</v>
       </c>
       <c r="AU27" s="4">
         <f t="shared" si="16"/>
-        <v>0.9549883339094366</v>
+        <v>0.95501533874870381</v>
       </c>
       <c r="AV27" s="5">
         <v>127611</v>
@@ -4760,14 +4760,14 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" si="17"/>
-        <v>66569</v>
+        <v>66572</v>
       </c>
       <c r="AY27" s="5">
-        <v>119116</v>
+        <v>119119</v>
       </c>
       <c r="AZ27" s="4">
         <f t="shared" si="18"/>
-        <v>0.93343050363996838</v>
+        <v>0.93345401258512195</v>
       </c>
       <c r="BA27" s="10">
         <v>122070</v>
@@ -4777,14 +4777,14 @@
       </c>
       <c r="BC27" s="3">
         <f t="shared" si="19"/>
-        <v>69512</v>
+        <v>69516</v>
       </c>
       <c r="BD27" s="5">
-        <v>120777</v>
+        <v>120781</v>
       </c>
       <c r="BE27" s="4">
         <f t="shared" si="20"/>
-        <v>0.98940771688375517</v>
+        <v>0.98944048496764148</v>
       </c>
       <c r="BF27" s="10">
         <v>180737</v>
@@ -4794,14 +4794,14 @@
       </c>
       <c r="BH27" s="3">
         <f t="shared" si="21"/>
-        <v>116077</v>
+        <v>116083</v>
       </c>
       <c r="BI27" s="5">
-        <v>179742</v>
+        <v>179748</v>
       </c>
       <c r="BJ27" s="4">
         <f t="shared" si="22"/>
-        <v>0.99449476310882667</v>
+        <v>0.99452796051721559</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4819,14 +4819,14 @@
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>155505</v>
+        <v>155507</v>
       </c>
       <c r="F28" s="5">
-        <v>342707</v>
+        <v>342709</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>0.94057251070369963</v>
+        <v>0.94057799978043688</v>
       </c>
       <c r="H28" s="5">
         <v>368904</v>
@@ -4836,14 +4836,14 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>152908</v>
+        <v>152909</v>
       </c>
       <c r="K28" s="5">
-        <v>347630</v>
+        <v>347631</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="3"/>
-        <v>0.94233188038080373</v>
+        <v>0.94233459111313511</v>
       </c>
       <c r="M28" s="9">
         <v>633580</v>
@@ -4855,11 +4855,11 @@
         <v>594498</v>
       </c>
       <c r="P28" s="5">
-        <v>595745</v>
+        <v>595748</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="4"/>
-        <v>0.94028378421036019</v>
+        <v>0.94028851920830836</v>
       </c>
       <c r="R28" s="5">
         <v>370844</v>
@@ -4869,14 +4869,14 @@
       </c>
       <c r="T28" s="3">
         <f t="shared" si="5"/>
-        <v>152909</v>
+        <v>152911</v>
       </c>
       <c r="U28" s="5">
-        <v>350178</v>
+        <v>350180</v>
       </c>
       <c r="V28" s="4">
         <f t="shared" si="6"/>
-        <v>0.94427306360626029</v>
+        <v>0.94427845670955979</v>
       </c>
       <c r="W28" s="5">
         <v>375522</v>
@@ -4886,14 +4886,14 @@
       </c>
       <c r="Y28" s="3">
         <f t="shared" si="7"/>
-        <v>159774</v>
+        <v>159776</v>
       </c>
       <c r="Z28" s="5">
-        <v>355205</v>
+        <v>355207</v>
       </c>
       <c r="AA28" s="4">
         <f t="shared" si="8"/>
-        <v>0.94589664520321048</v>
+        <v>0.94590197112286367</v>
       </c>
       <c r="AB28" s="5">
         <v>643156</v>
@@ -4903,14 +4903,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="9"/>
-        <v>319758</v>
+        <v>319761</v>
       </c>
       <c r="AE28" s="5">
-        <v>621205</v>
+        <v>621208</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="10"/>
-        <v>0.96586986671973829</v>
+        <v>0.96587453121793154</v>
       </c>
       <c r="AG28" s="5">
         <v>378725</v>
@@ -4920,14 +4920,14 @@
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="11"/>
-        <v>153063</v>
+        <v>153066</v>
       </c>
       <c r="AJ28" s="5">
-        <v>362802</v>
+        <v>362805</v>
       </c>
       <c r="AK28" s="4">
         <f t="shared" si="12"/>
-        <v>0.95795630074592386</v>
+        <v>0.95796422206086207</v>
       </c>
       <c r="AL28" s="5">
         <v>382864</v>
@@ -4937,14 +4937,14 @@
       </c>
       <c r="AN28" s="3">
         <f t="shared" si="13"/>
-        <v>155546</v>
+        <v>155549</v>
       </c>
       <c r="AO28" s="5">
-        <v>368179</v>
+        <v>368182</v>
       </c>
       <c r="AP28" s="4">
         <f t="shared" si="14"/>
-        <v>0.96164434368339669</v>
+        <v>0.96165217936395164</v>
       </c>
       <c r="AQ28" s="3">
         <v>653033</v>
@@ -4954,14 +4954,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="15"/>
-        <v>268771</v>
+        <v>268774</v>
       </c>
       <c r="AT28" s="3">
-        <v>629788</v>
+        <v>629791</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" si="16"/>
-        <v>0.96440455535937697</v>
+        <v>0.96440914930792165</v>
       </c>
       <c r="AV28" s="5">
         <v>393378</v>
@@ -4971,14 +4971,14 @@
       </c>
       <c r="AX28" s="3">
         <f t="shared" si="17"/>
-        <v>145237</v>
+        <v>145240</v>
       </c>
       <c r="AY28" s="5">
-        <v>371028</v>
+        <v>371031</v>
       </c>
       <c r="AZ28" s="4">
         <f t="shared" si="18"/>
-        <v>0.94318441804066322</v>
+        <v>0.94319204429327519</v>
       </c>
       <c r="BA28" s="10">
         <v>381893</v>
@@ -4988,14 +4988,14 @@
       </c>
       <c r="BC28" s="3">
         <f t="shared" si="19"/>
-        <v>155338</v>
+        <v>155341</v>
       </c>
       <c r="BD28" s="5">
-        <v>376424</v>
+        <v>376427</v>
       </c>
       <c r="BE28" s="4">
         <f t="shared" si="20"/>
-        <v>0.9856792347594745</v>
+        <v>0.98568709036300739</v>
       </c>
       <c r="BF28" s="10">
         <v>643514</v>
@@ -5005,14 +5005,14 @@
       </c>
       <c r="BH28" s="3">
         <f t="shared" si="21"/>
-        <v>301325</v>
+        <v>301327</v>
       </c>
       <c r="BI28" s="5">
-        <v>640674</v>
+        <v>640676</v>
       </c>
       <c r="BJ28" s="4">
         <f t="shared" si="22"/>
-        <v>0.99558673160179889</v>
+        <v>0.99558983953729052</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5030,14 +5030,14 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>61357</v>
+        <v>61358</v>
       </c>
       <c r="F29" s="5">
-        <v>113609</v>
+        <v>113610</v>
       </c>
       <c r="G29" s="4">
         <f t="shared" si="1"/>
-        <v>0.9423596940891521</v>
+        <v>0.94236798885183892</v>
       </c>
       <c r="H29" s="5">
         <v>121339</v>
@@ -5047,14 +5047,14 @@
       </c>
       <c r="J29" s="3">
         <f t="shared" si="2"/>
-        <v>63074</v>
+        <v>63075</v>
       </c>
       <c r="K29" s="5">
-        <v>114672</v>
+        <v>114673</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="3"/>
-        <v>0.94505476392586063</v>
+        <v>0.94506300529920306</v>
       </c>
       <c r="M29" s="9">
         <v>168897</v>
@@ -5066,11 +5066,11 @@
         <v>159082</v>
       </c>
       <c r="P29" s="5">
-        <v>159523</v>
+        <v>159524</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="4"/>
-        <v>0.94449871815366759</v>
+        <v>0.94450463892194647</v>
       </c>
       <c r="R29" s="5">
         <v>122532</v>
@@ -5080,14 +5080,14 @@
       </c>
       <c r="T29" s="3">
         <f t="shared" si="5"/>
-        <v>61110</v>
+        <v>61111</v>
       </c>
       <c r="U29" s="5">
-        <v>115919</v>
+        <v>115920</v>
       </c>
       <c r="V29" s="4">
         <f t="shared" si="6"/>
-        <v>0.94603042470538312</v>
+        <v>0.94603858583880129</v>
       </c>
       <c r="W29" s="5">
         <v>124179</v>
@@ -5097,14 +5097,14 @@
       </c>
       <c r="Y29" s="3">
         <f t="shared" si="7"/>
-        <v>62470</v>
+        <v>62471</v>
       </c>
       <c r="Z29" s="5">
-        <v>117316</v>
+        <v>117317</v>
       </c>
       <c r="AA29" s="4">
         <f t="shared" si="8"/>
-        <v>0.94473300638594282</v>
+        <v>0.94474105927733354</v>
       </c>
       <c r="AB29" s="5">
         <v>172673</v>
@@ -5114,14 +5114,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="9"/>
-        <v>96105</v>
+        <v>96106</v>
       </c>
       <c r="AE29" s="5">
-        <v>166283</v>
+        <v>166284</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="10"/>
-        <v>0.96299363536858684</v>
+        <v>0.96299942666195637</v>
       </c>
       <c r="AG29" s="5">
         <v>125793</v>
@@ -5131,14 +5131,14 @@
       </c>
       <c r="AI29" s="3">
         <f t="shared" si="11"/>
-        <v>61138</v>
+        <v>61139</v>
       </c>
       <c r="AJ29" s="5">
-        <v>120741</v>
+        <v>120742</v>
       </c>
       <c r="AK29" s="4">
         <f t="shared" si="12"/>
-        <v>0.95983878276215684</v>
+        <v>0.95984673233009787</v>
       </c>
       <c r="AL29" s="5">
         <v>126934</v>
@@ -5148,14 +5148,14 @@
       </c>
       <c r="AN29" s="3">
         <f t="shared" si="13"/>
-        <v>59756</v>
+        <v>59757</v>
       </c>
       <c r="AO29" s="5">
-        <v>122149</v>
+        <v>122150</v>
       </c>
       <c r="AP29" s="4">
         <f t="shared" si="14"/>
-        <v>0.96230324420565017</v>
+        <v>0.96231112231553406</v>
       </c>
       <c r="AQ29" s="3">
         <v>175834</v>
@@ -5165,14 +5165,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="15"/>
-        <v>84974</v>
+        <v>84975</v>
       </c>
       <c r="AT29" s="3">
-        <v>169374</v>
+        <v>169375</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="16"/>
-        <v>0.96326080280264337</v>
+        <v>0.96326648998487208</v>
       </c>
       <c r="AV29" s="5">
         <v>130198</v>
@@ -5182,14 +5182,14 @@
       </c>
       <c r="AX29" s="3">
         <f t="shared" si="17"/>
-        <v>57546</v>
+        <v>57547</v>
       </c>
       <c r="AY29" s="5">
-        <v>123684</v>
+        <v>123685</v>
       </c>
       <c r="AZ29" s="4">
         <f t="shared" si="18"/>
-        <v>0.94996850950091394</v>
+        <v>0.94997619011044721</v>
       </c>
       <c r="BA29" s="10">
         <v>127545</v>
@@ -5199,14 +5199,14 @@
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="19"/>
-        <v>63485</v>
+        <v>63486</v>
       </c>
       <c r="BD29" s="5">
-        <v>125566</v>
+        <v>125567</v>
       </c>
       <c r="BE29" s="4">
         <f t="shared" si="20"/>
-        <v>0.98448390764044058</v>
+        <v>0.9844917480105061</v>
       </c>
       <c r="BF29" s="10">
         <v>174166</v>
@@ -5216,14 +5216,14 @@
       </c>
       <c r="BH29" s="3">
         <f t="shared" si="21"/>
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="BI29" s="5">
-        <v>172942</v>
+        <v>172944</v>
       </c>
       <c r="BJ29" s="4">
         <f t="shared" si="22"/>
-        <v>0.99297222190324175</v>
+        <v>0.99298370520078549</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>88712</v>
+        <v>88714</v>
       </c>
       <c r="F30" s="5">
-        <v>147124</v>
+        <v>147126</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>0.92748981881910908</v>
+        <v>0.92750242709265818</v>
       </c>
       <c r="H30" s="5">
         <v>160653</v>
@@ -5258,14 +5258,14 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>85767</v>
+        <v>85769</v>
       </c>
       <c r="K30" s="5">
-        <v>150118</v>
+        <v>150120</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="3"/>
-        <v>0.93442388252942676</v>
+        <v>0.93443633172116303</v>
       </c>
       <c r="M30" s="9">
         <v>275749</v>
@@ -5277,11 +5277,11 @@
         <v>254361</v>
       </c>
       <c r="P30" s="5">
-        <v>255527</v>
+        <v>255530</v>
       </c>
       <c r="Q30" s="4">
         <f t="shared" si="4"/>
-        <v>0.92666519189552821</v>
+        <v>0.9266760713547465</v>
       </c>
       <c r="R30" s="5">
         <v>161454</v>
@@ -5291,14 +5291,14 @@
       </c>
       <c r="T30" s="3">
         <f t="shared" si="5"/>
-        <v>89019</v>
+        <v>89021</v>
       </c>
       <c r="U30" s="5">
-        <v>150304</v>
+        <v>150306</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" si="6"/>
-        <v>0.93094008200478151</v>
+        <v>0.93095246943401833</v>
       </c>
       <c r="W30" s="5">
         <v>163696</v>
@@ -5308,14 +5308,14 @@
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="7"/>
-        <v>91671</v>
+        <v>91673</v>
       </c>
       <c r="Z30" s="5">
-        <v>153488</v>
+        <v>153490</v>
       </c>
       <c r="AA30" s="4">
         <f t="shared" si="8"/>
-        <v>0.93764050434952595</v>
+        <v>0.93765272211904993</v>
       </c>
       <c r="AB30" s="5">
         <v>281667</v>
@@ -5325,14 +5325,14 @@
       </c>
       <c r="AD30" s="3">
         <f t="shared" si="9"/>
-        <v>177388</v>
+        <v>177392</v>
       </c>
       <c r="AE30" s="5">
-        <v>271178</v>
+        <v>271182</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="10"/>
-        <v>0.96276099081539546</v>
+        <v>0.96277519198202133</v>
       </c>
       <c r="AG30" s="5">
         <v>165324</v>
@@ -5342,14 +5342,14 @@
       </c>
       <c r="AI30" s="3">
         <f t="shared" si="11"/>
-        <v>90154</v>
+        <v>90156</v>
       </c>
       <c r="AJ30" s="5">
-        <v>158271</v>
+        <v>158273</v>
       </c>
       <c r="AK30" s="4">
         <f t="shared" si="12"/>
-        <v>0.95733831748566456</v>
+        <v>0.95735041494277906</v>
       </c>
       <c r="AL30" s="5">
         <v>168552</v>
@@ -5359,14 +5359,14 @@
       </c>
       <c r="AN30" s="3">
         <f t="shared" si="13"/>
-        <v>88491</v>
+        <v>88493</v>
       </c>
       <c r="AO30" s="5">
-        <v>161678</v>
+        <v>161680</v>
       </c>
       <c r="AP30" s="4">
         <f t="shared" si="14"/>
-        <v>0.95921733352318572</v>
+        <v>0.95922919929754613</v>
       </c>
       <c r="AQ30" s="3">
         <v>288456</v>
@@ -5376,14 +5376,14 @@
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="15"/>
-        <v>160994</v>
+        <v>160997</v>
       </c>
       <c r="AT30" s="3">
-        <v>277801</v>
+        <v>277804</v>
       </c>
       <c r="AU30" s="4">
         <f t="shared" si="16"/>
-        <v>0.96306195745624978</v>
+        <v>0.96307235765593369</v>
       </c>
       <c r="AV30" s="5">
         <v>173481</v>
@@ -5393,14 +5393,14 @@
       </c>
       <c r="AX30" s="3">
         <f t="shared" si="17"/>
-        <v>85703</v>
+        <v>85705</v>
       </c>
       <c r="AY30" s="5">
-        <v>162673</v>
+        <v>162675</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="18"/>
-        <v>0.93769922931041438</v>
+        <v>0.93771075795043834</v>
       </c>
       <c r="BA30" s="10">
         <v>168414</v>
@@ -5410,14 +5410,14 @@
       </c>
       <c r="BC30" s="3">
         <f t="shared" si="19"/>
-        <v>90664</v>
+        <v>90666</v>
       </c>
       <c r="BD30" s="5">
-        <v>165615</v>
+        <v>165617</v>
       </c>
       <c r="BE30" s="4">
         <f t="shared" si="20"/>
-        <v>0.98338024154761483</v>
+        <v>0.98339211704490126</v>
       </c>
       <c r="BF30" s="10">
         <v>284492</v>
@@ -5427,14 +5427,14 @@
       </c>
       <c r="BH30" s="3">
         <f t="shared" si="21"/>
-        <v>173859</v>
+        <v>173862</v>
       </c>
       <c r="BI30" s="5">
-        <v>283722</v>
+        <v>283725</v>
       </c>
       <c r="BJ30" s="4">
         <f t="shared" si="22"/>
-        <v>0.99729342125613374</v>
+        <v>0.9973039663681228</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5452,14 +5452,14 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>37121</v>
+        <v>37122</v>
       </c>
       <c r="F31" s="5">
-        <v>70032</v>
+        <v>70033</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>0.9419233355749832</v>
+        <v>0.94193678547410897</v>
       </c>
       <c r="H31" s="5">
         <v>75353</v>
@@ -5469,14 +5469,14 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>35314</v>
+        <v>35315</v>
       </c>
       <c r="K31" s="5">
-        <v>71152</v>
+        <v>71153</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="3"/>
-        <v>0.94424906772125861</v>
+        <v>0.94426233859302222</v>
       </c>
       <c r="M31" s="9">
         <v>132153</v>
@@ -5488,11 +5488,11 @@
         <v>124102</v>
       </c>
       <c r="P31" s="5">
-        <v>124755</v>
+        <v>124759</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="4"/>
-        <v>0.94401943202197458</v>
+        <v>0.94404969996897536</v>
       </c>
       <c r="R31" s="5">
         <v>74474</v>
@@ -5502,14 +5502,14 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="5"/>
-        <v>35660</v>
+        <v>35661</v>
       </c>
       <c r="U31" s="5">
-        <v>70003</v>
+        <v>70004</v>
       </c>
       <c r="V31" s="4">
         <f t="shared" si="6"/>
-        <v>0.93996562558745334</v>
+        <v>0.93997905309235441</v>
       </c>
       <c r="W31" s="5">
         <v>75697</v>
@@ -5519,14 +5519,14 @@
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="7"/>
-        <v>36678</v>
+        <v>36679</v>
       </c>
       <c r="Z31" s="5">
-        <v>71282</v>
+        <v>71283</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" si="8"/>
-        <v>0.9416753636207511</v>
+        <v>0.94168857418391749</v>
       </c>
       <c r="AB31" s="5">
         <v>133809</v>
@@ -5536,14 +5536,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="9"/>
-        <v>73411</v>
+        <v>73413</v>
       </c>
       <c r="AE31" s="5">
-        <v>129297</v>
+        <v>129299</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="10"/>
-        <v>0.9662802950474183</v>
+        <v>0.96629524172514558</v>
       </c>
       <c r="AG31" s="5">
         <v>75434</v>
@@ -5587,14 +5587,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="15"/>
-        <v>64955</v>
+        <v>64957</v>
       </c>
       <c r="AT31" s="3">
-        <v>131247</v>
+        <v>131249</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="16"/>
-        <v>0.96828382984374306</v>
+        <v>0.9682985849822201</v>
       </c>
       <c r="AV31" s="5">
         <v>78435</v>
@@ -5638,14 +5638,14 @@
       </c>
       <c r="BH31" s="3">
         <f t="shared" si="21"/>
-        <v>74229</v>
+        <v>74230</v>
       </c>
       <c r="BI31" s="5">
-        <v>133204</v>
+        <v>133205</v>
       </c>
       <c r="BJ31" s="4">
         <f t="shared" si="22"/>
-        <v>1.001759795442581</v>
+        <v>1.0017673159359255</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5663,14 +5663,14 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>91611</v>
+        <v>91612</v>
       </c>
       <c r="F32" s="5">
-        <v>184445</v>
+        <v>184446</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>0.96066104855258905</v>
+        <v>0.96066625694017649</v>
       </c>
       <c r="H32" s="5">
         <v>196288</v>
@@ -5680,14 +5680,14 @@
       </c>
       <c r="J32" s="3">
         <f t="shared" si="2"/>
-        <v>87697</v>
+        <v>87698</v>
       </c>
       <c r="K32" s="5">
-        <v>188230</v>
+        <v>188231</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="3"/>
-        <v>0.95894807629605483</v>
+        <v>0.95895317085099441</v>
       </c>
       <c r="M32" s="9">
         <v>418497</v>
@@ -5699,11 +5699,11 @@
         <v>397306</v>
       </c>
       <c r="P32" s="5">
-        <v>398330</v>
+        <v>398332</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="4"/>
-        <v>0.95181088514374057</v>
+        <v>0.95181566415051955</v>
       </c>
       <c r="R32" s="5">
         <v>194320</v>
@@ -5713,14 +5713,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="5"/>
-        <v>94018</v>
+        <v>94019</v>
       </c>
       <c r="U32" s="5">
-        <v>186167</v>
+        <v>186168</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="6"/>
-        <v>0.95804343351173327</v>
+        <v>0.95804857966241252</v>
       </c>
       <c r="W32" s="5">
         <v>198209</v>
@@ -5730,14 +5730,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="7"/>
-        <v>97019</v>
+        <v>97020</v>
       </c>
       <c r="Z32" s="5">
-        <v>190199</v>
+        <v>190200</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="8"/>
-        <v>0.95958811153883028</v>
+        <v>0.95959315671841339</v>
       </c>
       <c r="AB32" s="5">
         <v>426405</v>
@@ -5747,14 +5747,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="9"/>
-        <v>243326</v>
+        <v>243327</v>
       </c>
       <c r="AE32" s="5">
-        <v>418625</v>
+        <v>418626</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="10"/>
-        <v>0.98175443533729667</v>
+        <v>0.9817567805255567</v>
       </c>
       <c r="AG32" s="5">
         <v>199136</v>
@@ -5764,14 +5764,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="11"/>
-        <v>82207</v>
+        <v>82208</v>
       </c>
       <c r="AJ32" s="5">
-        <v>194597</v>
+        <v>194598</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="12"/>
-        <v>0.97720653221918685</v>
+        <v>0.97721155391290371</v>
       </c>
       <c r="AL32" s="5">
         <v>204506</v>
@@ -5781,14 +5781,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="13"/>
-        <v>84510</v>
+        <v>84512</v>
       </c>
       <c r="AO32" s="5">
-        <v>199092</v>
+        <v>199094</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="14"/>
-        <v>0.9735264491017378</v>
+        <v>0.97353622876590418</v>
       </c>
       <c r="AQ32" s="3">
         <v>435626</v>
@@ -5798,14 +5798,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="15"/>
-        <v>206039</v>
+        <v>206042</v>
       </c>
       <c r="AT32" s="3">
-        <v>427431</v>
+        <v>427434</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="16"/>
-        <v>0.98118799153402225</v>
+        <v>0.98119487817531548</v>
       </c>
       <c r="AV32" s="5">
         <v>208760</v>
@@ -5815,14 +5815,14 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="17"/>
-        <v>78089</v>
+        <v>78092</v>
       </c>
       <c r="AY32" s="5">
-        <v>198448</v>
+        <v>198451</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="18"/>
-        <v>0.95060356390113043</v>
+        <v>0.95061793447020504</v>
       </c>
       <c r="BA32" s="10">
         <v>206539</v>
@@ -5832,14 +5832,14 @@
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="19"/>
-        <v>86626</v>
+        <v>86629</v>
       </c>
       <c r="BD32" s="5">
-        <v>203323</v>
+        <v>203326</v>
       </c>
       <c r="BE32" s="4">
         <f t="shared" si="20"/>
-        <v>0.98442909087387853</v>
+        <v>0.98444361597567531</v>
       </c>
       <c r="BF32" s="10">
         <v>435831</v>
@@ -5849,14 +5849,14 @@
       </c>
       <c r="BH32" s="3">
         <f t="shared" si="21"/>
-        <v>241654</v>
+        <v>241657</v>
       </c>
       <c r="BI32" s="5">
-        <v>436075</v>
+        <v>436078</v>
       </c>
       <c r="BJ32" s="4">
         <f t="shared" si="22"/>
-        <v>1.0005598500336139</v>
+        <v>1.0005667334356665</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5874,14 +5874,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>112234</v>
+        <v>112237</v>
       </c>
       <c r="F33" s="5">
-        <v>577924</v>
+        <v>577927</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>0.98536590356125331</v>
+        <v>0.98537101858971843</v>
       </c>
       <c r="H33" s="5">
         <v>594451</v>
@@ -5891,14 +5891,14 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>102377</v>
+        <v>102379</v>
       </c>
       <c r="K33" s="5">
-        <v>588537</v>
+        <v>588539</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="3"/>
-        <v>0.99005132466763446</v>
+        <v>0.99005468911651251</v>
       </c>
       <c r="M33" s="9">
         <v>1006436</v>
@@ -5910,11 +5910,11 @@
         <v>989274</v>
       </c>
       <c r="P33" s="5">
-        <v>989987</v>
+        <v>989992</v>
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="4"/>
-        <v>0.98365618876908223</v>
+        <v>0.98366115679486821</v>
       </c>
       <c r="R33" s="5">
         <v>599279</v>
@@ -5924,14 +5924,14 @@
       </c>
       <c r="T33" s="3">
         <f t="shared" si="5"/>
-        <v>115342</v>
+        <v>115344</v>
       </c>
       <c r="U33" s="5">
-        <v>590809</v>
+        <v>590811</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="6"/>
-        <v>0.98586634939652484</v>
+        <v>0.9858696867402329</v>
       </c>
       <c r="W33" s="5">
         <v>608923</v>
@@ -5941,14 +5941,14 @@
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="7"/>
-        <v>119616</v>
+        <v>119618</v>
       </c>
       <c r="Z33" s="5">
-        <v>598472</v>
+        <v>598474</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" si="8"/>
-        <v>0.98283691041396037</v>
+        <v>0.98284019490148999</v>
       </c>
       <c r="AB33" s="5">
         <v>1019860</v>
@@ -5958,14 +5958,14 @@
       </c>
       <c r="AD33" s="3">
         <f t="shared" si="9"/>
-        <v>208796</v>
+        <v>208798</v>
       </c>
       <c r="AE33" s="5">
-        <v>1007592</v>
+        <v>1007594</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="10"/>
-        <v>0.9879708979663876</v>
+        <v>0.98797285901986542</v>
       </c>
       <c r="AG33" s="5">
         <v>610453</v>
@@ -5975,14 +5975,14 @@
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="11"/>
-        <v>103204</v>
+        <v>103206</v>
       </c>
       <c r="AJ33" s="5">
-        <v>601261</v>
+        <v>601263</v>
       </c>
       <c r="AK33" s="4">
         <f t="shared" si="12"/>
-        <v>0.98494232971252493</v>
+        <v>0.98494560596802705</v>
       </c>
       <c r="AL33" s="5">
         <v>617988</v>
@@ -5992,14 +5992,14 @@
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="13"/>
-        <v>97621</v>
+        <v>97622</v>
       </c>
       <c r="AO33" s="5">
-        <v>607252</v>
+        <v>607253</v>
       </c>
       <c r="AP33" s="4">
         <f t="shared" si="14"/>
-        <v>0.98262749438500419</v>
+        <v>0.98262911253940211</v>
       </c>
       <c r="AQ33" s="3">
         <v>1027609</v>
@@ -6009,14 +6009,14 @@
       </c>
       <c r="AS33" s="3">
         <f t="shared" si="15"/>
-        <v>158969</v>
+        <v>158971</v>
       </c>
       <c r="AT33" s="3">
-        <v>1016490</v>
+        <v>1016492</v>
       </c>
       <c r="AU33" s="4">
         <f t="shared" si="16"/>
-        <v>0.98917973665080783</v>
+        <v>0.9891816829163621</v>
       </c>
       <c r="AV33" s="5">
         <v>625585</v>
@@ -6026,14 +6026,14 @@
       </c>
       <c r="AX33" s="3">
         <f t="shared" si="17"/>
-        <v>80340</v>
+        <v>80341</v>
       </c>
       <c r="AY33" s="5">
-        <v>609869</v>
+        <v>609870</v>
       </c>
       <c r="AZ33" s="4">
         <f t="shared" si="18"/>
-        <v>0.97487791427224113</v>
+        <v>0.97487951277604168</v>
       </c>
       <c r="BA33" s="10">
         <v>617039</v>
@@ -6043,14 +6043,14 @@
       </c>
       <c r="BC33" s="3">
         <f t="shared" si="19"/>
-        <v>85342</v>
+        <v>85343</v>
       </c>
       <c r="BD33" s="5">
-        <v>616847</v>
+        <v>616848</v>
       </c>
       <c r="BE33" s="4">
         <f t="shared" si="20"/>
-        <v>0.99968883652410945</v>
+        <v>0.99969045716721305</v>
       </c>
       <c r="BF33" s="10">
         <v>1025594</v>
@@ -6060,14 +6060,14 @@
       </c>
       <c r="BH33" s="3">
         <f t="shared" si="21"/>
-        <v>198101</v>
+        <v>198103</v>
       </c>
       <c r="BI33" s="5">
-        <v>1029962</v>
+        <v>1029964</v>
       </c>
       <c r="BJ33" s="4">
         <f t="shared" si="22"/>
-        <v>1.0042589952749335</v>
+        <v>1.004260945364345</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6484,14 +6484,14 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="0"/>
-        <v>280751</v>
+        <v>280756</v>
       </c>
       <c r="F36" s="5">
-        <v>767037</v>
+        <v>767042</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="1"/>
-        <v>0.95384697650068206</v>
+        <v>0.95385319423839554</v>
       </c>
       <c r="H36" s="5">
         <v>814447</v>
@@ -6501,14 +6501,14 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="2"/>
-        <v>265476</v>
+        <v>265482</v>
       </c>
       <c r="K36" s="5">
-        <v>778886</v>
+        <v>778892</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="3"/>
-        <v>0.9563372447808145</v>
+        <v>0.9563446117426917</v>
       </c>
       <c r="M36" s="9">
         <v>1485608</v>
@@ -6520,11 +6520,11 @@
         <v>1417521</v>
       </c>
       <c r="P36" s="5">
-        <v>1420019</v>
+        <v>1420028</v>
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="4"/>
-        <v>0.95585039929779592</v>
+        <v>0.95585645742349257</v>
       </c>
       <c r="R36" s="5">
         <v>815623</v>
@@ -6534,14 +6534,14 @@
       </c>
       <c r="T36" s="3">
         <f t="shared" si="5"/>
-        <v>268193</v>
+        <v>268199</v>
       </c>
       <c r="U36" s="5">
-        <v>778548</v>
+        <v>778554</v>
       </c>
       <c r="V36" s="4">
         <f t="shared" si="6"/>
-        <v>0.95454394983957047</v>
+        <v>0.95455130617944806</v>
       </c>
       <c r="W36" s="5">
         <v>826349</v>
@@ -6551,14 +6551,14 @@
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="7"/>
-        <v>288615</v>
+        <v>288621</v>
       </c>
       <c r="Z36" s="5">
-        <v>788767</v>
+        <v>788773</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="8"/>
-        <v>0.95452042659941505</v>
+        <v>0.95452768745409022</v>
       </c>
       <c r="AB36" s="5">
         <v>1500292</v>
@@ -6568,14 +6568,14 @@
       </c>
       <c r="AD36" s="3">
         <f t="shared" si="9"/>
-        <v>549426</v>
+        <v>549433</v>
       </c>
       <c r="AE36" s="5">
-        <v>1455742</v>
+        <v>1455749</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="10"/>
-        <v>0.97030578047473426</v>
+        <v>0.97031044623313323</v>
       </c>
       <c r="AG36" s="5">
         <v>833041</v>
@@ -6585,14 +6585,14 @@
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="11"/>
-        <v>255498</v>
+        <v>255504</v>
       </c>
       <c r="AJ36" s="5">
-        <v>802883</v>
+        <v>802889</v>
       </c>
       <c r="AK36" s="4">
         <f t="shared" si="12"/>
-        <v>0.96379770023324185</v>
+        <v>0.96380490275988817</v>
       </c>
       <c r="AL36" s="5">
         <v>845911</v>
@@ -6602,14 +6602,14 @@
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="13"/>
-        <v>252974</v>
+        <v>252981</v>
       </c>
       <c r="AO36" s="5">
-        <v>815209</v>
+        <v>815216</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="14"/>
-        <v>0.96370540163208662</v>
+        <v>0.96371367673431363</v>
       </c>
       <c r="AQ36" s="3">
         <v>1519147</v>
@@ -6619,14 +6619,14 @@
       </c>
       <c r="AS36" s="3">
         <f t="shared" si="15"/>
-        <v>450259</v>
+        <v>450268</v>
       </c>
       <c r="AT36" s="3">
-        <v>1477399</v>
+        <v>1477408</v>
       </c>
       <c r="AU36" s="4">
         <f t="shared" si="16"/>
-        <v>0.97251878850433826</v>
+        <v>0.97252471288163689</v>
       </c>
       <c r="AV36" s="5">
         <v>864672</v>
@@ -6636,14 +6636,14 @@
       </c>
       <c r="AX36" s="3">
         <f t="shared" si="17"/>
-        <v>218887</v>
+        <v>218895</v>
       </c>
       <c r="AY36" s="5">
-        <v>817748</v>
+        <v>817756</v>
       </c>
       <c r="AZ36" s="4">
         <f t="shared" si="18"/>
-        <v>0.94573202324118277</v>
+        <v>0.94574127530439289</v>
       </c>
       <c r="BA36" s="10">
         <v>838532</v>
@@ -6653,14 +6653,14 @@
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="19"/>
-        <v>226531</v>
+        <v>226539</v>
       </c>
       <c r="BD36" s="5">
-        <v>830285</v>
+        <v>830293</v>
       </c>
       <c r="BE36" s="4">
         <f t="shared" si="20"/>
-        <v>0.99016495494507062</v>
+        <v>0.99017449542772373</v>
       </c>
       <c r="BF36" s="10">
         <v>1502094</v>
@@ -6670,14 +6670,14 @@
       </c>
       <c r="BH36" s="3">
         <f t="shared" si="23"/>
-        <v>507869</v>
+        <v>507878</v>
       </c>
       <c r="BI36" s="5">
-        <v>1498519</v>
+        <v>1498528</v>
       </c>
       <c r="BJ36" s="4">
         <f t="shared" si="24"/>
-        <v>0.99761998916179684</v>
+        <v>0.99762598079747344</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6695,14 +6695,14 @@
       </c>
       <c r="E37" s="3">
         <f t="shared" si="0"/>
-        <v>268698</v>
+        <v>268704</v>
       </c>
       <c r="F37" s="5">
-        <v>609915</v>
+        <v>609921</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="1"/>
-        <v>0.93741210536750907</v>
+        <v>0.93742132709944259</v>
       </c>
       <c r="H37" s="5">
         <v>656039</v>
@@ -6712,14 +6712,14 @@
       </c>
       <c r="J37" s="3">
         <f t="shared" si="2"/>
-        <v>249937</v>
+        <v>249943</v>
       </c>
       <c r="K37" s="5">
-        <v>615206</v>
+        <v>615212</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="3"/>
-        <v>0.9377582735172757</v>
+        <v>0.93776741931501029</v>
       </c>
       <c r="M37" s="9">
         <v>844882</v>
@@ -6731,11 +6731,11 @@
         <v>786859</v>
       </c>
       <c r="P37" s="5">
-        <v>789079</v>
+        <v>789086</v>
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="4"/>
-        <v>0.93395172343593547</v>
+        <v>0.9339600086165879</v>
       </c>
       <c r="R37" s="5">
         <v>664863</v>
@@ -6745,14 +6745,14 @@
       </c>
       <c r="T37" s="3">
         <f t="shared" si="5"/>
-        <v>256853</v>
+        <v>256861</v>
       </c>
       <c r="U37" s="5">
-        <v>621980</v>
+        <v>621988</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="6"/>
-        <v>0.93550099794995356</v>
+        <v>0.93551303050402868</v>
       </c>
       <c r="W37" s="5">
         <v>670009</v>
@@ -6762,14 +6762,14 @@
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="7"/>
-        <v>275174</v>
+        <v>275180</v>
       </c>
       <c r="Z37" s="5">
-        <v>628419</v>
+        <v>628425</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="8"/>
-        <v>0.93792620696139906</v>
+        <v>0.93793516206498717</v>
       </c>
       <c r="AB37" s="5">
         <v>858143</v>
@@ -6779,14 +6779,14 @@
       </c>
       <c r="AD37" s="3">
         <f t="shared" si="9"/>
-        <v>383164</v>
+        <v>383166</v>
       </c>
       <c r="AE37" s="5">
-        <v>819535</v>
+        <v>819537</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="10"/>
-        <v>0.95500982936410361</v>
+        <v>0.95501215997799904</v>
       </c>
       <c r="AG37" s="5">
         <v>675943</v>
@@ -6796,14 +6796,14 @@
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="11"/>
-        <v>251708</v>
+        <v>251711</v>
       </c>
       <c r="AJ37" s="5">
-        <v>644685</v>
+        <v>644688</v>
       </c>
       <c r="AK37" s="4">
         <f t="shared" si="12"/>
-        <v>0.95375645579582891</v>
+        <v>0.95376089403988207</v>
       </c>
       <c r="AL37" s="5">
         <v>678429</v>
@@ -6813,14 +6813,14 @@
       </c>
       <c r="AN37" s="3">
         <f t="shared" si="13"/>
-        <v>248277</v>
+        <v>248279</v>
       </c>
       <c r="AO37" s="5">
-        <v>650795</v>
+        <v>650797</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="14"/>
-        <v>0.95926766102274519</v>
+        <v>0.95927060900993322</v>
       </c>
       <c r="AQ37" s="3">
         <v>865622</v>
@@ -6830,14 +6830,14 @@
       </c>
       <c r="AS37" s="3">
         <f t="shared" si="15"/>
-        <v>314997</v>
+        <v>315000</v>
       </c>
       <c r="AT37" s="3">
-        <v>834241</v>
+        <v>834244</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="16"/>
-        <v>0.96374745558684971</v>
+        <v>0.96375092130283191</v>
       </c>
       <c r="AV37" s="5">
         <v>690116</v>
@@ -6847,14 +6847,14 @@
       </c>
       <c r="AX37" s="3">
         <f t="shared" si="17"/>
-        <v>235066</v>
+        <v>235071</v>
       </c>
       <c r="AY37" s="5">
-        <v>658592</v>
+        <v>658597</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="18"/>
-        <v>0.95432072289296288</v>
+        <v>0.9543279680517478</v>
       </c>
       <c r="BA37" s="10">
         <v>673244</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="19"/>
-        <v>241650</v>
+        <v>241655</v>
       </c>
       <c r="BD37" s="5">
-        <v>665217</v>
+        <v>665222</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="20"/>
-        <v>0.98807713102530437</v>
+        <v>0.98808455775320692</v>
       </c>
       <c r="BF37" s="10">
         <v>856336</v>
@@ -6881,14 +6881,14 @@
       </c>
       <c r="BH37" s="3">
         <f t="shared" si="23"/>
-        <v>356969</v>
+        <v>356974</v>
       </c>
       <c r="BI37" s="5">
-        <v>848352</v>
+        <v>848357</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="24"/>
-        <v>0.99067655686552947</v>
+        <v>0.99068239569514771</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7328,14 +7328,14 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="0"/>
-        <v>105547</v>
+        <v>105550</v>
       </c>
       <c r="F40" s="5">
-        <v>258594</v>
+        <v>258597</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="1"/>
-        <v>0.94557168923390822</v>
+        <v>0.94558265899758298</v>
       </c>
       <c r="H40" s="5">
         <v>275367</v>
@@ -7345,14 +7345,14 @@
       </c>
       <c r="J40" s="3">
         <f t="shared" si="2"/>
-        <v>98772</v>
+        <v>98775</v>
       </c>
       <c r="K40" s="5">
-        <v>260334</v>
+        <v>260337</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="3"/>
-        <v>0.94540740175838067</v>
+        <v>0.94541829631001539</v>
       </c>
       <c r="M40" s="9">
         <v>339208</v>
@@ -7364,11 +7364,11 @@
         <v>320573</v>
       </c>
       <c r="P40" s="5">
-        <v>321299</v>
+        <v>321304</v>
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="4"/>
-        <v>0.9472034857668451</v>
+        <v>0.9472182259852362</v>
       </c>
       <c r="R40" s="5">
         <v>277547</v>
@@ -7378,14 +7378,14 @@
       </c>
       <c r="T40" s="3">
         <f t="shared" si="5"/>
-        <v>97299</v>
+        <v>97305</v>
       </c>
       <c r="U40" s="5">
-        <v>262673</v>
+        <v>262679</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" si="6"/>
-        <v>0.94640907666088991</v>
+        <v>0.9464306946210912</v>
       </c>
       <c r="W40" s="5">
         <v>278758</v>
@@ -7395,14 +7395,14 @@
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="7"/>
-        <v>125348</v>
+        <v>125355</v>
       </c>
       <c r="Z40" s="5">
-        <v>265222</v>
+        <v>265229</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" si="8"/>
-        <v>0.95144175234432737</v>
+        <v>0.9514668637312651</v>
       </c>
       <c r="AB40" s="5">
         <v>343140</v>
@@ -7412,14 +7412,14 @@
       </c>
       <c r="AD40" s="3">
         <f t="shared" si="9"/>
-        <v>142729</v>
+        <v>142738</v>
       </c>
       <c r="AE40" s="5">
-        <v>328425</v>
+        <v>328434</v>
       </c>
       <c r="AF40" s="4">
         <f t="shared" si="10"/>
-        <v>0.95711662878125547</v>
+        <v>0.95714285714285718</v>
       </c>
       <c r="AG40" s="5">
         <v>282101</v>
@@ -7429,14 +7429,14 @@
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="11"/>
-        <v>100019</v>
+        <v>100027</v>
       </c>
       <c r="AJ40" s="5">
-        <v>268715</v>
+        <v>268723</v>
       </c>
       <c r="AK40" s="4">
         <f t="shared" si="12"/>
-        <v>0.95254890978762929</v>
+        <v>0.95257726842513857</v>
       </c>
       <c r="AL40" s="5">
         <v>282756</v>
@@ -7446,14 +7446,14 @@
       </c>
       <c r="AN40" s="3">
         <f t="shared" si="13"/>
-        <v>99025</v>
+        <v>99035</v>
       </c>
       <c r="AO40" s="5">
-        <v>270972</v>
+        <v>270982</v>
       </c>
       <c r="AP40" s="4">
         <f t="shared" si="14"/>
-        <v>0.95832449178797263</v>
+        <v>0.95835985796941536</v>
       </c>
       <c r="AQ40" s="3">
         <v>343988</v>
@@ -7463,14 +7463,14 @@
       </c>
       <c r="AS40" s="3">
         <f t="shared" si="15"/>
-        <v>125860</v>
+        <v>125872</v>
       </c>
       <c r="AT40" s="3">
-        <v>332723</v>
+        <v>332735</v>
       </c>
       <c r="AU40" s="4">
         <f t="shared" si="16"/>
-        <v>0.96725176459643936</v>
+        <v>0.96728664953428611</v>
       </c>
       <c r="AV40" s="5">
         <v>285285</v>
@@ -7480,14 +7480,14 @@
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="17"/>
-        <v>94340</v>
+        <v>94351</v>
       </c>
       <c r="AY40" s="5">
-        <v>273386</v>
+        <v>273397</v>
       </c>
       <c r="AZ40" s="4">
         <f t="shared" si="18"/>
-        <v>0.9582908319750425</v>
+        <v>0.95832938990833727</v>
       </c>
       <c r="BA40" s="10">
         <v>276279</v>
@@ -7497,14 +7497,14 @@
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="19"/>
-        <v>95256</v>
+        <v>95266</v>
       </c>
       <c r="BD40" s="5">
-        <v>275440</v>
+        <v>275450</v>
       </c>
       <c r="BE40" s="4">
         <f t="shared" si="20"/>
-        <v>0.99696321472135052</v>
+        <v>0.99699941001668602</v>
       </c>
       <c r="BF40" s="10">
         <v>339189</v>
@@ -7514,14 +7514,14 @@
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="23"/>
-        <v>141269</v>
+        <v>141278</v>
       </c>
       <c r="BI40" s="5">
-        <v>337570</v>
+        <v>337579</v>
       </c>
       <c r="BJ40" s="4">
         <f t="shared" si="24"/>
-        <v>0.99522684992732668</v>
+        <v>0.99525338380666828</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7539,14 +7539,14 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" si="0"/>
-        <v>326713</v>
+        <v>326737</v>
       </c>
       <c r="F41" s="5">
-        <v>832937</v>
+        <v>832961</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="1"/>
-        <v>0.95444774203898286</v>
+        <v>0.95447524321351229</v>
       </c>
       <c r="H41" s="5">
         <v>878008</v>
@@ -7556,14 +7556,14 @@
       </c>
       <c r="J41" s="3">
         <f t="shared" si="2"/>
-        <v>326520</v>
+        <v>326541</v>
       </c>
       <c r="K41" s="5">
-        <v>839644</v>
+        <v>839665</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="3"/>
-        <v>0.95630563730626605</v>
+        <v>0.95632955508378059</v>
       </c>
       <c r="M41" s="9">
         <v>999035</v>
@@ -7575,11 +7575,11 @@
         <v>948683</v>
       </c>
       <c r="P41" s="5">
-        <v>951004</v>
+        <v>951030</v>
       </c>
       <c r="Q41" s="4">
         <f t="shared" si="4"/>
-        <v>0.95192260531412809</v>
+        <v>0.95194863042836342</v>
       </c>
       <c r="R41" s="5">
         <v>889467</v>
@@ -7589,14 +7589,14 @@
       </c>
       <c r="T41" s="3">
         <f t="shared" si="5"/>
-        <v>328403</v>
+        <v>328425</v>
       </c>
       <c r="U41" s="5">
-        <v>849387</v>
+        <v>849409</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" si="6"/>
-        <v>0.95493930634863355</v>
+        <v>0.95496404026231441</v>
       </c>
       <c r="W41" s="5">
         <v>894020</v>
@@ -7606,14 +7606,14 @@
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="7"/>
-        <v>361341</v>
+        <v>361360</v>
       </c>
       <c r="Z41" s="5">
-        <v>855279</v>
+        <v>855298</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" si="8"/>
-        <v>0.95666651752757204</v>
+        <v>0.9566877698485492</v>
       </c>
       <c r="AB41" s="5">
         <v>1012178</v>
@@ -7623,14 +7623,14 @@
       </c>
       <c r="AD41" s="3">
         <f t="shared" si="9"/>
-        <v>420712</v>
+        <v>420726</v>
       </c>
       <c r="AE41" s="5">
-        <v>977762</v>
+        <v>977776</v>
       </c>
       <c r="AF41" s="4">
         <f t="shared" si="10"/>
-        <v>0.9659980754373243</v>
+        <v>0.96601190699659545</v>
       </c>
       <c r="AG41" s="5">
         <v>904846</v>
@@ -7640,14 +7640,14 @@
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="11"/>
-        <v>322116</v>
+        <v>322130</v>
       </c>
       <c r="AJ41" s="5">
-        <v>873172</v>
+        <v>873186</v>
       </c>
       <c r="AK41" s="4">
         <f t="shared" si="12"/>
-        <v>0.96499514834568534</v>
+        <v>0.96501062059179132</v>
       </c>
       <c r="AL41" s="5">
         <v>910192</v>
@@ -7657,14 +7657,14 @@
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="13"/>
-        <v>324170</v>
+        <v>324183</v>
       </c>
       <c r="AO41" s="5">
-        <v>879145</v>
+        <v>879158</v>
       </c>
       <c r="AP41" s="4">
         <f t="shared" si="14"/>
-        <v>0.96588961449891886</v>
+        <v>0.9659038971997117</v>
       </c>
       <c r="AQ41" s="3">
         <v>1025826</v>
@@ -7674,14 +7674,14 @@
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="15"/>
-        <v>359853</v>
+        <v>359868</v>
       </c>
       <c r="AT41" s="3">
-        <v>993431</v>
+        <v>993446</v>
       </c>
       <c r="AU41" s="4">
         <f t="shared" si="16"/>
-        <v>0.9684205703501374</v>
+        <v>0.96843519271299416</v>
       </c>
       <c r="AV41" s="5">
         <v>923071</v>
@@ -7691,14 +7691,14 @@
       </c>
       <c r="AX41" s="3">
         <f t="shared" si="17"/>
-        <v>308194</v>
+        <v>308208</v>
       </c>
       <c r="AY41" s="5">
-        <v>890920</v>
+        <v>890934</v>
       </c>
       <c r="AZ41" s="4">
         <f t="shared" si="18"/>
-        <v>0.96516952650446175</v>
+        <v>0.96518469326844847</v>
       </c>
       <c r="BA41" s="11">
         <v>907892</v>
@@ -7708,14 +7708,14 @@
       </c>
       <c r="BC41" s="3">
         <f t="shared" si="19"/>
-        <v>315658</v>
+        <v>315671</v>
       </c>
       <c r="BD41" s="5">
-        <v>897966</v>
+        <v>897979</v>
       </c>
       <c r="BE41" s="4">
         <f t="shared" si="20"/>
-        <v>0.98906698153524863</v>
+        <v>0.98908130041899256</v>
       </c>
       <c r="BF41" s="11">
         <v>1023930</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="BH41" s="3">
         <f t="shared" si="23"/>
-        <v>403376</v>
+        <v>403390</v>
       </c>
       <c r="BI41" s="5">
-        <v>1012283</v>
+        <v>1012297</v>
       </c>
       <c r="BJ41" s="4">
         <f t="shared" si="24"/>
-        <v>0.98862519898821211</v>
+        <v>0.98863887179787679</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7851,14 +7851,14 @@
       </c>
       <c r="AI42" s="3">
         <f t="shared" si="11"/>
-        <v>7693</v>
+        <v>7694</v>
       </c>
       <c r="AJ42" s="5">
-        <v>17755</v>
+        <v>17756</v>
       </c>
       <c r="AK42" s="4">
         <f t="shared" si="12"/>
-        <v>0.95534032822168413</v>
+        <v>0.95539413505515203</v>
       </c>
       <c r="AL42" s="5">
         <v>18498</v>
@@ -7868,14 +7868,14 @@
       </c>
       <c r="AN42" s="3">
         <f t="shared" si="13"/>
-        <v>7820</v>
+        <v>7821</v>
       </c>
       <c r="AO42" s="5">
-        <v>17816</v>
+        <v>17817</v>
       </c>
       <c r="AP42" s="4">
         <f t="shared" si="14"/>
-        <v>0.96313114931343924</v>
+        <v>0.96318520921180673</v>
       </c>
       <c r="AQ42" s="3">
         <v>20775</v>
@@ -7885,14 +7885,14 @@
       </c>
       <c r="AS42" s="3">
         <f t="shared" si="15"/>
-        <v>8455</v>
+        <v>8456</v>
       </c>
       <c r="AT42" s="3">
-        <v>20051</v>
+        <v>20052</v>
       </c>
       <c r="AU42" s="4">
         <f t="shared" si="16"/>
-        <v>0.96515042117930205</v>
+        <v>0.96519855595667869</v>
       </c>
       <c r="AV42" s="5">
         <v>18672</v>
@@ -7902,14 +7902,14 @@
       </c>
       <c r="AX42" s="3">
         <f t="shared" si="17"/>
-        <v>7437</v>
+        <v>7438</v>
       </c>
       <c r="AY42" s="5">
-        <v>17994</v>
+        <v>17995</v>
       </c>
       <c r="AZ42" s="4">
         <f t="shared" si="18"/>
-        <v>0.96368894601542421</v>
+        <v>0.96374250214224511</v>
       </c>
       <c r="BA42" s="10">
         <v>18422</v>
@@ -7919,14 +7919,14 @@
       </c>
       <c r="BC42" s="3">
         <f t="shared" si="19"/>
-        <v>7562</v>
+        <v>7563</v>
       </c>
       <c r="BD42" s="5">
-        <v>18116</v>
+        <v>18117</v>
       </c>
       <c r="BE42" s="4">
         <f t="shared" si="20"/>
-        <v>0.98338942568667898</v>
+        <v>0.98344370860927155</v>
       </c>
       <c r="BF42" s="10">
         <v>20562</v>
@@ -7936,14 +7936,14 @@
       </c>
       <c r="BH42" s="3">
         <f t="shared" si="23"/>
-        <v>9479</v>
+        <v>9480</v>
       </c>
       <c r="BI42" s="5">
-        <v>20431</v>
+        <v>20432</v>
       </c>
       <c r="BJ42" s="4">
         <f t="shared" si="24"/>
-        <v>0.9936290244139675</v>
+        <v>0.99367765781538764</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8172,14 +8172,14 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="0"/>
-        <v>151688</v>
+        <v>151691</v>
       </c>
       <c r="F44" s="5">
-        <v>296320</v>
+        <v>296323</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="1"/>
-        <v>0.87115276630398031</v>
+        <v>0.87116158602016192</v>
       </c>
       <c r="H44" s="5">
         <v>343940</v>
@@ -8189,14 +8189,14 @@
       </c>
       <c r="J44" s="3">
         <f t="shared" si="2"/>
-        <v>148674</v>
+        <v>148676</v>
       </c>
       <c r="K44" s="5">
-        <v>299524</v>
+        <v>299526</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" si="3"/>
-        <v>0.87086119672035822</v>
+        <v>0.87086701168808511</v>
       </c>
       <c r="M44" s="9">
         <v>415294</v>
@@ -8208,11 +8208,11 @@
         <v>362232</v>
       </c>
       <c r="P44" s="5">
-        <v>363094</v>
+        <v>363097</v>
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="4"/>
-        <v>0.87430591340110864</v>
+        <v>0.87431313719918902</v>
       </c>
       <c r="R44" s="5">
         <v>349377</v>
@@ -8222,14 +8222,14 @@
       </c>
       <c r="T44" s="3">
         <f t="shared" si="5"/>
-        <v>152719</v>
+        <v>152722</v>
       </c>
       <c r="U44" s="5">
-        <v>304258</v>
+        <v>304261</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" si="6"/>
-        <v>0.87085869991441911</v>
+        <v>0.87086728662733948</v>
       </c>
       <c r="W44" s="5">
         <v>352323</v>
@@ -8239,14 +8239,14 @@
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="7"/>
-        <v>164139</v>
+        <v>164142</v>
       </c>
       <c r="Z44" s="5">
-        <v>307799</v>
+        <v>307802</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="8"/>
-        <v>0.87362732492627504</v>
+        <v>0.8736358398401467</v>
       </c>
       <c r="AB44" s="5">
         <v>424236</v>
@@ -8256,14 +8256,14 @@
       </c>
       <c r="AD44" s="3">
         <f t="shared" si="9"/>
-        <v>208462</v>
+        <v>208464</v>
       </c>
       <c r="AE44" s="5">
-        <v>382948</v>
+        <v>382950</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="10"/>
-        <v>0.90267681196315264</v>
+        <v>0.90268152632025567</v>
       </c>
       <c r="AG44" s="5">
         <v>358309</v>
@@ -8273,14 +8273,14 @@
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="11"/>
-        <v>154198</v>
+        <v>154201</v>
       </c>
       <c r="AJ44" s="5">
-        <v>319717</v>
+        <v>319720</v>
       </c>
       <c r="AK44" s="4">
         <f t="shared" si="12"/>
-        <v>0.89229408136552524</v>
+        <v>0.89230245402711073</v>
       </c>
       <c r="AL44" s="5">
         <v>359722</v>
@@ -8290,14 +8290,14 @@
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="13"/>
-        <v>150213</v>
+        <v>150217</v>
       </c>
       <c r="AO44" s="5">
-        <v>323554</v>
+        <v>323558</v>
       </c>
       <c r="AP44" s="4">
         <f t="shared" si="14"/>
-        <v>0.89945569078343834</v>
+        <v>0.89946681048142729</v>
       </c>
       <c r="AQ44" s="3">
         <v>432157</v>
@@ -8307,14 +8307,14 @@
       </c>
       <c r="AS44" s="3">
         <f t="shared" si="15"/>
-        <v>178597</v>
+        <v>178601</v>
       </c>
       <c r="AT44" s="3">
-        <v>391664</v>
+        <v>391668</v>
       </c>
       <c r="AU44" s="4">
         <f t="shared" si="16"/>
-        <v>0.90630025661970071</v>
+        <v>0.90630951251512759</v>
       </c>
       <c r="AV44" s="5">
         <v>367733</v>
@@ -8324,14 +8324,14 @@
       </c>
       <c r="AX44" s="3">
         <f t="shared" si="17"/>
-        <v>145692</v>
+        <v>145696</v>
       </c>
       <c r="AY44" s="5">
-        <v>327662</v>
+        <v>327666</v>
       </c>
       <c r="AZ44" s="4">
         <f t="shared" si="18"/>
-        <v>0.89103235227733169</v>
+        <v>0.89104322973461725</v>
       </c>
       <c r="BA44" s="10">
         <v>337773</v>
@@ -8341,14 +8341,14 @@
       </c>
       <c r="BC44" s="3">
         <f t="shared" si="19"/>
-        <v>150755</v>
+        <v>150760</v>
       </c>
       <c r="BD44" s="5">
-        <v>331423</v>
+        <v>331428</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="20"/>
-        <v>0.9812003919792287</v>
+        <v>0.98121519482018993</v>
       </c>
       <c r="BF44" s="10">
         <v>408499</v>
@@ -8358,14 +8358,14 @@
       </c>
       <c r="BH44" s="3">
         <f t="shared" si="23"/>
-        <v>201486</v>
+        <v>201491</v>
       </c>
       <c r="BI44" s="5">
-        <v>400220</v>
+        <v>400225</v>
       </c>
       <c r="BJ44" s="4">
         <f t="shared" si="24"/>
-        <v>0.97973312052171491</v>
+        <v>0.97974536045375871</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8383,14 +8383,14 @@
       </c>
       <c r="E45" s="3">
         <f t="shared" si="0"/>
-        <v>112352</v>
+        <v>112355</v>
       </c>
       <c r="F45" s="5">
-        <v>232576</v>
+        <v>232579</v>
       </c>
       <c r="G45" s="4">
         <f t="shared" si="1"/>
-        <v>0.9296643908990615</v>
+        <v>0.92967638264873764</v>
       </c>
       <c r="H45" s="5">
         <v>249985</v>
@@ -8400,14 +8400,14 @@
       </c>
       <c r="J45" s="3">
         <f t="shared" si="2"/>
-        <v>104748</v>
+        <v>104751</v>
       </c>
       <c r="K45" s="5">
-        <v>234326</v>
+        <v>234329</v>
       </c>
       <c r="L45" s="4">
         <f t="shared" si="3"/>
-        <v>0.93736024161449683</v>
+        <v>0.93737224233454008</v>
       </c>
       <c r="M45" s="9">
         <v>300587</v>
@@ -8419,11 +8419,11 @@
         <v>284476</v>
       </c>
       <c r="P45" s="5">
-        <v>285015</v>
+        <v>285017</v>
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="4"/>
-        <v>0.94819469903888054</v>
+        <v>0.94820135268657657</v>
       </c>
       <c r="R45" s="5">
         <v>247712</v>
@@ -8433,14 +8433,14 @@
       </c>
       <c r="T45" s="3">
         <f t="shared" si="5"/>
-        <v>109593</v>
+        <v>109595</v>
       </c>
       <c r="U45" s="5">
-        <v>235852</v>
+        <v>235854</v>
       </c>
       <c r="V45" s="4">
         <f t="shared" si="6"/>
-        <v>0.95212181888644876</v>
+        <v>0.95212989277871074</v>
       </c>
       <c r="W45" s="5">
         <v>250023</v>
@@ -8450,14 +8450,14 @@
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="7"/>
-        <v>116273</v>
+        <v>116275</v>
       </c>
       <c r="Z45" s="5">
-        <v>237775</v>
+        <v>237777</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="8"/>
-        <v>0.95101250684936989</v>
+        <v>0.95102050611343758</v>
       </c>
       <c r="AB45" s="5">
         <v>306096</v>
@@ -8467,14 +8467,14 @@
       </c>
       <c r="AD45" s="3">
         <f t="shared" si="9"/>
-        <v>151897</v>
+        <v>151899</v>
       </c>
       <c r="AE45" s="5">
-        <v>293863</v>
+        <v>293865</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="10"/>
-        <v>0.96003541372641266</v>
+        <v>0.96004194762427475</v>
       </c>
       <c r="AG45" s="5">
         <v>252706</v>
@@ -8484,14 +8484,14 @@
       </c>
       <c r="AI45" s="3">
         <f t="shared" si="11"/>
-        <v>106720</v>
+        <v>106722</v>
       </c>
       <c r="AJ45" s="5">
-        <v>243710</v>
+        <v>243712</v>
       </c>
       <c r="AK45" s="4">
         <f t="shared" si="12"/>
-        <v>0.96440132011111723</v>
+        <v>0.96440923444635263</v>
       </c>
       <c r="AL45" s="5">
         <v>254538</v>
@@ -8501,14 +8501,14 @@
       </c>
       <c r="AN45" s="3">
         <f t="shared" si="13"/>
-        <v>96697</v>
+        <v>96699</v>
       </c>
       <c r="AO45" s="5">
-        <v>246024</v>
+        <v>246026</v>
       </c>
       <c r="AP45" s="4">
         <f t="shared" si="14"/>
-        <v>0.96655116328406765</v>
+        <v>0.96655902065703347</v>
       </c>
       <c r="AQ45" s="3">
         <v>310997</v>
@@ -8518,14 +8518,14 @@
       </c>
       <c r="AS45" s="3">
         <f t="shared" si="15"/>
-        <v>122782</v>
+        <v>122784</v>
       </c>
       <c r="AT45" s="3">
-        <v>299909</v>
+        <v>299911</v>
       </c>
       <c r="AU45" s="4">
         <f t="shared" si="16"/>
-        <v>0.96434692296067159</v>
+        <v>0.96435335389087351</v>
       </c>
       <c r="AV45" s="5">
         <v>259359</v>
@@ -8535,14 +8535,14 @@
       </c>
       <c r="AX45" s="3">
         <f t="shared" si="17"/>
-        <v>98678</v>
+        <v>98680</v>
       </c>
       <c r="AY45" s="5">
-        <v>248520</v>
+        <v>248522</v>
       </c>
       <c r="AZ45" s="4">
         <f t="shared" si="18"/>
-        <v>0.9582085063560547</v>
+        <v>0.95821621767511445</v>
       </c>
       <c r="BA45" s="10">
         <v>254394</v>
@@ -8552,14 +8552,14 @@
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="19"/>
-        <v>102918</v>
+        <v>102919</v>
       </c>
       <c r="BD45" s="5">
-        <v>250486</v>
+        <v>250487</v>
       </c>
       <c r="BE45" s="4">
         <f t="shared" si="20"/>
-        <v>0.98463800246861166</v>
+        <v>0.98464193337893191</v>
       </c>
       <c r="BF45" s="10">
         <v>309142</v>
@@ -9016,15 +9016,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>2891942</v>
+        <v>2892021</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>6970456</v>
+        <v>6970535</v>
       </c>
       <c r="G48" s="6">
         <f>F48/C48</f>
-        <v>0.94238611968223795</v>
+        <v>0.94239680026087647</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -9036,15 +9036,15 @@
       </c>
       <c r="J48" s="8">
         <f t="shared" ref="J48" si="25">K48-I48</f>
-        <v>2779712</v>
+        <v>2779787</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>7078260</v>
+        <v>7078335</v>
       </c>
       <c r="L48" s="6">
         <f t="shared" ref="L48" si="26">K48/H48</f>
-        <v>0.94432452191825045</v>
+        <v>0.944334527815059</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -9056,15 +9056,15 @@
       </c>
       <c r="O48" s="7">
         <f t="shared" ref="O48" si="27">P48-N48</f>
-        <v>4723168</v>
+        <v>4723285</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>11176219</v>
+        <v>11176336</v>
       </c>
       <c r="Q48" s="6">
         <f t="shared" ref="Q48" si="28">P48/M48</f>
-        <v>0.94384135736185637</v>
+        <v>0.94385123811301297</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -9076,15 +9076,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>2871406</v>
+        <v>2871488</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>7104461</v>
+        <v>7104543</v>
       </c>
       <c r="V48" s="6">
         <f>U48/R48</f>
-        <v>0.94180889546003066</v>
+        <v>0.9418197658595483</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -9096,15 +9096,15 @@
       </c>
       <c r="Y48" s="8">
         <f t="shared" ref="Y48" si="29">Z48-X48</f>
-        <v>3037784</v>
+        <v>3037865</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>7205359</v>
+        <v>7205440</v>
       </c>
       <c r="AA48" s="6">
         <f t="shared" ref="AA48" si="30">Z48/W48</f>
-        <v>0.94421271652909755</v>
+        <v>0.94422333102173273</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -9116,15 +9116,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>5143197</v>
+        <v>5143286</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>11574008</v>
+        <v>11574097</v>
       </c>
       <c r="AF48" s="6">
         <f>AE48/AB48</f>
-        <v>0.96126265341862605</v>
+        <v>0.96127004518612391</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -9136,15 +9136,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>2802471</v>
+        <v>2802544</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7356215</v>
+        <v>7356288</v>
       </c>
       <c r="AK48" s="6">
         <f>AJ48/AG48</f>
-        <v>0.95453863627457414</v>
+        <v>0.95454810871664497</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -9156,15 +9156,15 @@
       </c>
       <c r="AN48" s="8">
         <f t="shared" ref="AN48" si="31">AO48-AM48</f>
-        <v>2784669</v>
+        <v>2784744</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>7459805</v>
+        <v>7459880</v>
       </c>
       <c r="AP48" s="6">
         <f t="shared" ref="AP48" si="32">AO48/AL48</f>
-        <v>0.956479800759793</v>
+        <v>0.95648941709494617</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -9176,15 +9176,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>4440120</v>
+        <v>4440225</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>11781066</v>
+        <v>11781171</v>
       </c>
       <c r="AU48" s="6">
         <f>AT48/AQ48</f>
-        <v>0.9632726262118414</v>
+        <v>0.96328121148126888</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -9196,15 +9196,15 @@
       </c>
       <c r="AX48" s="8">
         <f t="shared" ref="AX48" si="33">AY48-AW48</f>
-        <v>2608360</v>
+        <v>2608442</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>7517126</v>
+        <v>7517208</v>
       </c>
       <c r="AZ48" s="6">
         <f t="shared" ref="AZ48" si="34">AY48/AV48</f>
-        <v>0.94124215587294835</v>
+        <v>0.94125242334176307</v>
       </c>
       <c r="BA48" s="7">
         <f>SUM(BA10:BA47)</f>
@@ -9216,15 +9216,15 @@
       </c>
       <c r="BC48" s="8">
         <f t="shared" ref="BC48" si="35">BD48-BB48</f>
-        <v>2771618</v>
+        <v>2771698</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>7629987</v>
+        <v>7630067</v>
       </c>
       <c r="BE48" s="6">
         <f t="shared" ref="BE48" si="36">BD48/BA48</f>
-        <v>0.98815443002171099</v>
+        <v>0.98816479076733232</v>
       </c>
       <c r="BF48" s="7">
         <f>SUM(BF10:BF47)</f>
@@ -9236,15 +9236,15 @@
       </c>
       <c r="BH48" s="8">
         <f>BI48-BG48</f>
-        <v>5013827</v>
+        <v>5013932</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>12006208</v>
+        <v>12006313</v>
       </c>
       <c r="BJ48" s="6">
         <f>BI48/BF48</f>
-        <v>0.99492807613363365</v>
+        <v>0.99493677725292073</v>
       </c>
     </row>
   </sheetData>
